--- a/EFETIVIDADE.xlsx
+++ b/EFETIVIDADE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://spotpromo.sharepoint.com/sites/bko.pribeiro/Documentos Compartilhados/PRibeiro/BAUDUCCO TMP/20 - EFETIVIDADE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="829" documentId="13_ncr:1_{C64068DB-D04A-49E7-B037-1281E1EE8D6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8568F00D-16E1-4823-9ABC-1753563D026C}"/>
+  <xr:revisionPtr revIDLastSave="830" documentId="13_ncr:1_{C64068DB-D04A-49E7-B037-1281E1EE8D6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C935DEFC-C7C3-42BA-86F1-DB433C34F2D8}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="121">
   <si>
     <t>ROTA</t>
   </si>
@@ -308,12 +308,6 @@
     <t>BH - R MARTE, 505 - CONTAGEM/MG</t>
   </si>
   <si>
-    <t>07:39</t>
-  </si>
-  <si>
-    <t>08:07</t>
-  </si>
-  <si>
     <t>VESPASIANO</t>
   </si>
   <si>
@@ -326,22 +320,82 @@
     <t>SUPERMERCADO REX - RUA MISSENO DE PADUA, 555 - LAVRAS/MG</t>
   </si>
   <si>
-    <t>06:56</t>
-  </si>
-  <si>
-    <t>07:00</t>
-  </si>
-  <si>
-    <t>06:49</t>
-  </si>
-  <si>
     <t>VILA SUL - AVENIDA SILVIO MONTEIRO DOS SANTOS , 180 - POÇOS DE CALDAS/MG</t>
   </si>
   <si>
-    <t>07:28</t>
-  </si>
-  <si>
     <t>07:31  08:59</t>
+  </si>
+  <si>
+    <t>07:38</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>07:45</t>
+  </si>
+  <si>
+    <t>08:14</t>
+  </si>
+  <si>
+    <t>07:00  08:20</t>
+  </si>
+  <si>
+    <t>08:40</t>
+  </si>
+  <si>
+    <t>07:46</t>
+  </si>
+  <si>
+    <t>07:43</t>
+  </si>
+  <si>
+    <t>06:59</t>
+  </si>
+  <si>
+    <t>09:21  11:35</t>
+  </si>
+  <si>
+    <t>14:12  16:11</t>
+  </si>
+  <si>
+    <t>06:49  09:37</t>
+  </si>
+  <si>
+    <t>10:00  12:28</t>
+  </si>
+  <si>
+    <t>08:07  17:31</t>
+  </si>
+  <si>
+    <t>06:56  12:00</t>
+  </si>
+  <si>
+    <t>13:00  16:00</t>
+  </si>
+  <si>
+    <t>APRESENTOU ATESTADO</t>
+  </si>
+  <si>
+    <t>07:39  14:04</t>
+  </si>
+  <si>
+    <t>14:28  16:44</t>
+  </si>
+  <si>
+    <t>07:28  14:10</t>
+  </si>
+  <si>
+    <t>14:30</t>
+  </si>
+  <si>
+    <t>07:00  11:54</t>
+  </si>
+  <si>
+    <t>13:19  16:01</t>
+  </si>
+  <si>
+    <t>INFORMOU QUE A TELA QUEBROU, MAS ESTÁ EM CAMPO.</t>
   </si>
 </sst>
 </file>
@@ -489,33 +543,54 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{CCF9025B-0226-4389-80E6-00916CE7E00D}"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="8">
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -537,12 +612,14 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor rgb="FFEF5350"/>
+          <bgColor rgb="FFFFA726"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
         <right style="thin">
           <color auto="1"/>
         </right>
@@ -552,6 +629,8 @@
         <bottom style="thin">
           <color auto="1"/>
         </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -570,28 +649,6 @@
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <extLst>
@@ -606,19 +663,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A4474625-D582-4F1B-AA27-C9E6E4248EEA}" name="Tabela1" displayName="Tabela1" ref="A1:G53" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="A1:G53" xr:uid="{A4474625-D582-4F1B-AA27-C9E6E4248EEA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A4474625-D582-4F1B-AA27-C9E6E4248EEA}" name="Tabela1" displayName="Tabela1" ref="A1:G74" totalsRowShown="0" headerRowDxfId="0" headerRowCellStyle="Normal 2">
+  <autoFilter ref="A1:G74" xr:uid="{A4474625-D582-4F1B-AA27-C9E6E4248EEA}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G53">
     <sortCondition descending="1" ref="E1:E53"/>
   </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{8C18829A-5E6C-4A32-820C-446F688CFF40}" name="ROTA" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{DDEFB02C-4E13-4B44-94BC-0CCC56093F37}" name="CIDADE" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{9F96407A-940B-423E-9DF5-FB53E8D959FF}" name="LOJA" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{5015EE94-DAE4-4146-9FAD-52E70AC74336}" name="PROMOTOR(A)" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{5020E202-8D33-4205-AA6B-6F5C1729064E}" name="DATA" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{9E844A3F-01F3-4B57-A20A-B083E62DB332}" name="STATUS" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{106C1984-84DF-496B-AC73-8C510020C178}" name="OBSERVAÇÃO" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{8C18829A-5E6C-4A32-820C-446F688CFF40}" name="ROTA" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{DDEFB02C-4E13-4B44-94BC-0CCC56093F37}" name="CIDADE" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{9F96407A-940B-423E-9DF5-FB53E8D959FF}" name="LOJA" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{5015EE94-DAE4-4146-9FAD-52E70AC74336}" name="PROMOTOR(A)" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{5020E202-8D33-4205-AA6B-6F5C1729064E}" name="DATA" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{9E844A3F-01F3-4B57-A20A-B083E62DB332}" name="STATUS" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{106C1984-84DF-496B-AC73-8C510020C178}" name="OBSERVAÇÃO" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -941,7 +998,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" style="4" customWidth="1"/>
@@ -985,16 +1042,16 @@
         <v>7</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>53</v>
+        <v>46170</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -1005,38 +1062,37 @@
         <v>7</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>102</v>
+        <v>46170</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="D4" s="17" t="s">
+      <c r="C4" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G4" s="17"/>
+        <v>46170</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="5" spans="1:7" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
@@ -1052,10 +1108,10 @@
         <v>5</v>
       </c>
       <c r="E5" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>53</v>
+        <v>46170</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -1072,30 +1128,30 @@
         <v>5</v>
       </c>
       <c r="E6" s="7">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E7" s="7">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -1106,944 +1162,1380 @@
         <v>18</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E8" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>53</v>
+        <v>46170</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>96</v>
+        <v>58</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E9" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>53</v>
+        <v>46170</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B11" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D10" s="4" t="s">
+      <c r="C13" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
+      <c r="E13" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D11" s="4" t="s">
+      <c r="B14" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G11" s="5" t="s">
+      <c r="E14" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="G14" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
+    <row r="15" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B15" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D12" s="4" t="s">
+      <c r="C15" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G12" s="5" t="s">
+      <c r="E15" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="G15" s="5" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E14" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E15" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>100</v>
+        <v>14</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E16" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>53</v>
+        <v>46170</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E17" s="7">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E18" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F18" s="15" t="s">
-        <v>98</v>
+        <v>46170</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F19" s="15" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B20" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C20" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D21" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E21" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="7">
         <v>46169</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="F22" s="11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E25" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E26" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E27" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E28" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F28" s="8" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" t="s">
-        <v>46</v>
-      </c>
-      <c r="D20" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>6</v>
-      </c>
-      <c r="B21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" t="s">
-        <v>47</v>
-      </c>
-      <c r="D21" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F21" s="14" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F22" s="14" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="E23" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F23" s="11" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="E24" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="E25" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F25" s="11" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B26" s="12" t="s">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E30" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B32" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C26" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E26" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G26" s="5"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="D27" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E27" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G27" s="5"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C28" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E28" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F28" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="G28" s="5"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="E29" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F29" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="G29" s="6"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B30" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="E30" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F30" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="G30" s="6"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B31" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="C31" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D31" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="E31" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F31" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="G31" s="6"/>
-    </row>
-    <row r="32" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A32" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B32" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D32" s="12" t="s">
+      <c r="C32" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D32" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E32" s="7">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="F32" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="G32" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A33" s="12" t="s">
+      <c r="G32" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B33" s="12" t="s">
+      <c r="B33" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C33" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D33" s="12" t="s">
+      <c r="C33" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D33" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E33" s="7">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="F33" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="G33" s="5" t="s">
-        <v>31</v>
+      <c r="G33" s="4" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="12" t="s">
+      <c r="A34" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B34" s="12" t="s">
+      <c r="B34" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C34" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D34" s="12" t="s">
+      <c r="C34" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D34" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E34" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E35" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F37" s="12" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E38" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E39" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F39" s="11" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>6</v>
+      </c>
+      <c r="B40" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" t="s">
+        <v>47</v>
+      </c>
+      <c r="D40" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="7">
         <v>46168</v>
       </c>
-      <c r="F34" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="G34" s="5"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B35" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="D35" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="E35" s="7">
+      <c r="F40" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="G40" s="5"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>6</v>
+      </c>
+      <c r="B41" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" t="s">
+        <v>48</v>
+      </c>
+      <c r="D41" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="7">
         <v>46168</v>
       </c>
-      <c r="F35" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="G35" s="6"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B36" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C36" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D36" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E36" s="7">
+      <c r="F41" s="13" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>6</v>
+      </c>
+      <c r="B42" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" t="s">
+        <v>46</v>
+      </c>
+      <c r="D42" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="7">
         <v>46168</v>
       </c>
-      <c r="F36" s="11" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B37" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C37" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="D37" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E37" s="7">
+      <c r="F42" s="12" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>3</v>
+      </c>
+      <c r="B43" t="s">
+        <v>4</v>
+      </c>
+      <c r="C43" t="s">
+        <v>29</v>
+      </c>
+      <c r="D43" t="s">
+        <v>5</v>
+      </c>
+      <c r="E43" s="7">
         <v>46168</v>
       </c>
-      <c r="F37" s="11" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="B38" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C38" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D38" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="E38" s="7">
+      <c r="F43" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="G43" s="5"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B44" t="s">
+        <v>4</v>
+      </c>
+      <c r="C44" t="s">
+        <v>28</v>
+      </c>
+      <c r="D44" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="7">
         <v>46168</v>
       </c>
-      <c r="F38" s="14" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="B39" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C39" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="D39" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="E39" s="7">
+      <c r="F44" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="G44" s="6"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>3</v>
+      </c>
+      <c r="B45" t="s">
+        <v>4</v>
+      </c>
+      <c r="C45" t="s">
+        <v>44</v>
+      </c>
+      <c r="D45" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="7">
         <v>46168</v>
       </c>
-      <c r="F39" s="14" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E40" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E41" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F41" s="9" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E42" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F42" s="10" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E43" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F43" s="10" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="4" t="s">
+      <c r="F45" s="11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
         <v>16</v>
       </c>
-      <c r="B44" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D44" s="4" t="s">
+      <c r="B46" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46" t="s">
+        <v>36</v>
+      </c>
+      <c r="D46" t="s">
         <v>17</v>
       </c>
-      <c r="E44" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F44" s="9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="4" t="s">
+      <c r="E46" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F46" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="G46" s="6"/>
+    </row>
+    <row r="47" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
         <v>16</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B47" t="s">
         <v>18</v>
       </c>
-      <c r="C45" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D45" s="4" t="s">
+      <c r="C47" t="s">
+        <v>34</v>
+      </c>
+      <c r="D47" t="s">
         <v>17</v>
       </c>
-      <c r="E45" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F45" s="8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E46" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F46" s="9" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A47" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>20</v>
-      </c>
       <c r="E47" s="7">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>53</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>31</v>
+        <v>120</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A48" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B48" s="4" t="s">
+      <c r="A48" t="s">
+        <v>16</v>
+      </c>
+      <c r="B48" t="s">
         <v>18</v>
       </c>
-      <c r="C48" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>20</v>
+      <c r="C48" t="s">
+        <v>35</v>
+      </c>
+      <c r="D48" t="s">
+        <v>17</v>
       </c>
       <c r="E48" s="7">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="F48" s="8" t="s">
         <v>53</v>
       </c>
       <c r="G48" s="5" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>21</v>
+      </c>
+      <c r="B49" t="s">
+        <v>39</v>
+      </c>
+      <c r="C49" t="s">
+        <v>40</v>
+      </c>
+      <c r="D49" t="s">
+        <v>23</v>
+      </c>
+      <c r="E49" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F49" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="G49" s="5"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>21</v>
+      </c>
+      <c r="B50" t="s">
+        <v>39</v>
+      </c>
+      <c r="C50" t="s">
+        <v>41</v>
+      </c>
+      <c r="D50" t="s">
+        <v>23</v>
+      </c>
+      <c r="E50" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F50" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="G50" s="6"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>21</v>
+      </c>
+      <c r="B51" t="s">
+        <v>22</v>
+      </c>
+      <c r="C51" t="s">
+        <v>38</v>
+      </c>
+      <c r="D51" t="s">
+        <v>23</v>
+      </c>
+      <c r="E51" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F51" s="13" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>19</v>
+      </c>
+      <c r="B52" t="s">
+        <v>18</v>
+      </c>
+      <c r="C52" t="s">
+        <v>37</v>
+      </c>
+      <c r="D52" t="s">
+        <v>20</v>
+      </c>
+      <c r="E52" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G52" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="4" t="s">
+    <row r="53" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>19</v>
+      </c>
+      <c r="B53" t="s">
+        <v>18</v>
+      </c>
+      <c r="C53" t="s">
+        <v>32</v>
+      </c>
+      <c r="D53" t="s">
+        <v>20</v>
+      </c>
+      <c r="E53" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
         <v>11</v>
       </c>
-      <c r="B49" s="4" t="s">
+      <c r="B54" t="s">
         <v>10</v>
       </c>
-      <c r="C49" s="4" t="s">
+      <c r="C54" t="s">
         <v>14</v>
       </c>
-      <c r="D49" s="4" t="s">
+      <c r="D54" t="s">
         <v>15</v>
       </c>
-      <c r="E49" s="7">
+      <c r="E54" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F54" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="G54" s="5"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>11</v>
+      </c>
+      <c r="B55" t="s">
+        <v>10</v>
+      </c>
+      <c r="C55" t="s">
+        <v>33</v>
+      </c>
+      <c r="D55" t="s">
+        <v>15</v>
+      </c>
+      <c r="E55" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F55" s="13" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>12</v>
+      </c>
+      <c r="B56" t="s">
+        <v>9</v>
+      </c>
+      <c r="C56" t="s">
+        <v>30</v>
+      </c>
+      <c r="D56" t="s">
+        <v>13</v>
+      </c>
+      <c r="E56" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F56" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="G56" s="5"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>12</v>
+      </c>
+      <c r="B57" t="s">
+        <v>9</v>
+      </c>
+      <c r="C57" t="s">
+        <v>45</v>
+      </c>
+      <c r="D57" t="s">
+        <v>13</v>
+      </c>
+      <c r="E57" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F57" s="11" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>24</v>
+      </c>
+      <c r="B58" t="s">
+        <v>25</v>
+      </c>
+      <c r="C58" t="s">
+        <v>27</v>
+      </c>
+      <c r="D58" t="s">
+        <v>26</v>
+      </c>
+      <c r="E58" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F58" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="G58" s="6"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>24</v>
+      </c>
+      <c r="B59" t="s">
+        <v>25</v>
+      </c>
+      <c r="C59" t="s">
+        <v>42</v>
+      </c>
+      <c r="D59" t="s">
+        <v>26</v>
+      </c>
+      <c r="E59" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F59" s="13" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A60" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="7">
         <v>46167</v>
       </c>
-      <c r="F49" s="9" t="s">
+      <c r="F60" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A61" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E61" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A62" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E62" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F62" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A63" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E63" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F63" s="10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A64" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D64" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E64" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G64" s="5" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A65" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E65" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A66" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E66" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A67" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E67" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F67" s="9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A68" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E68" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A69" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E69" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G69" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A70" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E70" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F70" s="9" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="4" t="s">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A71" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="B71" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C50" s="4" t="s">
+      <c r="C71" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="D71" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E50" s="7">
+      <c r="E71" s="7">
         <v>46167</v>
       </c>
-      <c r="F50" s="10" t="s">
+      <c r="F71" s="10" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="4" t="s">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A72" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="B72" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C51" s="4" t="s">
+      <c r="C72" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D51" s="4" t="s">
+      <c r="D72" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E51" s="7">
+      <c r="E72" s="7">
         <v>46167</v>
       </c>
-      <c r="F51" s="10" t="s">
+      <c r="F72" s="10" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="4" t="s">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A73" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B73" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="C73" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="4" t="s">
+      <c r="D73" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E52" s="7">
+      <c r="E73" s="7">
         <v>46167</v>
       </c>
-      <c r="F52" s="9" t="s">
+      <c r="F73" s="9" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="4" t="s">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A74" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="B74" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C53" s="4" t="s">
+      <c r="C74" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D53" s="4" t="s">
+      <c r="D74" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E53" s="7">
+      <c r="E74" s="7">
         <v>46167</v>
       </c>
-      <c r="F53" s="9" t="s">
+      <c r="F74" s="18" t="s">
         <v>64</v>
       </c>
     </row>
@@ -2067,15 +2559,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100AC3CF276C202334E979D7C4EA00D1CCA" ma:contentTypeVersion="13" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="fb5f1640dc82e33e0e3c6b4a833ae52f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6b3feda4-8a83-4113-98ac-b9b0c9bd9eab" xmlns:ns3="6ca87d14-fc9d-4fcf-a42b-2754e6b3d00d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dc11f865ff45eacf010d723a908863aa" ns2:_="" ns3:_="">
     <xsd:import namespace="6b3feda4-8a83-4113-98ac-b9b0c9bd9eab"/>
@@ -2282,6 +2765,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFC5C71E-79D6-437C-A06A-B0BD52E89317}">
   <ds:schemaRefs>
@@ -2294,14 +2786,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6F72255-F15E-4B46-A16C-2F18C675CB37}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E295317-F47C-4C92-88FC-9DAD72755AAC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2318,4 +2802,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6F72255-F15E-4B46-A16C-2F18C675CB37}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/EFETIVIDADE.xlsx
+++ b/EFETIVIDADE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://spotpromo.sharepoint.com/sites/bko.pribeiro/Documentos Compartilhados/PRibeiro/BAUDUCCO TMP/20 - EFETIVIDADE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="830" documentId="13_ncr:1_{C64068DB-D04A-49E7-B037-1281E1EE8D6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C935DEFC-C7C3-42BA-86F1-DB433C34F2D8}"/>
+  <xr:revisionPtr revIDLastSave="852" documentId="13_ncr:1_{C64068DB-D04A-49E7-B037-1281E1EE8D6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F4AFE73-FD97-47CA-9FA3-007CC4A13E3F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="134">
   <si>
     <t>ROTA</t>
   </si>
@@ -326,33 +326,9 @@
     <t>07:31  08:59</t>
   </si>
   <si>
-    <t>07:38</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>07:45</t>
-  </si>
-  <si>
-    <t>08:14</t>
-  </si>
-  <si>
     <t>07:00  08:20</t>
   </si>
   <si>
-    <t>08:40</t>
-  </si>
-  <si>
-    <t>07:46</t>
-  </si>
-  <si>
-    <t>07:43</t>
-  </si>
-  <si>
-    <t>06:59</t>
-  </si>
-  <si>
     <t>09:21  11:35</t>
   </si>
   <si>
@@ -396,6 +372,69 @@
   </si>
   <si>
     <t>INFORMOU QUE A TELA QUEBROU, MAS ESTÁ EM CAMPO.</t>
+  </si>
+  <si>
+    <t>06:59  11:18</t>
+  </si>
+  <si>
+    <t>07:38  09:36</t>
+  </si>
+  <si>
+    <t>07:43  11:49</t>
+  </si>
+  <si>
+    <t>07:45  14:40</t>
+  </si>
+  <si>
+    <t>07:46  13:41</t>
+  </si>
+  <si>
+    <t>08:14  13:19</t>
+  </si>
+  <si>
+    <t>08:40  11:30</t>
+  </si>
+  <si>
+    <t>10:02  12:08</t>
+  </si>
+  <si>
+    <t>12:05  17:21</t>
+  </si>
+  <si>
+    <t>12:27  16:08</t>
+  </si>
+  <si>
+    <t>12:57  16:00</t>
+  </si>
+  <si>
+    <t>13:20  17:01</t>
+  </si>
+  <si>
+    <t>13:46</t>
+  </si>
+  <si>
+    <t>13:51  16:10</t>
+  </si>
+  <si>
+    <t>14:50  15:08</t>
+  </si>
+  <si>
+    <t>06:55</t>
+  </si>
+  <si>
+    <t>07:00</t>
+  </si>
+  <si>
+    <t>07:30  08:54</t>
+  </si>
+  <si>
+    <t>07:39</t>
+  </si>
+  <si>
+    <t>07:40</t>
+  </si>
+  <si>
+    <t>08:01</t>
   </si>
 </sst>
 </file>
@@ -549,20 +588,20 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -570,25 +609,6 @@
     <cellStyle name="Normal 2" xfId="1" xr:uid="{CCF9025B-0226-4389-80E6-00916CE7E00D}"/>
   </cellStyles>
   <dxfs count="8">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -649,6 +669,25 @@
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <extLst>
@@ -663,19 +702,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A4474625-D582-4F1B-AA27-C9E6E4248EEA}" name="Tabela1" displayName="Tabela1" ref="A1:G74" totalsRowShown="0" headerRowDxfId="0" headerRowCellStyle="Normal 2">
-  <autoFilter ref="A1:G74" xr:uid="{A4474625-D582-4F1B-AA27-C9E6E4248EEA}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G53">
-    <sortCondition descending="1" ref="E1:E53"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A4474625-D582-4F1B-AA27-C9E6E4248EEA}" name="Tabela1" displayName="Tabela1" ref="A1:G93" totalsRowShown="0" headerRowDxfId="7" headerRowCellStyle="Normal 2">
+  <autoFilter ref="A1:G93" xr:uid="{A4474625-D582-4F1B-AA27-C9E6E4248EEA}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G93">
+    <sortCondition descending="1" ref="E1:E93"/>
   </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{8C18829A-5E6C-4A32-820C-446F688CFF40}" name="ROTA" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{DDEFB02C-4E13-4B44-94BC-0CCC56093F37}" name="CIDADE" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{9F96407A-940B-423E-9DF5-FB53E8D959FF}" name="LOJA" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{5015EE94-DAE4-4146-9FAD-52E70AC74336}" name="PROMOTOR(A)" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{5020E202-8D33-4205-AA6B-6F5C1729064E}" name="DATA" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{9E844A3F-01F3-4B57-A20A-B083E62DB332}" name="STATUS" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{106C1984-84DF-496B-AC73-8C510020C178}" name="OBSERVAÇÃO" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{8C18829A-5E6C-4A32-820C-446F688CFF40}" name="ROTA" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{DDEFB02C-4E13-4B44-94BC-0CCC56093F37}" name="CIDADE" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{9F96407A-940B-423E-9DF5-FB53E8D959FF}" name="LOJA" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{5015EE94-DAE4-4146-9FAD-52E70AC74336}" name="PROMOTOR(A)" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{5020E202-8D33-4205-AA6B-6F5C1729064E}" name="DATA" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{9E844A3F-01F3-4B57-A20A-B083E62DB332}" name="STATUS" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{106C1984-84DF-496B-AC73-8C510020C178}" name="OBSERVAÇÃO" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -998,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" style="4" customWidth="1"/>
@@ -1048,11 +1087,12 @@
         <v>8</v>
       </c>
       <c r="E2" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F2" s="14" t="s">
-        <v>97</v>
-      </c>
+        <v>46171</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="G2" s="5"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
@@ -1062,17 +1102,18 @@
         <v>7</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>98</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
@@ -1082,17 +1123,18 @@
         <v>7</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="7">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>98</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
@@ -1102,17 +1144,18 @@
         <v>4</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>5</v>
       </c>
       <c r="E5" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>99</v>
-      </c>
+        <v>46171</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G5" s="5"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
@@ -1122,37 +1165,39 @@
         <v>4</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>5</v>
       </c>
       <c r="E6" s="7">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>98</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="G6" s="5"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E7" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>98</v>
-      </c>
+        <v>46171</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="G7" s="5"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
@@ -1162,17 +1207,18 @@
         <v>18</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E8" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>100</v>
-      </c>
+        <v>46171</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8" s="5"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
@@ -1182,96 +1228,105 @@
         <v>18</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E9" s="7">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>98</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="G9" s="5"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E10" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>98</v>
-      </c>
+        <v>46171</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="G10" s="5"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>23</v>
       </c>
       <c r="E11" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F11" s="16" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+        <v>46171</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="G11" s="5"/>
+    </row>
+    <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>39</v>
+        <v>91</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E12" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F12" s="14" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+        <v>46171</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E13" s="7">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>98</v>
+        <v>53</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1282,43 +1337,41 @@
         <v>18</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>37</v>
+        <v>93</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E14" s="7">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E15" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>31</v>
-      </c>
+        <v>46171</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="G15" s="5"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
@@ -1328,77 +1381,81 @@
         <v>10</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>14</v>
+        <v>90</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E16" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F16" s="14" t="s">
-        <v>103</v>
-      </c>
+        <v>46171</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="G16" s="5"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E17" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F17" s="15" t="s">
-        <v>98</v>
-      </c>
+        <v>46171</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="G17" s="5"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18" s="4" t="s">
+      <c r="B18" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E18" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F18" s="14" t="s">
-        <v>104</v>
-      </c>
+        <v>46171</v>
+      </c>
+      <c r="F18" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="G18" s="17"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E19" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F19" s="15" t="s">
-        <v>98</v>
-      </c>
+        <v>46171</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="G19" s="5"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
@@ -1408,1134 +1465,1523 @@
         <v>25</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>26</v>
       </c>
       <c r="E20" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F20" s="14" t="s">
-        <v>105</v>
-      </c>
+        <v>46171</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="G20" s="5"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>26</v>
+      <c r="A21" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" t="s">
+        <v>47</v>
+      </c>
+      <c r="D21" t="s">
+        <v>8</v>
       </c>
       <c r="E21" s="7">
         <v>46170</v>
       </c>
-      <c r="F21" s="15" t="s">
-        <v>98</v>
+      <c r="F21" s="13" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
+      <c r="A22" t="s">
         <v>6</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D22" s="4" t="s">
+      <c r="C22" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22" t="s">
         <v>8</v>
       </c>
       <c r="E22" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>96</v>
-      </c>
+        <v>46170</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="G22" s="5"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
+      <c r="A23" t="s">
         <v>6</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" t="s">
         <v>7</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D23" s="4" t="s">
+      <c r="C23" t="s">
+        <v>46</v>
+      </c>
+      <c r="D23" t="s">
         <v>8</v>
       </c>
       <c r="E23" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F23" s="11" t="s">
-        <v>106</v>
+        <v>46170</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>8</v>
+      <c r="A24" t="s">
+        <v>3</v>
+      </c>
+      <c r="B24" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24" t="s">
+        <v>5</v>
       </c>
       <c r="E24" s="7">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
+      <c r="A25" t="s">
         <v>3</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" t="s">
         <v>29</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" t="s">
         <v>5</v>
       </c>
       <c r="E25" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F25" s="11" t="s">
-        <v>108</v>
+        <v>46170</v>
+      </c>
+      <c r="F25" s="15" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="4" t="s">
+      <c r="A26" t="s">
         <v>3</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" t="s">
         <v>4</v>
       </c>
-      <c r="C26" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D26" s="4" t="s">
+      <c r="C26" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" t="s">
         <v>5</v>
       </c>
       <c r="E26" s="7">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="4" t="s">
+      <c r="A27" t="s">
         <v>16</v>
       </c>
-      <c r="B27" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D27" s="4" t="s">
+      <c r="B27" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" t="s">
+        <v>35</v>
+      </c>
+      <c r="D27" t="s">
         <v>17</v>
       </c>
       <c r="E27" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F27" s="11" t="s">
-        <v>110</v>
+        <v>46170</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="4" t="s">
+      <c r="A28" t="s">
         <v>16</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" t="s">
         <v>18</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" t="s">
         <v>58</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" t="s">
         <v>17</v>
       </c>
       <c r="E28" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F28" s="8" t="s">
+        <v>46170</v>
+      </c>
+      <c r="F28" s="15" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="4" t="s">
+      <c r="A29" t="s">
+        <v>16</v>
+      </c>
+      <c r="B29" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" t="s">
+        <v>34</v>
+      </c>
+      <c r="D29" t="s">
+        <v>17</v>
+      </c>
+      <c r="E29" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>21</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B30" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" t="s">
+        <v>40</v>
+      </c>
+      <c r="D30" t="s">
+        <v>23</v>
+      </c>
+      <c r="E30" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F30" s="13" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>21</v>
+      </c>
+      <c r="B31" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" t="s">
+        <v>41</v>
+      </c>
+      <c r="D31" t="s">
+        <v>23</v>
+      </c>
+      <c r="E31" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>21</v>
+      </c>
+      <c r="B32" t="s">
         <v>22</v>
       </c>
-      <c r="C29" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D29" s="4" t="s">
+      <c r="C32" t="s">
+        <v>38</v>
+      </c>
+      <c r="D32" t="s">
         <v>23</v>
       </c>
-      <c r="E29" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F29" s="11" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E30" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F30" s="11" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="4" t="s">
+      <c r="E32" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F32" s="13" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>19</v>
       </c>
-      <c r="B31" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D31" s="4" t="s">
+      <c r="B33" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" t="s">
+        <v>37</v>
+      </c>
+      <c r="D33" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F31" s="8" t="s">
+      <c r="E33" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F33" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="G31" s="4" t="s">
+      <c r="G33" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>19</v>
+      </c>
+      <c r="B34" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" t="s">
+        <v>32</v>
+      </c>
+      <c r="D34" t="s">
+        <v>20</v>
+      </c>
+      <c r="E34" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F34" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>11</v>
+      </c>
+      <c r="B35" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" t="s">
+        <v>14</v>
+      </c>
+      <c r="D35" t="s">
+        <v>15</v>
+      </c>
+      <c r="E35" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F35" s="13" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" t="s">
+        <v>33</v>
+      </c>
+      <c r="D36" t="s">
+        <v>15</v>
+      </c>
+      <c r="E36" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F36" s="13" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" t="s">
+        <v>9</v>
+      </c>
+      <c r="C37" t="s">
+        <v>30</v>
+      </c>
+      <c r="D37" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>12</v>
+      </c>
+      <c r="B38" t="s">
+        <v>9</v>
+      </c>
+      <c r="C38" t="s">
+        <v>45</v>
+      </c>
+      <c r="D38" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="G38" s="5"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>24</v>
+      </c>
+      <c r="B39" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" t="s">
+        <v>42</v>
+      </c>
+      <c r="D39" t="s">
+        <v>26</v>
+      </c>
+      <c r="E39" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F39" s="13" t="s">
         <v>113</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E32" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E34" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F34" s="11" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E35" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F35" s="11" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E36" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F36" s="11" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E37" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F37" s="12" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E38" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F38" s="11" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E39" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F39" s="11" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>24</v>
+      </c>
+      <c r="B40" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" t="s">
+        <v>27</v>
+      </c>
+      <c r="D40" t="s">
+        <v>26</v>
+      </c>
+      <c r="E40" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F40" s="13" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B41" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C41" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D41" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E40" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F40" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="G40" s="5"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+      <c r="E41" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B42" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C41" t="s">
-        <v>48</v>
-      </c>
-      <c r="D41" t="s">
+      <c r="C42" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D42" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E41" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F41" s="13" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+      <c r="E42" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F42" s="11" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B43" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C42" t="s">
-        <v>46</v>
-      </c>
-      <c r="D42" t="s">
+      <c r="C43" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E42" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F42" s="12" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+      <c r="E43" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F43" s="11" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B44" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C44" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D44" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E43" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F43" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="G43" s="5"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+      <c r="E44" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F44" s="11" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B45" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C45" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D45" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E44" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F44" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="G44" s="6"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>3</v>
-      </c>
-      <c r="B45" t="s">
-        <v>4</v>
-      </c>
-      <c r="C45" t="s">
-        <v>44</v>
-      </c>
-      <c r="D45" t="s">
-        <v>5</v>
-      </c>
       <c r="E45" s="7">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+      <c r="A46" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E46" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F46" s="11" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B47" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C46" t="s">
-        <v>36</v>
-      </c>
-      <c r="D46" t="s">
+      <c r="C47" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D47" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E46" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F46" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="G46" s="6"/>
-    </row>
-    <row r="47" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>16</v>
-      </c>
-      <c r="B47" t="s">
-        <v>18</v>
-      </c>
-      <c r="C47" t="s">
-        <v>34</v>
-      </c>
-      <c r="D47" t="s">
-        <v>17</v>
-      </c>
       <c r="E47" s="7">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="G47" s="5" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>16</v>
-      </c>
-      <c r="B48" t="s">
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E48" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F48" s="11" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E49" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F49" s="11" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E50" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B51" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C48" t="s">
-        <v>35</v>
-      </c>
-      <c r="D48" t="s">
-        <v>17</v>
-      </c>
-      <c r="E48" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F48" s="8" t="s">
+      <c r="C51" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E51" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F51" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="G48" s="5" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>21</v>
-      </c>
-      <c r="B49" t="s">
-        <v>39</v>
-      </c>
-      <c r="C49" t="s">
-        <v>40</v>
-      </c>
-      <c r="D49" t="s">
-        <v>23</v>
-      </c>
-      <c r="E49" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F49" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="G49" s="5"/>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>21</v>
-      </c>
-      <c r="B50" t="s">
-        <v>39</v>
-      </c>
-      <c r="C50" t="s">
-        <v>41</v>
-      </c>
-      <c r="D50" t="s">
-        <v>23</v>
-      </c>
-      <c r="E50" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F50" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="G50" s="6"/>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>21</v>
-      </c>
-      <c r="B51" t="s">
-        <v>22</v>
-      </c>
-      <c r="C51" t="s">
-        <v>38</v>
-      </c>
-      <c r="D51" t="s">
-        <v>23</v>
-      </c>
-      <c r="E51" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F51" s="13" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+      <c r="G51" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C52" t="s">
-        <v>37</v>
-      </c>
-      <c r="D52" t="s">
+      <c r="C52" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D52" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E52" s="7">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="G52" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>19</v>
-      </c>
-      <c r="B53" t="s">
-        <v>18</v>
-      </c>
-      <c r="C53" t="s">
-        <v>32</v>
-      </c>
-      <c r="D53" t="s">
-        <v>20</v>
+      <c r="G52" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="E53" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F53" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G53" s="5" t="s">
-        <v>31</v>
+        <v>46169</v>
+      </c>
+      <c r="F53" s="11" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
+      <c r="A54" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C54" t="s">
-        <v>14</v>
-      </c>
-      <c r="D54" t="s">
+      <c r="C54" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D54" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E54" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F54" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="G54" s="5"/>
+        <v>46169</v>
+      </c>
+      <c r="F54" s="11" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>11</v>
-      </c>
-      <c r="B55" t="s">
-        <v>10</v>
-      </c>
-      <c r="C55" t="s">
-        <v>33</v>
-      </c>
-      <c r="D55" t="s">
-        <v>15</v>
+      <c r="A55" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="E55" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F55" s="13" t="s">
-        <v>75</v>
+        <v>46169</v>
+      </c>
+      <c r="F55" s="11" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
+      <c r="A56" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C56" t="s">
-        <v>30</v>
-      </c>
-      <c r="D56" t="s">
+      <c r="C56" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D56" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E56" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F56" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="G56" s="5"/>
+        <v>46169</v>
+      </c>
+      <c r="F56" s="12" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>12</v>
-      </c>
-      <c r="B57" t="s">
-        <v>9</v>
-      </c>
-      <c r="C57" t="s">
-        <v>45</v>
-      </c>
-      <c r="D57" t="s">
-        <v>13</v>
+      <c r="A57" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="E57" s="7">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
+      <c r="A58" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C58" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D58" s="4" t="s">
         <v>26</v>
       </c>
       <c r="E58" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F58" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="G58" s="6"/>
+        <v>46169</v>
+      </c>
+      <c r="F58" s="11" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="B59" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="C59" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D59" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="E59" s="7">
         <v>46168</v>
       </c>
       <c r="F59" s="13" t="s">
-        <v>81</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="G59" s="5"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60" s="4" t="s">
+      <c r="A60" t="s">
         <v>6</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="B60" t="s">
         <v>7</v>
       </c>
-      <c r="C60" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D60" s="4" t="s">
+      <c r="C60" t="s">
+        <v>48</v>
+      </c>
+      <c r="D60" t="s">
         <v>8</v>
       </c>
       <c r="E60" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F60" s="9" t="s">
-        <v>72</v>
+        <v>46168</v>
+      </c>
+      <c r="F60" s="13" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61" s="4" t="s">
+      <c r="A61" t="s">
         <v>6</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="B61" t="s">
         <v>7</v>
       </c>
-      <c r="C61" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D61" s="4" t="s">
+      <c r="C61" t="s">
+        <v>46</v>
+      </c>
+      <c r="D61" t="s">
         <v>8</v>
       </c>
       <c r="E61" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F61" s="9" t="s">
-        <v>74</v>
+        <v>46168</v>
+      </c>
+      <c r="F61" s="12" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62" s="4" t="s">
+      <c r="A62" t="s">
         <v>3</v>
       </c>
-      <c r="B62" s="4" t="s">
+      <c r="B62" t="s">
         <v>4</v>
       </c>
-      <c r="C62" s="4" t="s">
+      <c r="C62" t="s">
+        <v>29</v>
+      </c>
+      <c r="D62" t="s">
+        <v>5</v>
+      </c>
+      <c r="E62" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F62" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="G62" s="5"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>3</v>
+      </c>
+      <c r="B63" t="s">
+        <v>4</v>
+      </c>
+      <c r="C63" t="s">
         <v>28</v>
       </c>
-      <c r="D62" s="4" t="s">
+      <c r="D63" t="s">
         <v>5</v>
       </c>
-      <c r="E62" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F62" s="10" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63" s="4" t="s">
+      <c r="E63" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F63" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="G63" s="6"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
         <v>3</v>
       </c>
-      <c r="B63" s="4" t="s">
+      <c r="B64" t="s">
         <v>4</v>
       </c>
-      <c r="C63" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D63" s="4" t="s">
+      <c r="C64" t="s">
+        <v>44</v>
+      </c>
+      <c r="D64" t="s">
         <v>5</v>
       </c>
-      <c r="E63" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F63" s="10" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A64" s="4" t="s">
+      <c r="E64" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F64" s="11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
         <v>16</v>
       </c>
-      <c r="B64" s="4" t="s">
+      <c r="B65" t="s">
         <v>18</v>
       </c>
-      <c r="C64" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D64" s="17" t="s">
+      <c r="C65" t="s">
+        <v>36</v>
+      </c>
+      <c r="D65" t="s">
         <v>17</v>
       </c>
-      <c r="E64" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F64" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G64" s="5" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65" s="4" t="s">
+      <c r="E65" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F65" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="G65" s="6"/>
+    </row>
+    <row r="66" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
         <v>16</v>
       </c>
-      <c r="B65" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D65" s="4" t="s">
+      <c r="B66" t="s">
+        <v>18</v>
+      </c>
+      <c r="C66" t="s">
+        <v>34</v>
+      </c>
+      <c r="D66" t="s">
         <v>17</v>
       </c>
-      <c r="E65" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F65" s="9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A66" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B66" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C66" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D66" s="4" t="s">
-        <v>17</v>
-      </c>
       <c r="E66" s="7">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="F66" s="8" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A67" s="4" t="s">
+      <c r="G66" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>16</v>
+      </c>
+      <c r="B67" t="s">
+        <v>18</v>
+      </c>
+      <c r="C67" t="s">
+        <v>35</v>
+      </c>
+      <c r="D67" t="s">
+        <v>17</v>
+      </c>
+      <c r="E67" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G67" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
         <v>21</v>
       </c>
-      <c r="B67" s="4" t="s">
+      <c r="B68" t="s">
+        <v>39</v>
+      </c>
+      <c r="C68" t="s">
+        <v>40</v>
+      </c>
+      <c r="D68" t="s">
+        <v>23</v>
+      </c>
+      <c r="E68" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F68" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="G68" s="5"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>21</v>
+      </c>
+      <c r="B69" t="s">
+        <v>39</v>
+      </c>
+      <c r="C69" t="s">
+        <v>41</v>
+      </c>
+      <c r="D69" t="s">
+        <v>23</v>
+      </c>
+      <c r="E69" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F69" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="G69" s="6"/>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>21</v>
+      </c>
+      <c r="B70" t="s">
         <v>22</v>
       </c>
-      <c r="C67" s="4" t="s">
+      <c r="C70" t="s">
+        <v>38</v>
+      </c>
+      <c r="D70" t="s">
+        <v>23</v>
+      </c>
+      <c r="E70" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F70" s="13" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>19</v>
+      </c>
+      <c r="B71" t="s">
+        <v>18</v>
+      </c>
+      <c r="C71" t="s">
+        <v>37</v>
+      </c>
+      <c r="D71" t="s">
+        <v>20</v>
+      </c>
+      <c r="E71" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G71" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>19</v>
+      </c>
+      <c r="B72" t="s">
+        <v>18</v>
+      </c>
+      <c r="C72" t="s">
+        <v>32</v>
+      </c>
+      <c r="D72" t="s">
+        <v>20</v>
+      </c>
+      <c r="E72" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F72" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G72" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>11</v>
+      </c>
+      <c r="B73" t="s">
+        <v>10</v>
+      </c>
+      <c r="C73" t="s">
+        <v>14</v>
+      </c>
+      <c r="D73" t="s">
+        <v>15</v>
+      </c>
+      <c r="E73" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F73" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="G73" s="5"/>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>11</v>
+      </c>
+      <c r="B74" t="s">
+        <v>10</v>
+      </c>
+      <c r="C74" t="s">
+        <v>33</v>
+      </c>
+      <c r="D74" t="s">
+        <v>15</v>
+      </c>
+      <c r="E74" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F74" s="18" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>12</v>
+      </c>
+      <c r="B75" t="s">
+        <v>9</v>
+      </c>
+      <c r="C75" t="s">
+        <v>30</v>
+      </c>
+      <c r="D75" t="s">
+        <v>13</v>
+      </c>
+      <c r="E75" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F75" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="G75" s="5"/>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>12</v>
+      </c>
+      <c r="B76" t="s">
+        <v>9</v>
+      </c>
+      <c r="C76" t="s">
+        <v>45</v>
+      </c>
+      <c r="D76" t="s">
+        <v>13</v>
+      </c>
+      <c r="E76" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F76" s="11" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>24</v>
+      </c>
+      <c r="B77" t="s">
+        <v>25</v>
+      </c>
+      <c r="C77" t="s">
+        <v>27</v>
+      </c>
+      <c r="D77" t="s">
+        <v>26</v>
+      </c>
+      <c r="E77" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F77" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="G77" s="6"/>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>24</v>
+      </c>
+      <c r="B78" t="s">
+        <v>25</v>
+      </c>
+      <c r="C78" t="s">
+        <v>42</v>
+      </c>
+      <c r="D78" t="s">
+        <v>26</v>
+      </c>
+      <c r="E78" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F78" s="13" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A79" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E79" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F79" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A80" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E80" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F80" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A81" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E81" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F81" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A82" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E82" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F82" s="10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A83" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D83" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E83" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F83" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G83" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A84" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E84" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F84" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A85" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E85" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F85" s="8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A86" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C86" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D67" s="4" t="s">
+      <c r="D86" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E67" s="7">
+      <c r="E86" s="7">
         <v>46167</v>
       </c>
-      <c r="F67" s="9" t="s">
+      <c r="F86" s="9" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A68" s="4" t="s">
+    <row r="87" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A87" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B68" s="4" t="s">
+      <c r="B87" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C68" s="4" t="s">
+      <c r="C87" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D68" s="4" t="s">
+      <c r="D87" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E68" s="7">
+      <c r="E87" s="7">
         <v>46167</v>
       </c>
-      <c r="F68" s="8" t="s">
+      <c r="F87" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="G68" s="5" t="s">
+      <c r="G87" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A69" s="4" t="s">
+    <row r="88" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A88" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B69" s="4" t="s">
+      <c r="B88" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C69" s="4" t="s">
+      <c r="C88" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D69" s="4" t="s">
+      <c r="D88" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E69" s="7">
+      <c r="E88" s="7">
         <v>46167</v>
       </c>
-      <c r="F69" s="8" t="s">
+      <c r="F88" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="G69" s="5" t="s">
+      <c r="G88" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A70" s="4" t="s">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A89" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B70" s="4" t="s">
+      <c r="B89" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C70" s="4" t="s">
+      <c r="C89" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D70" s="4" t="s">
+      <c r="D89" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E70" s="7">
+      <c r="E89" s="7">
         <v>46167</v>
       </c>
-      <c r="F70" s="9" t="s">
+      <c r="F89" s="9" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A71" s="4" t="s">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A90" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B71" s="4" t="s">
+      <c r="B90" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C71" s="4" t="s">
+      <c r="C90" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D71" s="4" t="s">
+      <c r="D90" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E71" s="7">
+      <c r="E90" s="7">
         <v>46167</v>
       </c>
-      <c r="F71" s="10" t="s">
+      <c r="F90" s="10" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A72" s="4" t="s">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A91" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B72" s="4" t="s">
+      <c r="B91" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C72" s="4" t="s">
+      <c r="C91" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D72" s="4" t="s">
+      <c r="D91" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E72" s="7">
+      <c r="E91" s="7">
         <v>46167</v>
       </c>
-      <c r="F72" s="10" t="s">
+      <c r="F91" s="10" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A73" s="4" t="s">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A92" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B73" s="4" t="s">
+      <c r="B92" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C73" s="4" t="s">
+      <c r="C92" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="D73" s="4" t="s">
+      <c r="D92" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E73" s="7">
+      <c r="E92" s="7">
         <v>46167</v>
       </c>
-      <c r="F73" s="9" t="s">
+      <c r="F92" s="9" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A74" s="4" t="s">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A93" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B74" s="4" t="s">
+      <c r="B93" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C74" s="4" t="s">
+      <c r="C93" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D74" s="4" t="s">
+      <c r="D93" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E74" s="7">
+      <c r="E93" s="7">
         <v>46167</v>
       </c>
-      <c r="F74" s="18" t="s">
+      <c r="F93" s="9" t="s">
         <v>64</v>
       </c>
     </row>
@@ -2548,14 +2994,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6b3feda4-8a83-4113-98ac-b9b0c9bd9eab">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="6ca87d14-fc9d-4fcf-a42b-2754e6b3d00d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2766,21 +3210,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6b3feda4-8a83-4113-98ac-b9b0c9bd9eab">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="6ca87d14-fc9d-4fcf-a42b-2754e6b3d00d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFC5C71E-79D6-437C-A06A-B0BD52E89317}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6F72255-F15E-4B46-A16C-2F18C675CB37}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6b3feda4-8a83-4113-98ac-b9b0c9bd9eab"/>
-    <ds:schemaRef ds:uri="6ca87d14-fc9d-4fcf-a42b-2754e6b3d00d"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2805,9 +3248,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6F72255-F15E-4B46-A16C-2F18C675CB37}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFC5C71E-79D6-437C-A06A-B0BD52E89317}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6b3feda4-8a83-4113-98ac-b9b0c9bd9eab"/>
+    <ds:schemaRef ds:uri="6ca87d14-fc9d-4fcf-a42b-2754e6b3d00d"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/EFETIVIDADE.xlsx
+++ b/EFETIVIDADE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://spotpromo.sharepoint.com/sites/bko.pribeiro/Documentos Compartilhados/PRibeiro/BAUDUCCO TMP/20 - EFETIVIDADE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="892" documentId="13_ncr:1_{C64068DB-D04A-49E7-B037-1281E1EE8D6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33FA28B4-5224-491A-9450-7C6E7164F27D}"/>
+  <xr:revisionPtr revIDLastSave="931" documentId="13_ncr:1_{C64068DB-D04A-49E7-B037-1281E1EE8D6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2B81C12-E79C-4CEC-8A29-F11E447A3C47}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="222">
   <si>
     <t>ROTA</t>
   </si>
@@ -524,24 +524,6 @@
     <t>SUPERNOSSO - AVENIDA AFONSO PENA 3328, 3328 - BELO HORIZONTE/MG</t>
   </si>
   <si>
-    <t>07:30</t>
-  </si>
-  <si>
-    <t>07:10</t>
-  </si>
-  <si>
-    <t>08:09</t>
-  </si>
-  <si>
-    <t>07:45</t>
-  </si>
-  <si>
-    <t>07:04</t>
-  </si>
-  <si>
-    <t>06:59</t>
-  </si>
-  <si>
     <t>07:02</t>
   </si>
   <si>
@@ -549,6 +531,174 @@
   </si>
   <si>
     <t>ESTÁ EM CAMPO, APRESENTOU PROBLEMA NO APARELHO.</t>
+  </si>
+  <si>
+    <t>APRESENTOU PROBLEMA DE SAÚDE</t>
+  </si>
+  <si>
+    <t>06:59  10:58</t>
+  </si>
+  <si>
+    <t>07:02  10:14</t>
+  </si>
+  <si>
+    <t>07:04  16:11</t>
+  </si>
+  <si>
+    <t>07:10  17:56</t>
+  </si>
+  <si>
+    <t>07:30  12:15</t>
+  </si>
+  <si>
+    <t>07:30  16:52</t>
+  </si>
+  <si>
+    <t>07:45  12:38</t>
+  </si>
+  <si>
+    <t>08:00  17:11</t>
+  </si>
+  <si>
+    <t>08:09  14:40</t>
+  </si>
+  <si>
+    <t>10:22  12:49</t>
+  </si>
+  <si>
+    <t>11:36  16:03</t>
+  </si>
+  <si>
+    <t>13:33  16:05</t>
+  </si>
+  <si>
+    <t>13:51  16:39</t>
+  </si>
+  <si>
+    <t>18:09</t>
+  </si>
+  <si>
+    <t>18:56</t>
+  </si>
+  <si>
+    <t>BH - RUA MINAS GERAIS, 200 - RIBEIRAO DAS NEVES/MG</t>
+  </si>
+  <si>
+    <t>EPA - RUA TENENTE GARRO 120, 120 - BELO HORIZONTE/MG</t>
+  </si>
+  <si>
+    <t>EPA - RUA CARACA 600, 600 - BELO HORIZONTE/MG</t>
+  </si>
+  <si>
+    <t>EPA - AV DO CONTORNO 4255, 4255 - BELO HORIZONTE/MG</t>
+  </si>
+  <si>
+    <t>VILLEFORT - RODOVIA BR-040 3750, 3750 - CONTAGEM/MG</t>
+  </si>
+  <si>
+    <t>EPA - RUA IPANEMA, 10 - RIBEIRAO DAS NEVES/MG</t>
+  </si>
+  <si>
+    <t>VILLEFORT - RUA FRANCISCO LABANCA, 600 - RIBEIRAO DAS NEVES/MG</t>
+  </si>
+  <si>
+    <t>VILLEFORT - AV PROFESSOR CLOVIS SALGADO 3003, 3003 - BELO HORIZONTE/MG</t>
+  </si>
+  <si>
+    <t>06:58  08:25</t>
+  </si>
+  <si>
+    <t>07:00  09:24</t>
+  </si>
+  <si>
+    <t>07:00  12:54</t>
+  </si>
+  <si>
+    <t>07:16  10:44</t>
+  </si>
+  <si>
+    <t>07:18  09:28</t>
+  </si>
+  <si>
+    <t>07:18  10:25</t>
+  </si>
+  <si>
+    <t>07:29  17:32</t>
+  </si>
+  <si>
+    <t>07:58  13:52</t>
+  </si>
+  <si>
+    <t>08:01  15:04</t>
+  </si>
+  <si>
+    <t>08:05  09:36</t>
+  </si>
+  <si>
+    <t>08:32  11:30</t>
+  </si>
+  <si>
+    <t>09:43  10:54</t>
+  </si>
+  <si>
+    <t>09:57  16:54</t>
+  </si>
+  <si>
+    <t>10:39  14:31</t>
+  </si>
+  <si>
+    <t>10:56  12:32</t>
+  </si>
+  <si>
+    <t>11:06  13:25</t>
+  </si>
+  <si>
+    <t>12:11  12:17</t>
+  </si>
+  <si>
+    <t>12:30  16:00</t>
+  </si>
+  <si>
+    <t>13:32  16:17</t>
+  </si>
+  <si>
+    <t>14:01  16:27</t>
+  </si>
+  <si>
+    <t>14:07  16:04</t>
+  </si>
+  <si>
+    <t>14:33  16:42</t>
+  </si>
+  <si>
+    <t>14:49  19:41</t>
+  </si>
+  <si>
+    <t>15:28  17:30</t>
+  </si>
+  <si>
+    <t>BH - AV SEVERINO BALLESTEROS RODRIGUE 65, 65 - CONTAGEM/MG</t>
+  </si>
+  <si>
+    <t>06:58</t>
+  </si>
+  <si>
+    <t>07:00</t>
+  </si>
+  <si>
+    <t>07:06</t>
+  </si>
+  <si>
+    <t>07:18</t>
+  </si>
+  <si>
+    <t>07:29</t>
+  </si>
+  <si>
+    <t>07:52</t>
+  </si>
+  <si>
+    <t>08:08</t>
   </si>
 </sst>
 </file>
@@ -661,7 +811,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -699,15 +849,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -720,34 +861,27 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{CCF9025B-0226-4389-80E6-00916CE7E00D}"/>
   </cellStyles>
   <dxfs count="9">
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -806,6 +940,28 @@
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <extLst>
@@ -820,25 +976,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A4474625-D582-4F1B-AA27-C9E6E4248EEA}" name="Tabela1" displayName="Tabela1" ref="A1:G122" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0" headerRowCellStyle="Normal 2">
-  <autoFilter ref="A1:G122" xr:uid="{A4474625-D582-4F1B-AA27-C9E6E4248EEA}">
-    <filterColumn colId="4">
-      <filters>
-        <dateGroupItem year="2026" month="6" dateTimeGrouping="month"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G101">
-    <sortCondition descending="1" ref="E1:E101"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A4474625-D582-4F1B-AA27-C9E6E4248EEA}" name="Tabela1" displayName="Tabela1" ref="A1:G176" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7" headerRowCellStyle="Normal 2">
+  <autoFilter ref="A1:G176" xr:uid="{A4474625-D582-4F1B-AA27-C9E6E4248EEA}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G176">
+    <sortCondition descending="1" ref="E1:E176"/>
   </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{8C18829A-5E6C-4A32-820C-446F688CFF40}" name="ROTA" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{DDEFB02C-4E13-4B44-94BC-0CCC56093F37}" name="CIDADE" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{9F96407A-940B-423E-9DF5-FB53E8D959FF}" name="LOJA" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{5015EE94-DAE4-4146-9FAD-52E70AC74336}" name="PROMOTOR(A)" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{5020E202-8D33-4205-AA6B-6F5C1729064E}" name="DATA" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{9E844A3F-01F3-4B57-A20A-B083E62DB332}" name="STATUS" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{106C1984-84DF-496B-AC73-8C510020C178}" name="OBSERVAÇÃO" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{8C18829A-5E6C-4A32-820C-446F688CFF40}" name="ROTA" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{DDEFB02C-4E13-4B44-94BC-0CCC56093F37}" name="CIDADE" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{9F96407A-940B-423E-9DF5-FB53E8D959FF}" name="LOJA" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{5015EE94-DAE4-4146-9FAD-52E70AC74336}" name="PROMOTOR(A)" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{5020E202-8D33-4205-AA6B-6F5C1729064E}" name="DATA" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{9E844A3F-01F3-4B57-A20A-B083E62DB332}" name="STATUS" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{106C1984-84DF-496B-AC73-8C510020C178}" name="OBSERVAÇÃO" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1161,7 +1311,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G122"/>
+  <dimension ref="A1:G176"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" style="4" customWidth="1"/>
@@ -1197,7 +1347,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
@@ -1205,381 +1355,385 @@
         <v>7</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="7">
-        <v>46172</v>
-      </c>
-      <c r="F2" s="16" t="s">
-        <v>148</v>
+        <v>46176</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>220</v>
       </c>
       <c r="G2" s="5"/>
     </row>
-    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E3" s="7">
-        <v>46172</v>
+        <v>46176</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>53</v>
       </c>
       <c r="G3" s="5"/>
     </row>
-    <row r="4" spans="1:7" ht="28.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E4" s="7">
-        <v>46172</v>
-      </c>
-      <c r="F4" s="16" t="s">
-        <v>146</v>
+        <v>46176</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G4" s="5"/>
     </row>
-    <row r="5" spans="1:7" ht="33.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>21</v>
+        <v>153</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>22</v>
+        <v>154</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>38</v>
+        <v>155</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>23</v>
+        <v>156</v>
       </c>
       <c r="E5" s="7">
-        <v>46172</v>
-      </c>
-      <c r="F5" s="16" t="s">
-        <v>144</v>
+        <v>46176</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>217</v>
       </c>
       <c r="G5" s="5"/>
     </row>
-    <row r="6" spans="1:7" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>20</v>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>156</v>
       </c>
       <c r="E6" s="7">
-        <v>46172</v>
+        <v>46176</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="G6" s="5"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>11</v>
+        <v>149</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>33</v>
+        <v>150</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>15</v>
+        <v>151</v>
       </c>
       <c r="E7" s="7">
-        <v>46172</v>
-      </c>
-      <c r="F7" s="16" t="s">
-        <v>145</v>
+        <v>46176</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>219</v>
       </c>
       <c r="G7" s="5"/>
     </row>
-    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>12</v>
+        <v>149</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>95</v>
+        <v>189</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>13</v>
+        <v>151</v>
       </c>
       <c r="E8" s="7">
-        <v>46172</v>
-      </c>
-      <c r="F8" s="17" t="s">
-        <v>147</v>
+        <v>46176</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G8" s="5"/>
     </row>
-    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>42</v>
+        <v>214</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>26</v>
+        <v>151</v>
       </c>
       <c r="E9" s="7">
-        <v>46172</v>
-      </c>
-      <c r="F9" s="16" t="s">
-        <v>143</v>
+        <v>46176</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G9" s="5"/>
     </row>
-    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E10" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F10" s="16" t="s">
-        <v>128</v>
+        <v>46176</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>163</v>
       </c>
       <c r="G10" s="5"/>
     </row>
-    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>73</v>
+        <v>28</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E11" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F11" s="16" t="s">
-        <v>135</v>
+        <v>46176</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G11" s="5"/>
     </row>
-    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E12" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F12" s="16" t="s">
-        <v>140</v>
+        <v>46176</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>221</v>
       </c>
       <c r="G12" s="5"/>
     </row>
-    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E13" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F13" s="17" t="s">
-        <v>129</v>
+        <v>46176</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G13" s="5"/>
     </row>
-    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="E14" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F14" s="17" t="s">
-        <v>136</v>
+        <v>46176</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>215</v>
       </c>
       <c r="G14" s="5"/>
     </row>
-    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="7">
+        <v>46176</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G15" s="5"/>
+    </row>
+    <row r="16" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E15" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F15" s="17" t="s">
-        <v>134</v>
-      </c>
-      <c r="G15" s="5"/>
-    </row>
-    <row r="16" spans="1:7" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="4" t="s">
+      <c r="C16" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E16" s="7">
+        <v>46176</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E17" s="7">
+        <v>46176</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E18" s="7">
+        <v>46176</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E16" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F16" s="18" t="s">
+      <c r="C19" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="7">
+        <v>46176</v>
+      </c>
+      <c r="F19" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="G19" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E17" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F17" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="G17" s="5"/>
-    </row>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F18" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="G18" s="5"/>
-    </row>
-    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E19" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F19" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="G19" s="5"/>
-    </row>
-    <row r="20" spans="1:7" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>19</v>
       </c>
@@ -1593,16 +1747,16 @@
         <v>20</v>
       </c>
       <c r="E20" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F20" s="18" t="s">
+        <v>46176</v>
+      </c>
+      <c r="F20" s="8" t="s">
         <v>53</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>19</v>
       </c>
@@ -1610,45 +1764,41 @@
         <v>18</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E21" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F21" s="18" t="s">
+        <v>46176</v>
+      </c>
+      <c r="F21" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="G21" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="G21" s="5"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>93</v>
+        <v>14</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E22" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F22" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+        <v>46176</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="G22" s="5"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>11</v>
       </c>
@@ -1656,83 +1806,83 @@
         <v>10</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>14</v>
+        <v>90</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E23" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F23" s="16" t="s">
-        <v>132</v>
+        <v>46176</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G23" s="5"/>
     </row>
-    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E24" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F24" s="16" t="s">
-        <v>139</v>
+        <v>46176</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>164</v>
       </c>
       <c r="G24" s="5"/>
     </row>
-    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D25" s="4" t="s">
+      <c r="C25" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="D25" s="19" t="s">
         <v>13</v>
       </c>
       <c r="E25" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F25" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="G25" s="5"/>
-    </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+        <v>46176</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G25" s="20"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E26" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F26" s="17" t="s">
-        <v>141</v>
+        <v>46176</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>216</v>
       </c>
       <c r="G26" s="5"/>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>24</v>
       </c>
@@ -1740,41 +1890,41 @@
         <v>25</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>26</v>
       </c>
       <c r="E27" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F27" s="16" t="s">
-        <v>130</v>
+        <v>46176</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G27" s="5"/>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="E28" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F28" s="16" t="s">
-        <v>137</v>
+        <v>46175</v>
+      </c>
+      <c r="F28" s="17" t="s">
+        <v>199</v>
       </c>
       <c r="G28" s="5"/>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>6</v>
       </c>
@@ -1782,19 +1932,20 @@
         <v>7</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E29" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F29" s="16" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+        <v>46175</v>
+      </c>
+      <c r="F29" s="17" t="s">
+        <v>206</v>
+      </c>
+      <c r="G29" s="5"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>6</v>
       </c>
@@ -1802,1075 +1953,1103 @@
         <v>7</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E30" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F30" s="16" t="s">
-        <v>120</v>
+        <v>46175</v>
+      </c>
+      <c r="F30" s="17" t="s">
+        <v>210</v>
       </c>
       <c r="G30" s="5"/>
     </row>
-    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>6</v>
+        <v>153</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>7</v>
+        <v>154</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>46</v>
+        <v>182</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>8</v>
+        <v>156</v>
       </c>
       <c r="E31" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F31" s="19" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+        <v>46175</v>
+      </c>
+      <c r="F31" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="G31" s="5"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="E32" s="7">
+        <v>46175</v>
+      </c>
+      <c r="F32" s="17" t="s">
+        <v>204</v>
+      </c>
+      <c r="G32" s="5"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="E33" s="7">
+        <v>46175</v>
+      </c>
+      <c r="F33" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="G33" s="5"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="E34" s="7">
+        <v>46175</v>
+      </c>
+      <c r="F34" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="G34" s="5"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="E35" s="7">
+        <v>46175</v>
+      </c>
+      <c r="F35" s="17" t="s">
+        <v>203</v>
+      </c>
+      <c r="G35" s="5"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="E36" s="7">
+        <v>46175</v>
+      </c>
+      <c r="F36" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="G36" s="5"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B37" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C37" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E37" s="7">
+        <v>46175</v>
+      </c>
+      <c r="F37" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="G37" s="5"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D38" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E32" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F32" s="17" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="4" t="s">
+      <c r="E38" s="7">
+        <v>46175</v>
+      </c>
+      <c r="F38" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="G38" s="5"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B39" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C33" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D33" s="4" t="s">
+      <c r="C39" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D39" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E33" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F33" s="18" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E34" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F34" s="17" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="4" t="s">
+      <c r="E39" s="7">
+        <v>46175</v>
+      </c>
+      <c r="F39" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="G39" s="5"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B40" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C35" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D35" s="4" t="s">
+      <c r="C40" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D40" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E35" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F35" s="16" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="4" t="s">
+      <c r="E40" s="7">
+        <v>46175</v>
+      </c>
+      <c r="F40" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="G40" s="5"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E36" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F36" s="18" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E37" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F37" s="16" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E38" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F38" s="16" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E39" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F39" s="16" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E40" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F40" s="16" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="4" t="s">
-        <v>19</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C41" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E41" s="7">
+        <v>46175</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G41" s="5"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E42" s="7">
+        <v>46175</v>
+      </c>
+      <c r="F42" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="G42" s="5"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E43" s="7">
+        <v>46175</v>
+      </c>
+      <c r="F43" s="17" t="s">
+        <v>200</v>
+      </c>
+      <c r="G43" s="5"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E44" s="7">
+        <v>46175</v>
+      </c>
+      <c r="F44" s="17" t="s">
+        <v>207</v>
+      </c>
+      <c r="G44" s="5"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E45" s="7">
+        <v>46175</v>
+      </c>
+      <c r="F45" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="G45" s="5"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E46" s="7">
+        <v>46175</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G46" s="5"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E47" s="7">
+        <v>46175</v>
+      </c>
+      <c r="F47" s="17" t="s">
+        <v>202</v>
+      </c>
+      <c r="G47" s="5"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E48" s="7">
+        <v>46175</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G48" s="5"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="D49" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E41" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F41" s="18" t="s">
+      <c r="E49" s="7">
+        <v>46175</v>
+      </c>
+      <c r="F49" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="G41" s="5" t="s">
+      <c r="G49" s="5"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E50" s="7">
+        <v>46175</v>
+      </c>
+      <c r="F50" s="17" t="s">
+        <v>197</v>
+      </c>
+      <c r="G50" s="5"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E51" s="7">
+        <v>46175</v>
+      </c>
+      <c r="F51" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="G51" s="5"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E52" s="7">
+        <v>46175</v>
+      </c>
+      <c r="F52" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="G52" s="5"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B53" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="C53" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="D53" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E53" s="7">
+        <v>46175</v>
+      </c>
+      <c r="F53" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="G53" s="20"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A54" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E54" s="7">
+        <v>46175</v>
+      </c>
+      <c r="F54" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="G54" s="5"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A55" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E55" s="7">
+        <v>46175</v>
+      </c>
+      <c r="F55" s="17" t="s">
+        <v>211</v>
+      </c>
+      <c r="G55" s="5"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>6</v>
+      </c>
+      <c r="B56" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" t="s">
+        <v>73</v>
+      </c>
+      <c r="D56" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="7">
+        <v>46174</v>
+      </c>
+      <c r="F56" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="G56" s="5"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>6</v>
+      </c>
+      <c r="B57" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" t="s">
+        <v>71</v>
+      </c>
+      <c r="D57" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="7">
+        <v>46174</v>
+      </c>
+      <c r="F57" s="17" t="s">
+        <v>178</v>
+      </c>
+      <c r="G57" s="5"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>153</v>
+      </c>
+      <c r="B58" t="s">
+        <v>154</v>
+      </c>
+      <c r="C58" t="s">
+        <v>155</v>
+      </c>
+      <c r="D58" t="s">
+        <v>156</v>
+      </c>
+      <c r="E58" s="7">
+        <v>46174</v>
+      </c>
+      <c r="F58" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="G58" s="5"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>153</v>
+      </c>
+      <c r="B59" t="s">
+        <v>154</v>
+      </c>
+      <c r="C59" t="s">
+        <v>157</v>
+      </c>
+      <c r="D59" t="s">
+        <v>156</v>
+      </c>
+      <c r="E59" s="7">
+        <v>46174</v>
+      </c>
+      <c r="F59" s="17" t="s">
+        <v>179</v>
+      </c>
+      <c r="G59" s="5"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>149</v>
+      </c>
+      <c r="B60" t="s">
+        <v>10</v>
+      </c>
+      <c r="C60" t="s">
+        <v>150</v>
+      </c>
+      <c r="D60" t="s">
+        <v>151</v>
+      </c>
+      <c r="E60" s="7">
+        <v>46174</v>
+      </c>
+      <c r="F60" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="G60" s="5"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>149</v>
+      </c>
+      <c r="B61" t="s">
+        <v>10</v>
+      </c>
+      <c r="C61" t="s">
+        <v>152</v>
+      </c>
+      <c r="D61" t="s">
+        <v>151</v>
+      </c>
+      <c r="E61" s="7">
+        <v>46174</v>
+      </c>
+      <c r="F61" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="G61" s="5"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>3</v>
+      </c>
+      <c r="B62" t="s">
+        <v>4</v>
+      </c>
+      <c r="C62" t="s">
+        <v>29</v>
+      </c>
+      <c r="D62" t="s">
+        <v>5</v>
+      </c>
+      <c r="E62" s="7">
+        <v>46174</v>
+      </c>
+      <c r="F62" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="G62" s="5"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>3</v>
+      </c>
+      <c r="B63" t="s">
+        <v>4</v>
+      </c>
+      <c r="C63" t="s">
+        <v>28</v>
+      </c>
+      <c r="D63" t="s">
+        <v>5</v>
+      </c>
+      <c r="E63" s="7">
+        <v>46174</v>
+      </c>
+      <c r="F63" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="G63" s="5"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>16</v>
+      </c>
+      <c r="B64" t="s">
+        <v>55</v>
+      </c>
+      <c r="C64" t="s">
+        <v>56</v>
+      </c>
+      <c r="D64" t="s">
+        <v>17</v>
+      </c>
+      <c r="E64" s="7">
+        <v>46174</v>
+      </c>
+      <c r="F64" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="G64" s="5"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>16</v>
+      </c>
+      <c r="B65" t="s">
+        <v>18</v>
+      </c>
+      <c r="C65" t="s">
+        <v>58</v>
+      </c>
+      <c r="D65" t="s">
+        <v>17</v>
+      </c>
+      <c r="E65" s="7">
+        <v>46174</v>
+      </c>
+      <c r="F65" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G65" s="5"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>21</v>
+      </c>
+      <c r="B66" t="s">
+        <v>22</v>
+      </c>
+      <c r="C66" t="s">
+        <v>60</v>
+      </c>
+      <c r="D66" t="s">
+        <v>23</v>
+      </c>
+      <c r="E66" s="7">
+        <v>46174</v>
+      </c>
+      <c r="F66" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="G66" s="5"/>
+    </row>
+    <row r="67" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>158</v>
+      </c>
+      <c r="B67" t="s">
+        <v>55</v>
+      </c>
+      <c r="C67" t="s">
+        <v>159</v>
+      </c>
+      <c r="D67" t="s">
+        <v>160</v>
+      </c>
+      <c r="E67" s="7">
+        <v>46174</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G67" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>158</v>
+      </c>
+      <c r="B68" t="s">
+        <v>55</v>
+      </c>
+      <c r="C68" t="s">
+        <v>161</v>
+      </c>
+      <c r="D68" t="s">
+        <v>160</v>
+      </c>
+      <c r="E68" s="7">
+        <v>46174</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>158</v>
+      </c>
+      <c r="B69" t="s">
+        <v>55</v>
+      </c>
+      <c r="C69" t="s">
+        <v>162</v>
+      </c>
+      <c r="D69" t="s">
+        <v>160</v>
+      </c>
+      <c r="E69" s="7">
+        <v>46174</v>
+      </c>
+      <c r="F69" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="G69" s="5"/>
+    </row>
+    <row r="70" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>19</v>
+      </c>
+      <c r="B70" t="s">
+        <v>18</v>
+      </c>
+      <c r="C70" t="s">
+        <v>59</v>
+      </c>
+      <c r="D70" t="s">
+        <v>20</v>
+      </c>
+      <c r="E70" s="7">
+        <v>46174</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G70" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="4" t="s">
+    <row r="71" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
         <v>19</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B71" t="s">
         <v>18</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C71" t="s">
         <v>32</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D71" t="s">
         <v>20</v>
       </c>
-      <c r="E42" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F42" s="18" t="s">
+      <c r="E71" s="7">
+        <v>46174</v>
+      </c>
+      <c r="F71" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="G42" s="5" t="s">
+      <c r="G71" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="4" t="s">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
         <v>11</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B72" t="s">
         <v>10</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C72" t="s">
         <v>14</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D72" t="s">
         <v>15</v>
       </c>
-      <c r="E43" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F43" s="16" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E44" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F44" s="16" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="4" t="s">
+      <c r="E72" s="7">
+        <v>46174</v>
+      </c>
+      <c r="F72" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="G72" s="5"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
         <v>12</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B73" t="s">
         <v>9</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="C73" t="s">
         <v>30</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="D73" t="s">
         <v>13</v>
       </c>
-      <c r="E45" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F45" s="17" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="4" t="s">
+      <c r="E73" s="7">
+        <v>46174</v>
+      </c>
+      <c r="F73" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="G73" s="5"/>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
         <v>12</v>
       </c>
-      <c r="B46" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D46" s="4" t="s">
+      <c r="B74" t="s">
+        <v>67</v>
+      </c>
+      <c r="C74" t="s">
+        <v>68</v>
+      </c>
+      <c r="D74" t="s">
         <v>13</v>
       </c>
-      <c r="E46" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F46" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="G46" s="5"/>
-    </row>
-    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="4" t="s">
+      <c r="E74" s="7">
+        <v>46174</v>
+      </c>
+      <c r="F74" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="G74" s="5"/>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
         <v>24</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B75" t="s">
         <v>25</v>
       </c>
-      <c r="C47" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D47" s="4" t="s">
+      <c r="C75" t="s">
+        <v>62</v>
+      </c>
+      <c r="D75" t="s">
         <v>26</v>
       </c>
-      <c r="E47" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F47" s="16" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="4" t="s">
+      <c r="E75" s="7">
+        <v>46174</v>
+      </c>
+      <c r="F75" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="G75" s="5"/>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
         <v>24</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B76" t="s">
         <v>25</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C76" t="s">
         <v>27</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="D76" t="s">
         <v>26</v>
       </c>
-      <c r="E48" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F48" s="16" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="4" t="s">
+      <c r="E76" s="7">
+        <v>46174</v>
+      </c>
+      <c r="F76" s="17" t="s">
+        <v>177</v>
+      </c>
+      <c r="G76" s="5"/>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A77" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B49" s="4" t="s">
+      <c r="B77" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C49" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D49" s="4" t="s">
+      <c r="C77" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D77" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E49" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F49" s="17" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E50" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F50" s="17" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E51" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F51" s="17" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="4" t="s">
+      <c r="E77" s="7">
+        <v>46172</v>
+      </c>
+      <c r="F77" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="G77" s="5"/>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A78" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B78" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C52" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D52" s="4" t="s">
+      <c r="C78" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D78" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E52" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F52" s="17" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E53" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F53" s="17" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="4" t="s">
+      <c r="E78" s="7">
+        <v>46172</v>
+      </c>
+      <c r="F78" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G78" s="5" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A79" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E54" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F54" s="17" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E55" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F55" s="8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E56" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F56" s="17" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E57" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F57" s="17" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="C58" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D58" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E58" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F58" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G58" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D59" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E59" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F59" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G59" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E60" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F60" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G60" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E61" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F61" s="17" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E62" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F62" s="17" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B63" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C63" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E63" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F63" s="17" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B64" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C64" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E64" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F64" s="19" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B65" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E65" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F65" s="17" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B66" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C66" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D66" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E66" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F66" s="17" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B67" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E67" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F67" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="G67" s="5"/>
-    </row>
-    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B68" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E68" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F68" s="16" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B69" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C69" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D69" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E69" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F69" s="19" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B70" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D70" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E70" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F70" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="G70" s="5"/>
-    </row>
-    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B71" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D71" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E71" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F71" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="G71" s="6"/>
-    </row>
-    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B72" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C72" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D72" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E72" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F72" s="17" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B73" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C73" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D73" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E73" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F73" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="G73" s="6"/>
-    </row>
-    <row r="74" spans="1:7" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B74" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D74" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E74" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F74" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="G74" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B75" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C75" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D75" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E75" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F75" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G75" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B76" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C76" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D76" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E76" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F76" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="G76" s="5"/>
-    </row>
-    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B77" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E77" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F77" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="G77" s="6"/>
-    </row>
-    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B78" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C78" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D78" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E78" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F78" s="16" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="4" t="s">
-        <v>19</v>
       </c>
       <c r="B79" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D79" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E79" s="7">
+        <v>46172</v>
+      </c>
+      <c r="F79" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="G79" s="6"/>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A80" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E80" s="7">
+        <v>46172</v>
+      </c>
+      <c r="F80" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="G80" s="5"/>
+    </row>
+    <row r="81" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A81" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D81" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E79" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F79" s="8" t="s">
+      <c r="E81" s="7">
+        <v>46172</v>
+      </c>
+      <c r="F81" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="G79" s="5" t="s">
+      <c r="G81" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B80" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C80" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D80" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E80" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F80" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G80" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B81" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C81" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D81" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E81" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F81" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="G81" s="5"/>
-    </row>
-    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
         <v>11</v>
       </c>
@@ -2884,13 +3063,14 @@
         <v>15</v>
       </c>
       <c r="E82" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F82" s="16" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+        <v>46172</v>
+      </c>
+      <c r="F82" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="G82" s="5"/>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
         <v>12</v>
       </c>
@@ -2898,81 +3078,83 @@
         <v>9</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E83" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F83" s="17" t="s">
-        <v>86</v>
+        <v>46172</v>
+      </c>
+      <c r="F83" s="14" t="s">
+        <v>147</v>
       </c>
       <c r="G83" s="5"/>
     </row>
-    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E84" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F84" s="17" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+        <v>46172</v>
+      </c>
+      <c r="F84" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="G84" s="5"/>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="E85" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F85" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="G85" s="6"/>
-    </row>
-    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+        <v>46171</v>
+      </c>
+      <c r="F85" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="G85" s="5"/>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="E86" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F86" s="16" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+        <v>46171</v>
+      </c>
+      <c r="F86" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="G86" s="5"/>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
         <v>6</v>
       </c>
@@ -2986,33 +3168,35 @@
         <v>8</v>
       </c>
       <c r="E87" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F87" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+        <v>46171</v>
+      </c>
+      <c r="F87" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="G87" s="5"/>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E88" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F88" s="9" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+        <v>46171</v>
+      </c>
+      <c r="F88" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="G88" s="5"/>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
         <v>3</v>
       </c>
@@ -3026,33 +3210,35 @@
         <v>5</v>
       </c>
       <c r="E89" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F89" s="10" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+        <v>46171</v>
+      </c>
+      <c r="F89" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="G89" s="5"/>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E90" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F90" s="10" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+        <v>46171</v>
+      </c>
+      <c r="F90" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="G90" s="5"/>
+    </row>
+    <row r="91" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
         <v>16</v>
       </c>
@@ -3060,62 +3246,64 @@
         <v>18</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D91" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D91" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E91" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F91" s="8" t="s">
+        <v>46171</v>
+      </c>
+      <c r="F91" s="15" t="s">
         <v>53</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="D92" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E92" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F92" s="9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+        <v>46171</v>
+      </c>
+      <c r="F92" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="G92" s="5"/>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E93" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F93" s="8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+        <v>46171</v>
+      </c>
+      <c r="F93" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="G93" s="5"/>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
         <v>21</v>
       </c>
@@ -3123,42 +3311,43 @@
         <v>22</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="D94" s="4" t="s">
         <v>23</v>
       </c>
       <c r="E94" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F94" s="9" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+        <v>46171</v>
+      </c>
+      <c r="F94" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="G94" s="5"/>
+    </row>
+    <row r="95" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
         <v>19</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="D95" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E95" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F95" s="8" t="s">
+        <v>46171</v>
+      </c>
+      <c r="F95" s="15" t="s">
         <v>53</v>
       </c>
       <c r="G95" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
         <v>19</v>
       </c>
@@ -3166,508 +3355,496 @@
         <v>18</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D96" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E96" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F96" s="8" t="s">
+        <v>46171</v>
+      </c>
+      <c r="F96" s="15" t="s">
         <v>53</v>
       </c>
       <c r="G96" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E97" s="7">
+        <v>46171</v>
+      </c>
+      <c r="F97" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="G97" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A98" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B97" s="4" t="s">
+      <c r="B98" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C97" s="4" t="s">
+      <c r="C98" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D97" s="4" t="s">
+      <c r="D98" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E97" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F97" s="9" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="4" t="s">
+      <c r="E98" s="7">
+        <v>46171</v>
+      </c>
+      <c r="F98" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="G98" s="5"/>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A99" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E99" s="7">
+        <v>46171</v>
+      </c>
+      <c r="F99" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="G99" s="5"/>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A100" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B98" s="4" t="s">
+      <c r="B100" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E100" s="7">
+        <v>46171</v>
+      </c>
+      <c r="F100" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="G100" s="5"/>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A101" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B101" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C98" s="4" t="s">
+      <c r="C101" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D98" s="4" t="s">
+      <c r="D101" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E98" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F98" s="10" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B99" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C99" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D99" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E99" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F99" s="10" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B100" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C100" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D100" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E100" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F100" s="9" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B101" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C101" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D101" s="4" t="s">
-        <v>26</v>
-      </c>
       <c r="E101" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F101" s="9" t="s">
-        <v>64</v>
-      </c>
+        <v>46171</v>
+      </c>
+      <c r="F101" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="G101" s="5"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E102" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F102" s="11" t="s">
-        <v>163</v>
+        <v>46171</v>
+      </c>
+      <c r="F102" s="13" t="s">
+        <v>130</v>
       </c>
       <c r="G102" s="5"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
-        <v>149</v>
+        <v>24</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>150</v>
+        <v>27</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>151</v>
+        <v>26</v>
       </c>
       <c r="E103" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F103" s="11" t="s">
-        <v>164</v>
+        <v>46171</v>
+      </c>
+      <c r="F103" s="13" t="s">
+        <v>137</v>
       </c>
       <c r="G103" s="5"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
-        <v>149</v>
+        <v>6</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>152</v>
+        <v>47</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>151</v>
+        <v>8</v>
       </c>
       <c r="E104" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F104" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G104" s="5"/>
+        <v>46170</v>
+      </c>
+      <c r="F104" s="13" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E105" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F105" s="11" t="s">
-        <v>165</v>
+        <v>46170</v>
+      </c>
+      <c r="F105" s="13" t="s">
+        <v>120</v>
       </c>
       <c r="G105" s="5"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E106" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F106" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G106" s="5"/>
+        <v>46170</v>
+      </c>
+      <c r="F106" s="16" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
-        <v>153</v>
+        <v>3</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>154</v>
+        <v>4</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>155</v>
+        <v>28</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>156</v>
+        <v>5</v>
       </c>
       <c r="E107" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F107" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="G107" s="5"/>
+        <v>46170</v>
+      </c>
+      <c r="F107" s="14" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
-        <v>153</v>
+        <v>3</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>154</v>
+        <v>4</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>157</v>
+        <v>29</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>156</v>
+        <v>5</v>
       </c>
       <c r="E108" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F108" s="8" t="s">
+        <v>46170</v>
+      </c>
+      <c r="F108" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="G108" s="5"/>
-    </row>
-    <row r="109" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E109" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F109" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G109" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>46170</v>
+      </c>
+      <c r="F109" s="14" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B110" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E110" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F110" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G110" s="5" t="s">
-        <v>31</v>
+        <v>46170</v>
+      </c>
+      <c r="F110" s="13" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D111" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E111" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F111" s="15" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A112" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D112" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E112" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F112" s="13" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A113" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B111" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C111" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D111" s="4" t="s">
+      <c r="B113" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D113" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E111" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F111" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="G111" s="5"/>
-    </row>
-    <row r="112" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A112" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="B112" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C112" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="D112" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="E112" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F112" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G112" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A113" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="B113" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C113" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="D113" s="4" t="s">
-        <v>160</v>
-      </c>
       <c r="E113" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F113" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G113" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>46170</v>
+      </c>
+      <c r="F113" s="13" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
-        <v>158</v>
+        <v>21</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>162</v>
+        <v>41</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>160</v>
+        <v>23</v>
       </c>
       <c r="E114" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F114" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G114" s="5" t="s">
-        <v>171</v>
+        <v>46170</v>
+      </c>
+      <c r="F114" s="13" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E115" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F115" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="G115" s="5"/>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+        <v>46170</v>
+      </c>
+      <c r="F115" s="13" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A116" s="4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E116" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F116" s="8" t="s">
+        <v>46170</v>
+      </c>
+      <c r="F116" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="G116" s="5"/>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G116" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E117" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F117" s="8" t="s">
+        <v>46170</v>
+      </c>
+      <c r="F117" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="G117" s="5"/>
+      <c r="G117" s="5" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" s="4" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E118" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F118" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="G118" s="5"/>
+        <v>46170</v>
+      </c>
+      <c r="F118" s="13" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E119" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F119" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G119" s="5"/>
+        <v>46170</v>
+      </c>
+      <c r="F119" s="13" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" s="4" t="s">
@@ -3683,54 +3860,1171 @@
         <v>13</v>
       </c>
       <c r="E120" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F120" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="G120" s="5"/>
+        <v>46170</v>
+      </c>
+      <c r="F120" s="14" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D121" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E121" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F121" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="G121" s="5"/>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A122" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C122" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D122" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E122" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F122" s="13" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A123" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C123" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D123" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E123" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F123" s="13" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A124" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B121" s="4" t="s">
+      <c r="B124" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C121" s="4" t="s">
+      <c r="C124" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D124" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E124" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F124" s="14" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A125" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C125" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D125" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E125" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F125" s="14" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A126" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C126" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="D121" s="4" t="s">
+      <c r="D126" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E121" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F121" s="8" t="s">
+      <c r="E126" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F126" s="14" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A127" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C127" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D127" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E127" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F127" s="14" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A128" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C128" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D128" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E128" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F128" s="14" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A129" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C129" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D129" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E129" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F129" s="14" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A130" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C130" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D130" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E130" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F130" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="G121" s="5"/>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A122" s="13" t="s">
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A131" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B131" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C131" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D131" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E131" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F131" s="14" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A132" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D132" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E132" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F132" s="14" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A133" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D133" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E133" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F133" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G133" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A134" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D134" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E134" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F134" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G134" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A135" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C135" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D135" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E135" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F135" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G135" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A136" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C136" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D136" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E136" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F136" s="14" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A137" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C137" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D137" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E137" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F137" s="14" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A138" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B138" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C138" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D138" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E138" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F138" s="14" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A139" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B139" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C139" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D139" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E139" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F139" s="16" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A140" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B140" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C140" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D140" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E140" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F140" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A141" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B141" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C141" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D141" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E141" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F141" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A142" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B122" s="13" t="s">
+      <c r="B142" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C122" s="13" t="s">
+      <c r="C142" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D142" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E142" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F142" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="G142" s="5"/>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A143" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B143" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C143" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D143" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E143" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F143" s="13" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A144" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C144" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D144" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E144" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F144" s="16" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A145" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C145" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D145" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E145" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F145" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G145" s="5"/>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A146" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C146" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D146" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E146" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F146" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="G146" s="6"/>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A147" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B147" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C147" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D147" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E147" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F147" s="14" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A148" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B148" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C148" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D148" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E148" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F148" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="G148" s="6"/>
+    </row>
+    <row r="149" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A149" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B149" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C149" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D149" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E149" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F149" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G149" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A150" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B150" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C150" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D150" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E150" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F150" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G150" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A151" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C151" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D151" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E151" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F151" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="G151" s="5"/>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A152" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B152" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C152" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D152" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E152" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F152" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="G152" s="6"/>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A153" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C153" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D153" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E153" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F153" s="13" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A154" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B154" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C154" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D154" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E154" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F154" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G154" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A155" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B155" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C155" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D155" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E155" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F155" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G155" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A156" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B156" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C156" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D156" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E156" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F156" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="G156" s="5"/>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A157" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C157" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D157" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E157" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F157" s="13" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A158" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C158" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D158" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E158" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F158" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="G158" s="5"/>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A159" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C159" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D159" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E159" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F159" s="14" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A160" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C160" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D160" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E160" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F160" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="G160" s="6"/>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A161" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B161" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C161" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D161" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E161" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F161" s="13" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A162" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B162" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C162" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D162" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E162" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F162" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A163" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C163" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="D122" s="13" t="s">
+      <c r="D163" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E122" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F122" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="G122" s="14"/>
+      <c r="E163" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F163" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A164" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C164" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D164" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E164" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F164" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A165" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B165" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C165" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D165" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E165" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F165" s="10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A166" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B166" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C166" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D166" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E166" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F166" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G166" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A167" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B167" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C167" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D167" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E167" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F167" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A168" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B168" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C168" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D168" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E168" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F168" s="8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A169" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B169" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C169" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D169" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E169" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F169" s="9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A170" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B170" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C170" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D170" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E170" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F170" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G170" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A171" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B171" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C171" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D171" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E171" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F171" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G171" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A172" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B172" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C172" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D172" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E172" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F172" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A173" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B173" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C173" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D173" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E173" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F173" s="10" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A174" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B174" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C174" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D174" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E174" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F174" s="10" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A175" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B175" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C175" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D175" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E175" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F175" s="9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A176" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B176" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C176" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D176" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E176" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F176" s="9" t="s">
+        <v>64</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -3741,14 +5035,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6b3feda4-8a83-4113-98ac-b9b0c9bd9eab">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="6ca87d14-fc9d-4fcf-a42b-2754e6b3d00d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3959,21 +5251,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6b3feda4-8a83-4113-98ac-b9b0c9bd9eab">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="6ca87d14-fc9d-4fcf-a42b-2754e6b3d00d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFC5C71E-79D6-437C-A06A-B0BD52E89317}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6F72255-F15E-4B46-A16C-2F18C675CB37}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6b3feda4-8a83-4113-98ac-b9b0c9bd9eab"/>
-    <ds:schemaRef ds:uri="6ca87d14-fc9d-4fcf-a42b-2754e6b3d00d"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3998,9 +5289,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6F72255-F15E-4B46-A16C-2F18C675CB37}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFC5C71E-79D6-437C-A06A-B0BD52E89317}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6b3feda4-8a83-4113-98ac-b9b0c9bd9eab"/>
+    <ds:schemaRef ds:uri="6ca87d14-fc9d-4fcf-a42b-2754e6b3d00d"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/EFETIVIDADE.xlsx
+++ b/EFETIVIDADE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://spotpromo.sharepoint.com/sites/bko.pribeiro/Documentos Compartilhados/PRibeiro/BAUDUCCO TMP/20 - EFETIVIDADE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="931" documentId="13_ncr:1_{C64068DB-D04A-49E7-B037-1281E1EE8D6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2B81C12-E79C-4CEC-8A29-F11E447A3C47}"/>
+  <xr:revisionPtr revIDLastSave="959" documentId="13_ncr:1_{C64068DB-D04A-49E7-B037-1281E1EE8D6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98823DDE-43DD-46DA-837B-F1A26390B859}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="260">
   <si>
     <t>ROTA</t>
   </si>
@@ -524,12 +524,6 @@
     <t>SUPERNOSSO - AVENIDA AFONSO PENA 3328, 3328 - BELO HORIZONTE/MG</t>
   </si>
   <si>
-    <t>07:02</t>
-  </si>
-  <si>
-    <t>08:00</t>
-  </si>
-  <si>
     <t>ESTÁ EM CAMPO, APRESENTOU PROBLEMA NO APARELHO.</t>
   </si>
   <si>
@@ -680,12 +674,6 @@
     <t>BH - AV SEVERINO BALLESTEROS RODRIGUE 65, 65 - CONTAGEM/MG</t>
   </si>
   <si>
-    <t>06:58</t>
-  </si>
-  <si>
-    <t>07:00</t>
-  </si>
-  <si>
     <t>07:06</t>
   </si>
   <si>
@@ -695,10 +683,136 @@
     <t>07:29</t>
   </si>
   <si>
-    <t>07:52</t>
-  </si>
-  <si>
-    <t>08:08</t>
+    <t>06:58  10:59</t>
+  </si>
+  <si>
+    <t>07:00  11:49</t>
+  </si>
+  <si>
+    <t>07:02  09:44</t>
+  </si>
+  <si>
+    <t>07:06  12:28</t>
+  </si>
+  <si>
+    <t>07:29  09:29</t>
+  </si>
+  <si>
+    <t>07:52  09:31</t>
+  </si>
+  <si>
+    <t>08:00  14:09</t>
+  </si>
+  <si>
+    <t>08:08  13:27</t>
+  </si>
+  <si>
+    <t>09:45  12:17</t>
+  </si>
+  <si>
+    <t>10:01  13:26</t>
+  </si>
+  <si>
+    <t>10:12  12:00</t>
+  </si>
+  <si>
+    <t>10:13  14:39</t>
+  </si>
+  <si>
+    <t>12:26</t>
+  </si>
+  <si>
+    <t>13:34</t>
+  </si>
+  <si>
+    <t>13:49  16:01</t>
+  </si>
+  <si>
+    <t>13:51  19:35</t>
+  </si>
+  <si>
+    <t>14:28  17:20</t>
+  </si>
+  <si>
+    <t>14:54  17:28</t>
+  </si>
+  <si>
+    <t>17:28</t>
+  </si>
+  <si>
+    <t>07:04  12:12</t>
+  </si>
+  <si>
+    <t>07:25  11:24</t>
+  </si>
+  <si>
+    <t>07:38  12:27</t>
+  </si>
+  <si>
+    <t>07:58  14:41</t>
+  </si>
+  <si>
+    <t>08:18  11:38</t>
+  </si>
+  <si>
+    <t>08:25  09:42</t>
+  </si>
+  <si>
+    <t>10:10  12:10</t>
+  </si>
+  <si>
+    <t>11:33  13:02</t>
+  </si>
+  <si>
+    <t>13:05  16:42</t>
+  </si>
+  <si>
+    <t>13:09  14:22</t>
+  </si>
+  <si>
+    <t>13:41  14:24</t>
+  </si>
+  <si>
+    <t>14:11</t>
+  </si>
+  <si>
+    <t>14:28  16:08</t>
+  </si>
+  <si>
+    <t>14:37  16:24</t>
+  </si>
+  <si>
+    <t>14:55  17:01</t>
+  </si>
+  <si>
+    <t>07:10</t>
+  </si>
+  <si>
+    <t>07:10  12:16</t>
+  </si>
+  <si>
+    <t>07:11  10:44</t>
+  </si>
+  <si>
+    <t>07:22  11:33</t>
+  </si>
+  <si>
+    <t>07:28  12:03</t>
+  </si>
+  <si>
+    <t>10:02  11:36</t>
+  </si>
+  <si>
+    <t>07:36</t>
+  </si>
+  <si>
+    <t>07:53</t>
+  </si>
+  <si>
+    <t>07:59</t>
+  </si>
+  <si>
+    <t>08:03</t>
   </si>
 </sst>
 </file>
@@ -811,7 +925,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -867,14 +981,26 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="20" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -976,10 +1102,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A4474625-D582-4F1B-AA27-C9E6E4248EEA}" name="Tabela1" displayName="Tabela1" ref="A1:G176" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7" headerRowCellStyle="Normal 2">
-  <autoFilter ref="A1:G176" xr:uid="{A4474625-D582-4F1B-AA27-C9E6E4248EEA}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G176">
-    <sortCondition descending="1" ref="E1:E176"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A4474625-D582-4F1B-AA27-C9E6E4248EEA}" name="Tabela1" displayName="Tabela1" ref="A1:G237" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7" headerRowCellStyle="Normal 2">
+  <autoFilter ref="A1:G237" xr:uid="{A4474625-D582-4F1B-AA27-C9E6E4248EEA}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G237">
+    <sortCondition descending="1" ref="E1:E237"/>
   </sortState>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{8C18829A-5E6C-4A32-820C-446F688CFF40}" name="ROTA" dataDxfId="6"/>
@@ -1311,7 +1437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G176"/>
+  <dimension ref="A1:G237"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" style="4" customWidth="1"/>
@@ -1355,16 +1481,16 @@
         <v>7</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="7">
-        <v>46176</v>
+        <v>46181</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>220</v>
+        <v>258</v>
       </c>
       <c r="G2" s="5"/>
     </row>
@@ -1376,13 +1502,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7">
-        <v>46176</v>
+        <v>46181</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>53</v>
@@ -1391,22 +1517,22 @@
     </row>
     <row r="4" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>6</v>
+        <v>153</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>7</v>
+        <v>154</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>71</v>
+        <v>155</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>8</v>
+        <v>156</v>
       </c>
       <c r="E4" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>53</v>
+        <v>46181</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>213</v>
       </c>
       <c r="G4" s="5"/>
     </row>
@@ -1418,76 +1544,76 @@
         <v>154</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>156</v>
       </c>
       <c r="E5" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>217</v>
+        <v>46181</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G5" s="5"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>154</v>
+        <v>10</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>188</v>
+        <v>150</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E6" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>53</v>
+        <v>46181</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>256</v>
       </c>
       <c r="G6" s="5"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="22" t="s">
         <v>149</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="D7" s="4" t="s">
+      <c r="C7" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="D7" s="22" t="s">
         <v>151</v>
       </c>
       <c r="E7" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="G7" s="5"/>
+        <v>46181</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G7" s="23"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>149</v>
+        <v>3</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>189</v>
+        <v>28</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>151</v>
+        <v>5</v>
       </c>
       <c r="E8" s="7">
-        <v>46176</v>
+        <v>46181</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>53</v>
@@ -1496,19 +1622,19 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>149</v>
+        <v>3</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>214</v>
+        <v>29</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>151</v>
+        <v>5</v>
       </c>
       <c r="E9" s="7">
-        <v>46176</v>
+        <v>46181</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>53</v>
@@ -1517,40 +1643,40 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E10" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>163</v>
+        <v>46181</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G10" s="5"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E11" s="7">
-        <v>46176</v>
+        <v>46181</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>53</v>
@@ -1559,218 +1685,208 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E12" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>221</v>
+        <v>46181</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G12" s="5"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>16</v>
+        <v>158</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>55</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>56</v>
+        <v>159</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>17</v>
+        <v>160</v>
       </c>
       <c r="E13" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>53</v>
+        <v>46181</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>259</v>
       </c>
       <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>21</v>
+        <v>158</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>60</v>
+        <v>162</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>23</v>
+        <v>160</v>
       </c>
       <c r="E14" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>215</v>
+        <v>46181</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>21</v>
+        <v>158</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>94</v>
+        <v>161</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>23</v>
+        <v>160</v>
       </c>
       <c r="E15" s="7">
-        <v>46176</v>
+        <v>46181</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>53</v>
       </c>
       <c r="G15" s="5"/>
     </row>
-    <row r="16" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>158</v>
+        <v>19</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>159</v>
+        <v>32</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="E16" s="7">
-        <v>46176</v>
+        <v>46181</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="G16" s="5" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G16" s="5"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>158</v>
+        <v>19</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>161</v>
+        <v>59</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="E17" s="7">
-        <v>46176</v>
+        <v>46181</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="G17" s="5" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G17" s="5"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>158</v>
+        <v>11</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
       <c r="E18" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>46181</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="G18" s="5"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E19" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>46181</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="G19" s="5"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E20" s="7">
-        <v>46176</v>
+        <v>46181</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="G20" s="5" t="s">
-        <v>31</v>
-      </c>
+      <c r="G20" s="5"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E21" s="7">
-        <v>46176</v>
+        <v>46181</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>53</v>
@@ -1779,124 +1895,124 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E22" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>218</v>
+        <v>46181</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G22" s="5"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>15</v>
+      <c r="A23" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="D23" s="22" t="s">
+        <v>8</v>
       </c>
       <c r="E23" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G23" s="5"/>
+        <v>46179</v>
+      </c>
+      <c r="F23" s="21" t="s">
+        <v>255</v>
+      </c>
+      <c r="G23" s="23"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>12</v>
+        <v>153</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>9</v>
+        <v>154</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>30</v>
+        <v>186</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>13</v>
+        <v>156</v>
       </c>
       <c r="E24" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>164</v>
+        <v>46179</v>
+      </c>
+      <c r="F24" s="21" t="s">
+        <v>250</v>
       </c>
       <c r="G24" s="5"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B25" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="C25" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="D25" s="19" t="s">
-        <v>13</v>
+      <c r="A25" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>151</v>
       </c>
       <c r="E25" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G25" s="20"/>
+        <v>46179</v>
+      </c>
+      <c r="F25" s="21" t="s">
+        <v>254</v>
+      </c>
+      <c r="G25" s="5"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="E26" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F26" s="11" t="s">
-        <v>216</v>
+        <v>46179</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G26" s="5"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E27" s="7">
-        <v>46176</v>
+        <v>46179</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>53</v>
@@ -1905,460 +2021,460 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E28" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F28" s="17" t="s">
-        <v>199</v>
+        <v>46179</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G28" s="5"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>6</v>
+        <v>158</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>48</v>
+        <v>183</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>8</v>
+        <v>160</v>
       </c>
       <c r="E29" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F29" s="17" t="s">
-        <v>206</v>
+        <v>46179</v>
+      </c>
+      <c r="F29" s="21" t="s">
+        <v>253</v>
       </c>
       <c r="G29" s="5"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E30" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F30" s="17" t="s">
-        <v>210</v>
+        <v>46179</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G30" s="5"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>153</v>
+        <v>11</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>154</v>
+        <v>10</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>182</v>
+        <v>33</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>156</v>
+        <v>15</v>
       </c>
       <c r="E31" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F31" s="17" t="s">
-        <v>193</v>
+        <v>46179</v>
+      </c>
+      <c r="F31" s="21" t="s">
+        <v>252</v>
       </c>
       <c r="G31" s="5"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>153</v>
+        <v>12</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>154</v>
+        <v>9</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>187</v>
+        <v>95</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>156</v>
+        <v>13</v>
       </c>
       <c r="E32" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F32" s="17" t="s">
-        <v>204</v>
+        <v>46179</v>
+      </c>
+      <c r="F32" s="21" t="s">
+        <v>251</v>
       </c>
       <c r="G32" s="5"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>153</v>
+        <v>24</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>154</v>
+        <v>25</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>188</v>
+        <v>42</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>156</v>
+        <v>26</v>
       </c>
       <c r="E33" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F33" s="17" t="s">
-        <v>208</v>
+        <v>46179</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G33" s="5"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>149</v>
+        <v>6</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>150</v>
+        <v>47</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>151</v>
+        <v>8</v>
       </c>
       <c r="E34" s="7">
-        <v>46175</v>
+        <v>46178</v>
       </c>
       <c r="F34" s="17" t="s">
-        <v>195</v>
+        <v>240</v>
       </c>
       <c r="G34" s="5"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>149</v>
+        <v>6</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>186</v>
+        <v>73</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>151</v>
+        <v>8</v>
       </c>
       <c r="E35" s="7">
-        <v>46175</v>
+        <v>46178</v>
       </c>
       <c r="F35" s="17" t="s">
-        <v>203</v>
+        <v>241</v>
       </c>
       <c r="G35" s="5"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>149</v>
+        <v>6</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>189</v>
+        <v>71</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>151</v>
+        <v>8</v>
       </c>
       <c r="E36" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F36" s="17" t="s">
-        <v>212</v>
+        <v>46178</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>246</v>
       </c>
       <c r="G36" s="5"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>3</v>
+        <v>153</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>4</v>
+        <v>154</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>29</v>
+        <v>155</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>5</v>
+        <v>156</v>
       </c>
       <c r="E37" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F37" s="18" t="s">
-        <v>191</v>
+        <v>46178</v>
+      </c>
+      <c r="F37" s="17" t="s">
+        <v>235</v>
       </c>
       <c r="G37" s="5"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>3</v>
+        <v>153</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>4</v>
+        <v>154</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>28</v>
+        <v>186</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>5</v>
+        <v>156</v>
       </c>
       <c r="E38" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F38" s="18" t="s">
-        <v>201</v>
+        <v>46178</v>
+      </c>
+      <c r="F38" s="17" t="s">
+        <v>244</v>
       </c>
       <c r="G38" s="5"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>3</v>
+        <v>153</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>4</v>
+        <v>154</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>44</v>
+        <v>157</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>5</v>
+        <v>156</v>
       </c>
       <c r="E39" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F39" s="18" t="s">
-        <v>205</v>
+        <v>46178</v>
+      </c>
+      <c r="F39" s="17" t="s">
+        <v>247</v>
       </c>
       <c r="G39" s="5"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>16</v>
+        <v>149</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>36</v>
+        <v>150</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>17</v>
+        <v>151</v>
       </c>
       <c r="E40" s="7">
-        <v>46175</v>
+        <v>46178</v>
       </c>
       <c r="F40" s="17" t="s">
-        <v>196</v>
+        <v>236</v>
       </c>
       <c r="G40" s="5"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
-        <v>16</v>
+        <v>149</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>34</v>
+        <v>184</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>17</v>
+        <v>151</v>
       </c>
       <c r="E41" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F41" s="8" t="s">
-        <v>53</v>
+        <v>46178</v>
+      </c>
+      <c r="F41" s="17" t="s">
+        <v>242</v>
       </c>
       <c r="G41" s="5"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
-        <v>21</v>
+        <v>149</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>40</v>
+        <v>212</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>23</v>
+        <v>151</v>
       </c>
       <c r="E42" s="7">
-        <v>46175</v>
+        <v>46178</v>
       </c>
       <c r="F42" s="17" t="s">
-        <v>190</v>
+        <v>245</v>
       </c>
       <c r="G42" s="5"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
-        <v>21</v>
+        <v>149</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>41</v>
+        <v>187</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>23</v>
+        <v>151</v>
       </c>
       <c r="E43" s="7">
-        <v>46175</v>
+        <v>46178</v>
       </c>
       <c r="F43" s="17" t="s">
-        <v>200</v>
+        <v>248</v>
       </c>
       <c r="G43" s="5"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="E44" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F44" s="17" t="s">
-        <v>207</v>
+        <v>46178</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G44" s="5"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
-        <v>158</v>
+        <v>3</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>183</v>
+        <v>28</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>160</v>
+        <v>5</v>
       </c>
       <c r="E45" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F45" s="17" t="s">
-        <v>194</v>
+        <v>46178</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G45" s="5"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
-        <v>158</v>
+        <v>16</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>55</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>184</v>
+        <v>56</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>160</v>
+        <v>17</v>
       </c>
       <c r="E46" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F46" s="8" t="s">
-        <v>53</v>
+        <v>46178</v>
+      </c>
+      <c r="F46" s="17" t="s">
+        <v>239</v>
       </c>
       <c r="G46" s="5"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
-        <v>158</v>
+        <v>16</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>185</v>
+        <v>36</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>160</v>
+        <v>17</v>
       </c>
       <c r="E47" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F47" s="17" t="s">
-        <v>202</v>
+        <v>46178</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G47" s="5"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E48" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F48" s="8" t="s">
-        <v>53</v>
+        <v>46178</v>
+      </c>
+      <c r="F48" s="17" t="s">
+        <v>243</v>
       </c>
       <c r="G48" s="5"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E49" s="7">
-        <v>46175</v>
+        <v>46178</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>53</v>
@@ -2367,2662 +2483,3951 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E50" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F50" s="17" t="s">
-        <v>197</v>
+        <v>46178</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G50" s="5"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
-        <v>11</v>
+        <v>158</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>33</v>
+        <v>162</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>15</v>
+        <v>160</v>
       </c>
       <c r="E51" s="7">
-        <v>46175</v>
+        <v>46178</v>
       </c>
       <c r="F51" s="17" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="G51" s="5"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
-        <v>12</v>
+        <v>158</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>30</v>
+        <v>161</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>13</v>
+        <v>160</v>
       </c>
       <c r="E52" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F52" s="18" t="s">
-        <v>198</v>
+        <v>46178</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G52" s="5"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B53" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="C53" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="D53" s="19" t="s">
-        <v>13</v>
+      <c r="A53" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="B53" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="C53" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="D53" s="22" t="s">
+        <v>160</v>
       </c>
       <c r="E53" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F53" s="18" t="s">
-        <v>213</v>
-      </c>
-      <c r="G53" s="20"/>
+        <v>46178</v>
+      </c>
+      <c r="F53" s="24">
+        <v>0.34930555555555554</v>
+      </c>
+      <c r="G53" s="23"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>25</v>
+        <v>91</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>42</v>
+        <v>92</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E54" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F54" s="17" t="s">
-        <v>192</v>
+        <v>46178</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G54" s="5"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E55" s="7">
+        <v>46178</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G55" s="5"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A56" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E56" s="7">
+        <v>46178</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G56" s="5"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A57" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E57" s="7">
+        <v>46178</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G57" s="5"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A58" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E58" s="7">
+        <v>46178</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G58" s="5"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A59" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E59" s="7">
+        <v>46178</v>
+      </c>
+      <c r="F59" s="18" t="s">
+        <v>238</v>
+      </c>
+      <c r="G59" s="5"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A60" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E60" s="7">
+        <v>46178</v>
+      </c>
+      <c r="F60" s="18" t="s">
+        <v>249</v>
+      </c>
+      <c r="G60" s="5"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A61" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="B61" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C55" s="4" t="s">
+      <c r="C61" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D55" s="4" t="s">
+      <c r="D61" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E55" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F55" s="17" t="s">
-        <v>211</v>
-      </c>
-      <c r="G55" s="5"/>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>6</v>
-      </c>
-      <c r="B56" t="s">
-        <v>7</v>
-      </c>
-      <c r="C56" t="s">
-        <v>73</v>
-      </c>
-      <c r="D56" t="s">
-        <v>8</v>
-      </c>
-      <c r="E56" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F56" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="G56" s="5"/>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>6</v>
-      </c>
-      <c r="B57" t="s">
-        <v>7</v>
-      </c>
-      <c r="C57" t="s">
-        <v>71</v>
-      </c>
-      <c r="D57" t="s">
-        <v>8</v>
-      </c>
-      <c r="E57" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F57" s="17" t="s">
-        <v>178</v>
-      </c>
-      <c r="G57" s="5"/>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>153</v>
-      </c>
-      <c r="B58" t="s">
-        <v>154</v>
-      </c>
-      <c r="C58" t="s">
-        <v>155</v>
-      </c>
-      <c r="D58" t="s">
-        <v>156</v>
-      </c>
-      <c r="E58" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F58" s="17" t="s">
-        <v>173</v>
-      </c>
-      <c r="G58" s="5"/>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>153</v>
-      </c>
-      <c r="B59" t="s">
-        <v>154</v>
-      </c>
-      <c r="C59" t="s">
-        <v>157</v>
-      </c>
-      <c r="D59" t="s">
-        <v>156</v>
-      </c>
-      <c r="E59" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F59" s="17" t="s">
-        <v>179</v>
-      </c>
-      <c r="G59" s="5"/>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>149</v>
-      </c>
-      <c r="B60" t="s">
-        <v>10</v>
-      </c>
-      <c r="C60" t="s">
-        <v>150</v>
-      </c>
-      <c r="D60" t="s">
-        <v>151</v>
-      </c>
-      <c r="E60" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F60" s="17" t="s">
-        <v>170</v>
-      </c>
-      <c r="G60" s="5"/>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>149</v>
-      </c>
-      <c r="B61" t="s">
-        <v>10</v>
-      </c>
-      <c r="C61" t="s">
-        <v>152</v>
-      </c>
-      <c r="D61" t="s">
-        <v>151</v>
-      </c>
       <c r="E61" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F61" s="11" t="s">
-        <v>180</v>
+        <v>46178</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G61" s="5"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>3</v>
-      </c>
-      <c r="B62" t="s">
-        <v>4</v>
-      </c>
-      <c r="C62" t="s">
-        <v>29</v>
-      </c>
-      <c r="D62" t="s">
-        <v>5</v>
+      <c r="A62" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="E62" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F62" s="18" t="s">
-        <v>168</v>
+        <v>46178</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G62" s="5"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B63" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C63" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="D63" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E63" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F63" s="18" t="s">
-        <v>176</v>
+        <v>46176</v>
+      </c>
+      <c r="F63" s="17" t="s">
+        <v>221</v>
       </c>
       <c r="G63" s="5"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B64" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C64" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="D64" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E64" s="7">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="F64" s="17" t="s">
-        <v>175</v>
+        <v>224</v>
       </c>
       <c r="G64" s="5"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B65" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C65" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D65" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E65" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F65" s="8" t="s">
-        <v>53</v>
+        <v>46176</v>
+      </c>
+      <c r="F65" s="11" t="s">
+        <v>229</v>
       </c>
       <c r="G65" s="5"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>21</v>
+        <v>153</v>
       </c>
       <c r="B66" t="s">
-        <v>22</v>
+        <v>154</v>
       </c>
       <c r="C66" t="s">
-        <v>60</v>
+        <v>155</v>
       </c>
       <c r="D66" t="s">
-        <v>23</v>
+        <v>156</v>
       </c>
       <c r="E66" s="7">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="F66" s="17" t="s">
-        <v>169</v>
+        <v>219</v>
       </c>
       <c r="G66" s="5"/>
     </row>
-    <row r="67" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B67" t="s">
-        <v>55</v>
+        <v>154</v>
       </c>
       <c r="C67" t="s">
-        <v>159</v>
+        <v>186</v>
       </c>
       <c r="D67" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E67" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F67" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G67" s="5" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>46176</v>
+      </c>
+      <c r="F67" s="17" t="s">
+        <v>230</v>
+      </c>
+      <c r="G67" s="5"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="B68" t="s">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="C68" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="D68" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="E68" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F68" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G68" s="5" t="s">
-        <v>165</v>
-      </c>
+        <v>46176</v>
+      </c>
+      <c r="F68" s="17" t="s">
+        <v>220</v>
+      </c>
+      <c r="G68" s="5"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="B69" t="s">
         <v>55</v>
       </c>
       <c r="C69" t="s">
-        <v>162</v>
+        <v>187</v>
       </c>
       <c r="D69" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="E69" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F69" s="11" t="s">
-        <v>181</v>
+        <v>46176</v>
+      </c>
+      <c r="F69" s="17" t="s">
+        <v>225</v>
       </c>
       <c r="G69" s="5"/>
     </row>
-    <row r="70" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>19</v>
+        <v>149</v>
       </c>
       <c r="B70" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C70" t="s">
-        <v>59</v>
+        <v>212</v>
       </c>
       <c r="D70" t="s">
-        <v>20</v>
+        <v>151</v>
       </c>
       <c r="E70" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F70" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G70" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>46176</v>
+      </c>
+      <c r="F70" s="17" t="s">
+        <v>231</v>
+      </c>
+      <c r="G70" s="5"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="B71" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C71" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D71" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E71" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F71" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G71" s="5" t="s">
-        <v>31</v>
-      </c>
+        <v>46176</v>
+      </c>
+      <c r="F71" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="G71" s="5"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B72" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C72" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D72" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E72" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F72" s="17" t="s">
-        <v>172</v>
+        <v>46176</v>
+      </c>
+      <c r="F72" s="18" t="s">
+        <v>226</v>
       </c>
       <c r="G72" s="5"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B73" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C73" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="D73" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E73" s="7">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="F73" s="18" t="s">
-        <v>174</v>
+        <v>223</v>
       </c>
       <c r="G73" s="5"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B74" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="C74" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="D74" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E74" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F74" s="21" t="s">
+        <v>46176</v>
+      </c>
+      <c r="F74" s="25" t="s">
         <v>53</v>
       </c>
       <c r="G74" s="5"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
+        <v>21</v>
+      </c>
+      <c r="B75" t="s">
+        <v>22</v>
+      </c>
+      <c r="C75" t="s">
+        <v>60</v>
+      </c>
+      <c r="D75" t="s">
+        <v>23</v>
+      </c>
+      <c r="E75" s="7">
+        <v>46176</v>
+      </c>
+      <c r="F75" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="G75" s="5"/>
+    </row>
+    <row r="76" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>21</v>
+      </c>
+      <c r="B76" t="s">
+        <v>22</v>
+      </c>
+      <c r="C76" t="s">
+        <v>94</v>
+      </c>
+      <c r="D76" t="s">
+        <v>23</v>
+      </c>
+      <c r="E76" s="7">
+        <v>46176</v>
+      </c>
+      <c r="F76" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G76" s="5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>158</v>
+      </c>
+      <c r="B77" t="s">
+        <v>55</v>
+      </c>
+      <c r="C77" t="s">
+        <v>159</v>
+      </c>
+      <c r="D77" t="s">
+        <v>160</v>
+      </c>
+      <c r="E77" s="7">
+        <v>46176</v>
+      </c>
+      <c r="F77" s="17" t="s">
+        <v>227</v>
+      </c>
+      <c r="G77" s="5"/>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>158</v>
+      </c>
+      <c r="B78" t="s">
+        <v>55</v>
+      </c>
+      <c r="C78" t="s">
+        <v>161</v>
+      </c>
+      <c r="D78" t="s">
+        <v>160</v>
+      </c>
+      <c r="E78" s="7">
+        <v>46176</v>
+      </c>
+      <c r="F78" s="17" t="s">
+        <v>233</v>
+      </c>
+      <c r="G78" s="5"/>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>158</v>
+      </c>
+      <c r="B79" t="s">
+        <v>55</v>
+      </c>
+      <c r="C79" t="s">
+        <v>162</v>
+      </c>
+      <c r="D79" t="s">
+        <v>160</v>
+      </c>
+      <c r="E79" s="7">
+        <v>46176</v>
+      </c>
+      <c r="F79" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="G79" s="5"/>
+    </row>
+    <row r="80" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>19</v>
+      </c>
+      <c r="B80" t="s">
+        <v>91</v>
+      </c>
+      <c r="C80" t="s">
+        <v>92</v>
+      </c>
+      <c r="D80" t="s">
+        <v>20</v>
+      </c>
+      <c r="E80" s="7">
+        <v>46176</v>
+      </c>
+      <c r="F80" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G80" s="5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>19</v>
+      </c>
+      <c r="B81" t="s">
+        <v>18</v>
+      </c>
+      <c r="C81" t="s">
+        <v>59</v>
+      </c>
+      <c r="D81" t="s">
+        <v>20</v>
+      </c>
+      <c r="E81" s="7">
+        <v>46176</v>
+      </c>
+      <c r="F81" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G81" s="5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>19</v>
+      </c>
+      <c r="B82" t="s">
+        <v>18</v>
+      </c>
+      <c r="C82" t="s">
+        <v>93</v>
+      </c>
+      <c r="D82" t="s">
+        <v>20</v>
+      </c>
+      <c r="E82" s="7">
+        <v>46176</v>
+      </c>
+      <c r="F82" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G82" s="5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>11</v>
+      </c>
+      <c r="B83" t="s">
+        <v>10</v>
+      </c>
+      <c r="C83" t="s">
+        <v>14</v>
+      </c>
+      <c r="D83" t="s">
+        <v>15</v>
+      </c>
+      <c r="E83" s="7">
+        <v>46176</v>
+      </c>
+      <c r="F83" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="G83" s="5"/>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>11</v>
+      </c>
+      <c r="B84" t="s">
+        <v>10</v>
+      </c>
+      <c r="C84" t="s">
+        <v>90</v>
+      </c>
+      <c r="D84" t="s">
+        <v>15</v>
+      </c>
+      <c r="E84" s="7">
+        <v>46176</v>
+      </c>
+      <c r="F84" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G84" s="5"/>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>12</v>
+      </c>
+      <c r="B85" t="s">
+        <v>9</v>
+      </c>
+      <c r="C85" t="s">
+        <v>30</v>
+      </c>
+      <c r="D85" t="s">
+        <v>13</v>
+      </c>
+      <c r="E85" s="7">
+        <v>46176</v>
+      </c>
+      <c r="F85" s="18" t="s">
+        <v>222</v>
+      </c>
+      <c r="G85" s="5"/>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>12</v>
+      </c>
+      <c r="B86" t="s">
+        <v>9</v>
+      </c>
+      <c r="C86" t="s">
+        <v>95</v>
+      </c>
+      <c r="D86" t="s">
+        <v>13</v>
+      </c>
+      <c r="E86" s="7">
+        <v>46176</v>
+      </c>
+      <c r="F86" s="18" t="s">
+        <v>232</v>
+      </c>
+      <c r="G86" s="5"/>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
         <v>24</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B87" t="s">
         <v>25</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C87" t="s">
         <v>62</v>
       </c>
-      <c r="D75" t="s">
+      <c r="D87" t="s">
         <v>26</v>
       </c>
-      <c r="E75" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F75" s="17" t="s">
-        <v>167</v>
-      </c>
-      <c r="G75" s="5"/>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
+      <c r="E87" s="7">
+        <v>46176</v>
+      </c>
+      <c r="F87" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="G87" s="5"/>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
         <v>24</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B88" t="s">
         <v>25</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C88" t="s">
         <v>27</v>
       </c>
-      <c r="D76" t="s">
+      <c r="D88" t="s">
         <v>26</v>
       </c>
-      <c r="E76" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F76" s="17" t="s">
-        <v>177</v>
-      </c>
-      <c r="G76" s="5"/>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A77" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B77" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E77" s="7">
-        <v>46172</v>
-      </c>
-      <c r="F77" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="G77" s="5"/>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A78" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B78" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C78" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D78" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E78" s="7">
-        <v>46172</v>
-      </c>
-      <c r="F78" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G78" s="5" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A79" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B79" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D79" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E79" s="7">
-        <v>46172</v>
-      </c>
-      <c r="F79" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="G79" s="6"/>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A80" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B80" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C80" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D80" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E80" s="7">
-        <v>46172</v>
-      </c>
-      <c r="F80" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="G80" s="5"/>
-    </row>
-    <row r="81" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A81" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B81" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C81" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D81" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E81" s="7">
-        <v>46172</v>
-      </c>
-      <c r="F81" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G81" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A82" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B82" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C82" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D82" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E82" s="7">
-        <v>46172</v>
-      </c>
-      <c r="F82" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="G82" s="5"/>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A83" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B83" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C83" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D83" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E83" s="7">
-        <v>46172</v>
-      </c>
-      <c r="F83" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="G83" s="5"/>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A84" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B84" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C84" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D84" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E84" s="7">
-        <v>46172</v>
-      </c>
-      <c r="F84" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="G84" s="5"/>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A85" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B85" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D85" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E85" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F85" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="G85" s="5"/>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A86" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B86" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D86" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E86" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F86" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="G86" s="5"/>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A87" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B87" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C87" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D87" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E87" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F87" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="G87" s="5"/>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A88" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B88" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C88" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D88" s="4" t="s">
-        <v>5</v>
-      </c>
       <c r="E88" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F88" s="14" t="s">
-        <v>129</v>
+        <v>46176</v>
+      </c>
+      <c r="F88" s="11" t="s">
+        <v>228</v>
       </c>
       <c r="G88" s="5"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E89" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F89" s="14" t="s">
-        <v>136</v>
+        <v>46175</v>
+      </c>
+      <c r="F89" s="17" t="s">
+        <v>197</v>
       </c>
       <c r="G89" s="5"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E90" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F90" s="14" t="s">
-        <v>134</v>
+        <v>46175</v>
+      </c>
+      <c r="F90" s="17" t="s">
+        <v>204</v>
       </c>
       <c r="G90" s="5"/>
     </row>
-    <row r="91" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E91" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F91" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="G91" s="5" t="s">
-        <v>31</v>
-      </c>
+        <v>46175</v>
+      </c>
+      <c r="F91" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="G91" s="5"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
-        <v>16</v>
+        <v>153</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>18</v>
+        <v>154</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>36</v>
+        <v>180</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>17</v>
+        <v>156</v>
       </c>
       <c r="E92" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F92" s="14" t="s">
-        <v>142</v>
+        <v>46175</v>
+      </c>
+      <c r="F92" s="17" t="s">
+        <v>191</v>
       </c>
       <c r="G92" s="5"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
-        <v>21</v>
+        <v>153</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>22</v>
+        <v>154</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>60</v>
+        <v>185</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>23</v>
+        <v>156</v>
       </c>
       <c r="E93" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F93" s="13" t="s">
-        <v>131</v>
+        <v>46175</v>
+      </c>
+      <c r="F93" s="17" t="s">
+        <v>202</v>
       </c>
       <c r="G93" s="5"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
-        <v>21</v>
+        <v>153</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>22</v>
+        <v>154</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>94</v>
+        <v>186</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>23</v>
+        <v>156</v>
       </c>
       <c r="E94" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F94" s="13" t="s">
-        <v>138</v>
+        <v>46175</v>
+      </c>
+      <c r="F94" s="17" t="s">
+        <v>206</v>
       </c>
       <c r="G94" s="5"/>
     </row>
-    <row r="95" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
-        <v>19</v>
+        <v>149</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>92</v>
+        <v>150</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>20</v>
+        <v>151</v>
       </c>
       <c r="E95" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F95" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="G95" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>46175</v>
+      </c>
+      <c r="F95" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="G95" s="5"/>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
-        <v>19</v>
+        <v>149</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>59</v>
+        <v>184</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>20</v>
+        <v>151</v>
       </c>
       <c r="E96" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F96" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="G96" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>46175</v>
+      </c>
+      <c r="F96" s="17" t="s">
+        <v>201</v>
+      </c>
+      <c r="G96" s="5"/>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
-        <v>19</v>
+        <v>149</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>93</v>
+        <v>187</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>20</v>
+        <v>151</v>
       </c>
       <c r="E97" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F97" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="G97" s="5" t="s">
-        <v>31</v>
-      </c>
+        <v>46175</v>
+      </c>
+      <c r="F97" s="17" t="s">
+        <v>210</v>
+      </c>
+      <c r="G97" s="5"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E98" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F98" s="13" t="s">
-        <v>132</v>
+        <v>46175</v>
+      </c>
+      <c r="F98" s="18" t="s">
+        <v>189</v>
       </c>
       <c r="G98" s="5"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>90</v>
+        <v>28</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E99" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F99" s="13" t="s">
-        <v>139</v>
+        <v>46175</v>
+      </c>
+      <c r="F99" s="18" t="s">
+        <v>199</v>
       </c>
       <c r="G99" s="5"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E100" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F100" s="14" t="s">
-        <v>133</v>
+        <v>46175</v>
+      </c>
+      <c r="F100" s="18" t="s">
+        <v>203</v>
       </c>
       <c r="G100" s="5"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E101" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F101" s="14" t="s">
-        <v>141</v>
+        <v>46175</v>
+      </c>
+      <c r="F101" s="17" t="s">
+        <v>194</v>
       </c>
       <c r="G101" s="5"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E102" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F102" s="13" t="s">
-        <v>130</v>
+        <v>46175</v>
+      </c>
+      <c r="F102" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G102" s="5"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E103" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F103" s="13" t="s">
-        <v>137</v>
+        <v>46175</v>
+      </c>
+      <c r="F103" s="17" t="s">
+        <v>188</v>
       </c>
       <c r="G103" s="5"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E104" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F104" s="13" t="s">
-        <v>114</v>
-      </c>
+        <v>46175</v>
+      </c>
+      <c r="F104" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="G104" s="5"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E105" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F105" s="13" t="s">
-        <v>120</v>
+        <v>46175</v>
+      </c>
+      <c r="F105" s="17" t="s">
+        <v>205</v>
       </c>
       <c r="G105" s="5"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
-        <v>6</v>
+        <v>158</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>46</v>
+        <v>181</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>8</v>
+        <v>160</v>
       </c>
       <c r="E106" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F106" s="16" t="s">
-        <v>125</v>
-      </c>
+        <v>46175</v>
+      </c>
+      <c r="F106" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="G106" s="5"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
-        <v>3</v>
+        <v>158</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>28</v>
+        <v>182</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>5</v>
+        <v>160</v>
       </c>
       <c r="E107" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F107" s="14" t="s">
-        <v>116</v>
-      </c>
+        <v>46175</v>
+      </c>
+      <c r="F107" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G107" s="5"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
-        <v>3</v>
+        <v>158</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>29</v>
+        <v>183</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>5</v>
+        <v>160</v>
       </c>
       <c r="E108" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F108" s="15" t="s">
-        <v>53</v>
-      </c>
+        <v>46175</v>
+      </c>
+      <c r="F108" s="17" t="s">
+        <v>200</v>
+      </c>
+      <c r="G108" s="5"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E109" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F109" s="14" t="s">
-        <v>127</v>
-      </c>
+        <v>46175</v>
+      </c>
+      <c r="F109" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G109" s="5"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B110" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E110" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F110" s="13" t="s">
-        <v>118</v>
-      </c>
+        <v>46175</v>
+      </c>
+      <c r="F110" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G110" s="5"/>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E111" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F111" s="15" t="s">
-        <v>53</v>
-      </c>
+        <v>46175</v>
+      </c>
+      <c r="F111" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="G111" s="5"/>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" s="4" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E112" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F112" s="13" t="s">
-        <v>124</v>
-      </c>
+        <v>46175</v>
+      </c>
+      <c r="F112" s="17" t="s">
+        <v>207</v>
+      </c>
+      <c r="G112" s="5"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" s="4" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E113" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F113" s="13" t="s">
-        <v>97</v>
-      </c>
+        <v>46175</v>
+      </c>
+      <c r="F113" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="G113" s="5"/>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E114" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F114" s="13" t="s">
-        <v>119</v>
-      </c>
+        <v>46175</v>
+      </c>
+      <c r="F114" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="G114" s="5"/>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D115" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E115" s="7">
+        <v>46175</v>
+      </c>
+      <c r="F115" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="G115" s="5"/>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A116" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D116" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E116" s="7">
+        <v>46175</v>
+      </c>
+      <c r="F116" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="G116" s="5"/>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>6</v>
+      </c>
+      <c r="B117" t="s">
+        <v>7</v>
+      </c>
+      <c r="C117" t="s">
+        <v>73</v>
+      </c>
+      <c r="D117" t="s">
+        <v>8</v>
+      </c>
+      <c r="E117" s="7">
+        <v>46174</v>
+      </c>
+      <c r="F117" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="G117" s="5"/>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>6</v>
+      </c>
+      <c r="B118" t="s">
+        <v>7</v>
+      </c>
+      <c r="C118" t="s">
+        <v>71</v>
+      </c>
+      <c r="D118" t="s">
+        <v>8</v>
+      </c>
+      <c r="E118" s="7">
+        <v>46174</v>
+      </c>
+      <c r="F118" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="G118" s="5"/>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>153</v>
+      </c>
+      <c r="B119" t="s">
+        <v>154</v>
+      </c>
+      <c r="C119" t="s">
+        <v>155</v>
+      </c>
+      <c r="D119" t="s">
+        <v>156</v>
+      </c>
+      <c r="E119" s="7">
+        <v>46174</v>
+      </c>
+      <c r="F119" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="G119" s="5"/>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>153</v>
+      </c>
+      <c r="B120" t="s">
+        <v>154</v>
+      </c>
+      <c r="C120" t="s">
+        <v>157</v>
+      </c>
+      <c r="D120" t="s">
+        <v>156</v>
+      </c>
+      <c r="E120" s="7">
+        <v>46174</v>
+      </c>
+      <c r="F120" s="17" t="s">
+        <v>177</v>
+      </c>
+      <c r="G120" s="5"/>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>149</v>
+      </c>
+      <c r="B121" t="s">
+        <v>10</v>
+      </c>
+      <c r="C121" t="s">
+        <v>150</v>
+      </c>
+      <c r="D121" t="s">
+        <v>151</v>
+      </c>
+      <c r="E121" s="7">
+        <v>46174</v>
+      </c>
+      <c r="F121" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="G121" s="5"/>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>149</v>
+      </c>
+      <c r="B122" t="s">
+        <v>10</v>
+      </c>
+      <c r="C122" t="s">
+        <v>152</v>
+      </c>
+      <c r="D122" t="s">
+        <v>151</v>
+      </c>
+      <c r="E122" s="7">
+        <v>46174</v>
+      </c>
+      <c r="F122" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="G122" s="5"/>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>3</v>
+      </c>
+      <c r="B123" t="s">
+        <v>4</v>
+      </c>
+      <c r="C123" t="s">
+        <v>29</v>
+      </c>
+      <c r="D123" t="s">
+        <v>5</v>
+      </c>
+      <c r="E123" s="7">
+        <v>46174</v>
+      </c>
+      <c r="F123" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="G123" s="5"/>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>3</v>
+      </c>
+      <c r="B124" t="s">
+        <v>4</v>
+      </c>
+      <c r="C124" t="s">
+        <v>28</v>
+      </c>
+      <c r="D124" t="s">
+        <v>5</v>
+      </c>
+      <c r="E124" s="7">
+        <v>46174</v>
+      </c>
+      <c r="F124" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="G124" s="5"/>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>16</v>
+      </c>
+      <c r="B125" t="s">
+        <v>55</v>
+      </c>
+      <c r="C125" t="s">
+        <v>56</v>
+      </c>
+      <c r="D125" t="s">
+        <v>17</v>
+      </c>
+      <c r="E125" s="7">
+        <v>46174</v>
+      </c>
+      <c r="F125" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="G125" s="5"/>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>16</v>
+      </c>
+      <c r="B126" t="s">
+        <v>18</v>
+      </c>
+      <c r="C126" t="s">
+        <v>58</v>
+      </c>
+      <c r="D126" t="s">
+        <v>17</v>
+      </c>
+      <c r="E126" s="7">
+        <v>46174</v>
+      </c>
+      <c r="F126" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G126" s="5"/>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
         <v>21</v>
       </c>
-      <c r="B115" s="4" t="s">
+      <c r="B127" t="s">
         <v>22</v>
       </c>
-      <c r="C115" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D115" s="4" t="s">
+      <c r="C127" t="s">
+        <v>60</v>
+      </c>
+      <c r="D127" t="s">
         <v>23</v>
       </c>
-      <c r="E115" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F115" s="13" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A116" s="4" t="s">
+      <c r="E127" s="7">
+        <v>46174</v>
+      </c>
+      <c r="F127" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="G127" s="5"/>
+    </row>
+    <row r="128" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>158</v>
+      </c>
+      <c r="B128" t="s">
+        <v>55</v>
+      </c>
+      <c r="C128" t="s">
+        <v>159</v>
+      </c>
+      <c r="D128" t="s">
+        <v>160</v>
+      </c>
+      <c r="E128" s="7">
+        <v>46174</v>
+      </c>
+      <c r="F128" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G128" s="5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>158</v>
+      </c>
+      <c r="B129" t="s">
+        <v>55</v>
+      </c>
+      <c r="C129" t="s">
+        <v>161</v>
+      </c>
+      <c r="D129" t="s">
+        <v>160</v>
+      </c>
+      <c r="E129" s="7">
+        <v>46174</v>
+      </c>
+      <c r="F129" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G129" s="5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>158</v>
+      </c>
+      <c r="B130" t="s">
+        <v>55</v>
+      </c>
+      <c r="C130" t="s">
+        <v>162</v>
+      </c>
+      <c r="D130" t="s">
+        <v>160</v>
+      </c>
+      <c r="E130" s="7">
+        <v>46174</v>
+      </c>
+      <c r="F130" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="G130" s="5"/>
+    </row>
+    <row r="131" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
         <v>19</v>
       </c>
-      <c r="B116" s="4" t="s">
+      <c r="B131" t="s">
         <v>18</v>
       </c>
-      <c r="C116" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D116" s="4" t="s">
+      <c r="C131" t="s">
+        <v>59</v>
+      </c>
+      <c r="D131" t="s">
         <v>20</v>
       </c>
-      <c r="E116" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F116" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="G116" s="5" t="s">
+      <c r="E131" s="7">
+        <v>46174</v>
+      </c>
+      <c r="F131" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G131" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="117" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A117" s="4" t="s">
+    <row r="132" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
         <v>19</v>
       </c>
-      <c r="B117" s="4" t="s">
+      <c r="B132" t="s">
         <v>18</v>
       </c>
-      <c r="C117" s="4" t="s">
+      <c r="C132" t="s">
         <v>32</v>
       </c>
-      <c r="D117" s="4" t="s">
+      <c r="D132" t="s">
         <v>20</v>
       </c>
-      <c r="E117" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F117" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="G117" s="5" t="s">
+      <c r="E132" s="7">
+        <v>46174</v>
+      </c>
+      <c r="F132" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G132" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A118" s="4" t="s">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
         <v>11</v>
       </c>
-      <c r="B118" s="4" t="s">
+      <c r="B133" t="s">
         <v>10</v>
       </c>
-      <c r="C118" s="4" t="s">
+      <c r="C133" t="s">
         <v>14</v>
       </c>
-      <c r="D118" s="4" t="s">
+      <c r="D133" t="s">
         <v>15</v>
       </c>
-      <c r="E118" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F118" s="13" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A119" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B119" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C119" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D119" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E119" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F119" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A120" s="4" t="s">
+      <c r="E133" s="7">
+        <v>46174</v>
+      </c>
+      <c r="F133" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="G133" s="5"/>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
         <v>12</v>
       </c>
-      <c r="B120" s="4" t="s">
+      <c r="B134" t="s">
         <v>9</v>
       </c>
-      <c r="C120" s="4" t="s">
+      <c r="C134" t="s">
         <v>30</v>
       </c>
-      <c r="D120" s="4" t="s">
+      <c r="D134" t="s">
         <v>13</v>
       </c>
-      <c r="E120" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F120" s="14" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A121" s="4" t="s">
+      <c r="E134" s="7">
+        <v>46174</v>
+      </c>
+      <c r="F134" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="G134" s="5"/>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
         <v>12</v>
       </c>
-      <c r="B121" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C121" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D121" s="4" t="s">
+      <c r="B135" t="s">
+        <v>67</v>
+      </c>
+      <c r="C135" t="s">
+        <v>68</v>
+      </c>
+      <c r="D135" t="s">
         <v>13</v>
       </c>
-      <c r="E121" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F121" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="G121" s="5"/>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A122" s="4" t="s">
+      <c r="E135" s="7">
+        <v>46174</v>
+      </c>
+      <c r="F135" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G135" s="5"/>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
         <v>24</v>
       </c>
-      <c r="B122" s="4" t="s">
+      <c r="B136" t="s">
         <v>25</v>
       </c>
-      <c r="C122" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D122" s="4" t="s">
+      <c r="C136" t="s">
+        <v>62</v>
+      </c>
+      <c r="D136" t="s">
         <v>26</v>
       </c>
-      <c r="E122" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F122" s="13" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A123" s="4" t="s">
+      <c r="E136" s="7">
+        <v>46174</v>
+      </c>
+      <c r="F136" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="G136" s="5"/>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
         <v>24</v>
       </c>
-      <c r="B123" s="4" t="s">
+      <c r="B137" t="s">
         <v>25</v>
       </c>
-      <c r="C123" s="4" t="s">
+      <c r="C137" t="s">
         <v>27</v>
       </c>
-      <c r="D123" s="4" t="s">
+      <c r="D137" t="s">
         <v>26</v>
       </c>
-      <c r="E123" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F123" s="13" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A124" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B124" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C124" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D124" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E124" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F124" s="14" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A125" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B125" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C125" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D125" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E125" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F125" s="14" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A126" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B126" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C126" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D126" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E126" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F126" s="14" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A127" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B127" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C127" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D127" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E127" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F127" s="14" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A128" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B128" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C128" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D128" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E128" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F128" s="14" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A129" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B129" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C129" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D129" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E129" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F129" s="14" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A130" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B130" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C130" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D130" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E130" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F130" s="8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A131" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B131" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C131" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D131" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E131" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F131" s="14" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A132" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B132" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C132" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D132" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E132" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F132" s="14" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A133" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B133" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="C133" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D133" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E133" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F133" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G133" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A134" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B134" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C134" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D134" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E134" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F134" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G134" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A135" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B135" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C135" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="D135" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E135" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F135" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G135" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A136" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B136" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C136" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D136" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E136" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F136" s="14" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A137" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B137" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C137" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D137" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="E137" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F137" s="14" t="s">
-        <v>107</v>
-      </c>
+        <v>46174</v>
+      </c>
+      <c r="F137" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="G137" s="5"/>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" s="4" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E138" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F138" s="14" t="s">
-        <v>108</v>
-      </c>
+        <v>46172</v>
+      </c>
+      <c r="F138" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="G138" s="5"/>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" s="4" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>95</v>
+        <v>28</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E139" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F139" s="16" t="s">
-        <v>109</v>
+        <v>46172</v>
+      </c>
+      <c r="F139" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G139" s="5" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" s="4" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E140" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F140" s="14" t="s">
-        <v>110</v>
-      </c>
+        <v>46172</v>
+      </c>
+      <c r="F140" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="G140" s="6"/>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E141" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F141" s="14" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+        <v>46172</v>
+      </c>
+      <c r="F141" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="G141" s="5"/>
+    </row>
+    <row r="142" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A142" s="4" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E142" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F142" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="G142" s="5"/>
+        <v>46172</v>
+      </c>
+      <c r="F142" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G142" s="5" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" s="4" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E143" s="7">
-        <v>46168</v>
+        <v>46172</v>
       </c>
       <c r="F143" s="13" t="s">
-        <v>89</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="G143" s="5"/>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" s="4" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E144" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F144" s="16" t="s">
-        <v>87</v>
-      </c>
+        <v>46172</v>
+      </c>
+      <c r="F144" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="G144" s="5"/>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" s="4" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="E145" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F145" s="14" t="s">
-        <v>43</v>
+        <v>46172</v>
+      </c>
+      <c r="F145" s="13" t="s">
+        <v>143</v>
       </c>
       <c r="G145" s="5"/>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" s="4" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E146" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F146" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="G146" s="6"/>
+        <v>46171</v>
+      </c>
+      <c r="F146" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="G146" s="5"/>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" s="4" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E147" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F147" s="14" t="s">
-        <v>84</v>
-      </c>
+        <v>46171</v>
+      </c>
+      <c r="F147" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="G147" s="5"/>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" s="4" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E148" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F148" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="G148" s="6"/>
-    </row>
-    <row r="149" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>46171</v>
+      </c>
+      <c r="F148" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="G148" s="5"/>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" s="4" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E149" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F149" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G149" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>46171</v>
+      </c>
+      <c r="F149" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="G149" s="5"/>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" s="4" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E150" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F150" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G150" s="5" t="s">
-        <v>112</v>
-      </c>
+        <v>46171</v>
+      </c>
+      <c r="F150" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="G150" s="5"/>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" s="4" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E151" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F151" s="13" t="s">
-        <v>79</v>
+        <v>46171</v>
+      </c>
+      <c r="F151" s="14" t="s">
+        <v>134</v>
       </c>
       <c r="G151" s="5"/>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A152" s="4" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E152" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F152" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="G152" s="6"/>
+        <v>46171</v>
+      </c>
+      <c r="F152" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="G152" s="5" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C153" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D153" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E153" s="7">
+        <v>46171</v>
+      </c>
+      <c r="F153" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="G153" s="5"/>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A154" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B153" s="4" t="s">
+      <c r="B154" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C153" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D153" s="4" t="s">
+      <c r="C154" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D154" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E153" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F153" s="13" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A154" s="4" t="s">
+      <c r="E154" s="7">
+        <v>46171</v>
+      </c>
+      <c r="F154" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="G154" s="5"/>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A155" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B155" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C155" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D155" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E155" s="7">
+        <v>46171</v>
+      </c>
+      <c r="F155" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="G155" s="5"/>
+    </row>
+    <row r="156" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A156" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B154" s="4" t="s">
+      <c r="B156" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C156" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D156" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E156" s="7">
+        <v>46171</v>
+      </c>
+      <c r="F156" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="G156" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A157" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B157" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C154" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D154" s="4" t="s">
+      <c r="C157" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D157" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E154" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F154" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G154" s="5" t="s">
+      <c r="E157" s="7">
+        <v>46171</v>
+      </c>
+      <c r="F157" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="G157" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="155" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A155" s="4" t="s">
+    <row r="158" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A158" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B155" s="4" t="s">
+      <c r="B158" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C155" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D155" s="4" t="s">
+      <c r="C158" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D158" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E155" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F155" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G155" s="5" t="s">
+      <c r="E158" s="7">
+        <v>46171</v>
+      </c>
+      <c r="F158" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="G158" s="5" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A156" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B156" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C156" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D156" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E156" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F156" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="G156" s="5"/>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A157" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B157" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C157" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D157" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E157" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F157" s="13" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A158" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B158" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C158" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D158" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E158" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F158" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="G158" s="5"/>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E159" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F159" s="14" t="s">
-        <v>85</v>
-      </c>
+        <v>46171</v>
+      </c>
+      <c r="F159" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="G159" s="5"/>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" s="4" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="E160" s="7">
-        <v>46168</v>
+        <v>46171</v>
       </c>
       <c r="F160" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="G160" s="6"/>
+        <v>139</v>
+      </c>
+      <c r="G160" s="5"/>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" s="4" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E161" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F161" s="13" t="s">
-        <v>81</v>
-      </c>
+        <v>46171</v>
+      </c>
+      <c r="F161" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="G161" s="5"/>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162" s="4" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>7</v>
+        <v>67</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E162" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F162" s="9" t="s">
-        <v>72</v>
-      </c>
+        <v>46171</v>
+      </c>
+      <c r="F162" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="G162" s="5"/>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163" s="4" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="E163" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F163" s="9" t="s">
-        <v>74</v>
-      </c>
+        <v>46171</v>
+      </c>
+      <c r="F163" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="G163" s="5"/>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" s="4" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="E164" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F164" s="10" t="s">
-        <v>65</v>
-      </c>
+        <v>46171</v>
+      </c>
+      <c r="F164" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="G164" s="5"/>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" s="4" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E165" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F165" s="10" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>46170</v>
+      </c>
+      <c r="F165" s="13" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" s="4" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D166" s="12" t="s">
-        <v>17</v>
+        <v>48</v>
+      </c>
+      <c r="D166" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="E166" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F166" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G166" s="5" t="s">
-        <v>112</v>
-      </c>
+        <v>46170</v>
+      </c>
+      <c r="F166" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="G166" s="5"/>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" s="4" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E167" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F167" s="9" t="s">
-        <v>57</v>
+        <v>46170</v>
+      </c>
+      <c r="F167" s="16" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" s="4" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E168" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F168" s="8" t="s">
-        <v>53</v>
+        <v>46170</v>
+      </c>
+      <c r="F168" s="14" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" s="4" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="E169" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F169" s="9" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>46170</v>
+      </c>
+      <c r="F169" s="15" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" s="4" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E170" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F170" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G170" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>46170</v>
+      </c>
+      <c r="F170" s="14" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B171" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E171" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F171" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G171" s="5" t="s">
-        <v>31</v>
+        <v>46170</v>
+      </c>
+      <c r="F171" s="13" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" s="4" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E172" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F172" s="9" t="s">
-        <v>54</v>
+        <v>46170</v>
+      </c>
+      <c r="F172" s="15" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" s="4" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E173" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F173" s="10" t="s">
-        <v>69</v>
+        <v>46170</v>
+      </c>
+      <c r="F173" s="13" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" s="4" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E174" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F174" s="10" t="s">
-        <v>70</v>
+        <v>46170</v>
+      </c>
+      <c r="F174" s="13" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E175" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F175" s="9" t="s">
-        <v>63</v>
+        <v>46170</v>
+      </c>
+      <c r="F175" s="13" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B176" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C176" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D176" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E176" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F176" s="13" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A177" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B177" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C177" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D177" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E177" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F177" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="G177" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A178" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B178" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C178" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D178" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E178" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F178" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="G178" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A179" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B179" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C179" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D179" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E179" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F179" s="13" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A180" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B180" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C180" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D180" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E180" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F180" s="13" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A181" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B181" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C181" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D181" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E181" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F181" s="14" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A182" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B182" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C182" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D182" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E182" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F182" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="G182" s="5"/>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A183" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B176" s="4" t="s">
+      <c r="B183" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C176" s="4" t="s">
+      <c r="C183" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D183" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E183" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F183" s="13" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A184" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B184" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C184" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D176" s="4" t="s">
+      <c r="D184" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E176" s="7">
+      <c r="E184" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F184" s="13" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A185" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B185" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C185" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D185" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E185" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F185" s="14" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A186" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B186" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C186" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D186" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E186" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F186" s="14" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A187" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B187" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C187" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D187" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E187" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F187" s="14" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A188" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B188" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C188" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D188" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E188" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F188" s="14" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A189" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B189" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C189" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D189" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E189" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F189" s="14" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A190" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B190" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C190" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D190" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E190" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F190" s="14" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A191" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B191" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C191" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D191" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E191" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F191" s="8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A192" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B192" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C192" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D192" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E192" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F192" s="14" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A193" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B193" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C193" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D193" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E193" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F193" s="14" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A194" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B194" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C194" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D194" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E194" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F194" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G194" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A195" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B195" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C195" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D195" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E195" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F195" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G195" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A196" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B196" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C196" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D196" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E196" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F196" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G196" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A197" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B197" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C197" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D197" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E197" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F197" s="14" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A198" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B198" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C198" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D198" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E198" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F198" s="14" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A199" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B199" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C199" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D199" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E199" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F199" s="14" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A200" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B200" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C200" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D200" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E200" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F200" s="16" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A201" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B201" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C201" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D201" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E201" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F201" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A202" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B202" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C202" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D202" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E202" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F202" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A203" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B203" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C203" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D203" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E203" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F203" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="G203" s="5"/>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A204" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B204" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C204" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D204" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E204" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F204" s="13" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A205" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B205" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C205" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D205" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E205" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F205" s="16" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A206" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B206" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C206" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D206" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E206" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F206" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G206" s="5"/>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A207" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B207" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C207" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D207" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E207" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F207" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="G207" s="6"/>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A208" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B208" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C208" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D208" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E208" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F208" s="14" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A209" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B209" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C209" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D209" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E209" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F209" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="G209" s="6"/>
+    </row>
+    <row r="210" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A210" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B210" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C210" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D210" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E210" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F210" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G210" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A211" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B211" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C211" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D211" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E211" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F211" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G211" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A212" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B212" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C212" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D212" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E212" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F212" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="G212" s="5"/>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A213" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B213" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C213" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D213" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E213" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F213" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="G213" s="6"/>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A214" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B214" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C214" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D214" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E214" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F214" s="13" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A215" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B215" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C215" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D215" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E215" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F215" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G215" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A216" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B216" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C216" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D216" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E216" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F216" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="G216" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A217" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B217" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C217" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D217" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E217" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F217" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="G217" s="5"/>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A218" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B218" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C218" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D218" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E218" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F218" s="13" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A219" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B219" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C219" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D219" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E219" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F219" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="G219" s="5"/>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A220" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B220" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C220" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D220" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E220" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F220" s="14" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A221" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B221" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C221" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D221" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E221" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F221" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="G221" s="6"/>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A222" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B222" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C222" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D222" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E222" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F222" s="13" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A223" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B223" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C223" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D223" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E223" s="7">
         <v>46167</v>
       </c>
-      <c r="F176" s="9" t="s">
+      <c r="F223" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A224" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B224" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C224" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D224" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E224" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F224" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A225" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B225" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C225" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D225" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E225" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F225" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A226" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B226" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C226" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D226" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E226" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F226" s="10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A227" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B227" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C227" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D227" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E227" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F227" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G227" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A228" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B228" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C228" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D228" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E228" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F228" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A229" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B229" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C229" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D229" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E229" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F229" s="8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A230" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B230" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C230" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D230" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E230" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F230" s="9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A231" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B231" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C231" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D231" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E231" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F231" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G231" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A232" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B232" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C232" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D232" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E232" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F232" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G232" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A233" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B233" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C233" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D233" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E233" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F233" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A234" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B234" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C234" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D234" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E234" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F234" s="10" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A235" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B235" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C235" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D235" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E235" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F235" s="10" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A236" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B236" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C236" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D236" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E236" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F236" s="9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A237" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B237" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C237" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D237" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E237" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F237" s="9" t="s">
         <v>64</v>
       </c>
     </row>
@@ -5044,6 +6449,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6b3feda4-8a83-4113-98ac-b9b0c9bd9eab">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="6ca87d14-fc9d-4fcf-a42b-2754e6b3d00d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100AC3CF276C202334E979D7C4EA00D1CCA" ma:contentTypeVersion="13" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="fb5f1640dc82e33e0e3c6b4a833ae52f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6b3feda4-8a83-4113-98ac-b9b0c9bd9eab" xmlns:ns3="6ca87d14-fc9d-4fcf-a42b-2754e6b3d00d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dc11f865ff45eacf010d723a908863aa" ns2:_="" ns3:_="">
     <xsd:import namespace="6b3feda4-8a83-4113-98ac-b9b0c9bd9eab"/>
@@ -5250,17 +6666,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6b3feda4-8a83-4113-98ac-b9b0c9bd9eab">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="6ca87d14-fc9d-4fcf-a42b-2754e6b3d00d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6F72255-F15E-4B46-A16C-2F18C675CB37}">
   <ds:schemaRefs>
@@ -5270,6 +6675,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFC5C71E-79D6-437C-A06A-B0BD52E89317}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6b3feda4-8a83-4113-98ac-b9b0c9bd9eab"/>
+    <ds:schemaRef ds:uri="6ca87d14-fc9d-4fcf-a42b-2754e6b3d00d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E295317-F47C-4C92-88FC-9DAD72755AAC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5286,15 +6702,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFC5C71E-79D6-437C-A06A-B0BD52E89317}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6b3feda4-8a83-4113-98ac-b9b0c9bd9eab"/>
-    <ds:schemaRef ds:uri="6ca87d14-fc9d-4fcf-a42b-2754e6b3d00d"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/EFETIVIDADE.xlsx
+++ b/EFETIVIDADE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://spotpromo.sharepoint.com/sites/bko.pribeiro/Documentos Compartilhados/PRibeiro/BAUDUCCO TMP/20 - EFETIVIDADE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="959" documentId="13_ncr:1_{C64068DB-D04A-49E7-B037-1281E1EE8D6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98823DDE-43DD-46DA-837B-F1A26390B859}"/>
+  <xr:revisionPtr revIDLastSave="987" documentId="13_ncr:1_{C64068DB-D04A-49E7-B037-1281E1EE8D6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CBA4CB14-EFF3-4BD3-8808-958E7799F316}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1332" uniqueCount="286">
   <si>
     <t>ROTA</t>
   </si>
@@ -674,15 +674,9 @@
     <t>BH - AV SEVERINO BALLESTEROS RODRIGUE 65, 65 - CONTAGEM/MG</t>
   </si>
   <si>
-    <t>07:06</t>
-  </si>
-  <si>
     <t>07:18</t>
   </si>
   <si>
-    <t>07:29</t>
-  </si>
-  <si>
     <t>06:58  10:59</t>
   </si>
   <si>
@@ -803,16 +797,100 @@
     <t>10:02  11:36</t>
   </si>
   <si>
-    <t>07:36</t>
-  </si>
-  <si>
-    <t>07:53</t>
-  </si>
-  <si>
-    <t>07:59</t>
-  </si>
-  <si>
-    <t>08:03</t>
+    <t>07:06  11:58</t>
+  </si>
+  <si>
+    <t>07:36  17:13</t>
+  </si>
+  <si>
+    <t>07:53  17:25</t>
+  </si>
+  <si>
+    <t>07:59  12:18</t>
+  </si>
+  <si>
+    <t>08:03  12:36</t>
+  </si>
+  <si>
+    <t>09:55  09:56</t>
+  </si>
+  <si>
+    <t>11:22</t>
+  </si>
+  <si>
+    <t>12:59  17:29</t>
+  </si>
+  <si>
+    <t>13:20  16:27</t>
+  </si>
+  <si>
+    <t>14:02  16:08</t>
+  </si>
+  <si>
+    <t>17:33  18:48</t>
+  </si>
+  <si>
+    <t>17:38</t>
+  </si>
+  <si>
+    <t>06:53  11:18</t>
+  </si>
+  <si>
+    <t>07:31  15:18</t>
+  </si>
+  <si>
+    <t>07:49  13:39</t>
+  </si>
+  <si>
+    <t>07:56  17:19</t>
+  </si>
+  <si>
+    <t>08:10  09:22</t>
+  </si>
+  <si>
+    <t>09:28  12:48</t>
+  </si>
+  <si>
+    <t>09:36  12:01</t>
+  </si>
+  <si>
+    <t>11:19  14:51</t>
+  </si>
+  <si>
+    <t>12:49  15:49</t>
+  </si>
+  <si>
+    <t>13:49</t>
+  </si>
+  <si>
+    <t>13:53  18:02</t>
+  </si>
+  <si>
+    <t>14:58  16:12</t>
+  </si>
+  <si>
+    <t>15:19  15:19</t>
+  </si>
+  <si>
+    <t>15:20  15:21</t>
+  </si>
+  <si>
+    <t>15:57  17:21</t>
+  </si>
+  <si>
+    <t>18:15</t>
+  </si>
+  <si>
+    <t>06:48</t>
+  </si>
+  <si>
+    <t>07:28</t>
+  </si>
+  <si>
+    <t>07:33</t>
+  </si>
+  <si>
+    <t>08:02</t>
   </si>
 </sst>
 </file>
@@ -925,7 +1003,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -957,9 +1035,6 @@
     <xf numFmtId="14" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -975,32 +1050,32 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1102,10 +1177,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A4474625-D582-4F1B-AA27-C9E6E4248EEA}" name="Tabela1" displayName="Tabela1" ref="A1:G237" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7" headerRowCellStyle="Normal 2">
-  <autoFilter ref="A1:G237" xr:uid="{A4474625-D582-4F1B-AA27-C9E6E4248EEA}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G237">
-    <sortCondition descending="1" ref="E1:E237"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A4474625-D582-4F1B-AA27-C9E6E4248EEA}" name="Tabela1" displayName="Tabela1" ref="A1:G261" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7" headerRowCellStyle="Normal 2">
+  <autoFilter ref="A1:G261" xr:uid="{A4474625-D582-4F1B-AA27-C9E6E4248EEA}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G261">
+    <sortCondition descending="1" ref="E1:E261"/>
   </sortState>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{8C18829A-5E6C-4A32-820C-446F688CFF40}" name="ROTA" dataDxfId="6"/>
@@ -1437,7 +1512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G237"/>
+  <dimension ref="A1:G261"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" style="4" customWidth="1"/>
@@ -1481,16 +1556,16 @@
         <v>7</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="7">
-        <v>46181</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>258</v>
+        <v>46183</v>
+      </c>
+      <c r="F2" s="23" t="s">
+        <v>283</v>
       </c>
       <c r="G2" s="5"/>
     </row>
@@ -1502,41 +1577,41 @@
         <v>7</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>53</v>
       </c>
       <c r="G3" s="5"/>
     </row>
-    <row r="4" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>153</v>
+        <v>6</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>154</v>
+        <v>7</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>155</v>
+        <v>71</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>156</v>
+        <v>8</v>
       </c>
       <c r="E4" s="7">
-        <v>46181</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>213</v>
+        <v>46183</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G4" s="5"/>
     </row>
-    <row r="5" spans="1:7" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>153</v>
       </c>
@@ -1544,13 +1619,13 @@
         <v>154</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>157</v>
+        <v>186</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>156</v>
       </c>
       <c r="E5" s="7">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>53</v>
@@ -1559,61 +1634,61 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="E6" s="7">
+        <v>46183</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G6" s="5"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C7" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D7" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="E6" s="7">
-        <v>46181</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>256</v>
-      </c>
-      <c r="G6" s="5"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="22" t="s">
-        <v>149</v>
-      </c>
-      <c r="B7" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="22" t="s">
-        <v>152</v>
-      </c>
-      <c r="D7" s="22" t="s">
-        <v>151</v>
-      </c>
       <c r="E7" s="7">
-        <v>46181</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G7" s="23"/>
+        <v>46183</v>
+      </c>
+      <c r="F7" s="23" t="s">
+        <v>284</v>
+      </c>
+      <c r="G7" s="5"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>3</v>
+        <v>149</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>28</v>
+        <v>187</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>5</v>
+        <v>151</v>
       </c>
       <c r="E8" s="7">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>53</v>
@@ -1622,19 +1697,19 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>3</v>
+        <v>149</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>29</v>
+        <v>212</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>5</v>
+        <v>151</v>
       </c>
       <c r="E9" s="7">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>53</v>
@@ -1643,40 +1718,40 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E10" s="7">
-        <v>46181</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>53</v>
+        <v>46183</v>
+      </c>
+      <c r="F10" s="23" t="s">
+        <v>282</v>
       </c>
       <c r="G10" s="5"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E11" s="7">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>53</v>
@@ -1685,22 +1760,22 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>21</v>
+        <v>158</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>60</v>
+        <v>162</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>23</v>
+        <v>160</v>
       </c>
       <c r="E12" s="7">
-        <v>46181</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>53</v>
+        <v>46183</v>
+      </c>
+      <c r="F12" s="23" t="s">
+        <v>285</v>
       </c>
       <c r="G12" s="5"/>
     </row>
@@ -1718,10 +1793,10 @@
         <v>160</v>
       </c>
       <c r="E13" s="7">
-        <v>46181</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>259</v>
+        <v>46183</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G13" s="5"/>
     </row>
@@ -1733,13 +1808,13 @@
         <v>55</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>160</v>
       </c>
       <c r="E14" s="7">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>53</v>
@@ -1748,234 +1823,234 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>158</v>
+        <v>12</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>161</v>
+        <v>30</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>160</v>
+        <v>13</v>
       </c>
       <c r="E15" s="7">
-        <v>46181</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>53</v>
+        <v>46183</v>
+      </c>
+      <c r="F15" s="23" t="s">
+        <v>248</v>
       </c>
       <c r="G15" s="5"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>20</v>
+      <c r="A16" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>13</v>
       </c>
       <c r="E16" s="7">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="G16" s="5"/>
+      <c r="G16" s="20"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E17" s="7">
-        <v>46181</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>53</v>
+        <v>46182</v>
+      </c>
+      <c r="F17" s="22" t="s">
+        <v>270</v>
       </c>
       <c r="G17" s="5"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E18" s="7">
-        <v>46181</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>215</v>
+        <v>46182</v>
+      </c>
+      <c r="F18" s="22" t="s">
+        <v>272</v>
       </c>
       <c r="G18" s="5"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E19" s="7">
-        <v>46181</v>
-      </c>
-      <c r="F19" s="11" t="s">
-        <v>257</v>
+        <v>46182</v>
+      </c>
+      <c r="F19" s="23" t="s">
+        <v>275</v>
       </c>
       <c r="G19" s="5"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>12</v>
+        <v>153</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>67</v>
+        <v>154</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>68</v>
+        <v>180</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>13</v>
+        <v>156</v>
       </c>
       <c r="E20" s="7">
-        <v>46181</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>53</v>
+        <v>46182</v>
+      </c>
+      <c r="F20" s="22" t="s">
+        <v>266</v>
       </c>
       <c r="G20" s="5"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>24</v>
+        <v>153</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>25</v>
+        <v>154</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>27</v>
+        <v>186</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>26</v>
+        <v>156</v>
       </c>
       <c r="E21" s="7">
-        <v>46181</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>53</v>
+        <v>46182</v>
+      </c>
+      <c r="F21" s="22" t="s">
+        <v>273</v>
       </c>
       <c r="G21" s="5"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>24</v>
+        <v>153</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>25</v>
+        <v>154</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>62</v>
+        <v>185</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>26</v>
+        <v>156</v>
       </c>
       <c r="E22" s="7">
-        <v>46181</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>53</v>
+        <v>46182</v>
+      </c>
+      <c r="F22" s="22" t="s">
+        <v>277</v>
       </c>
       <c r="G22" s="5"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="D23" s="22" t="s">
-        <v>8</v>
+      <c r="A23" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>151</v>
       </c>
       <c r="E23" s="7">
-        <v>46179</v>
-      </c>
-      <c r="F23" s="21" t="s">
-        <v>255</v>
-      </c>
-      <c r="G23" s="23"/>
+        <v>46182</v>
+      </c>
+      <c r="F23" s="22" t="s">
+        <v>268</v>
+      </c>
+      <c r="G23" s="5"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>154</v>
+        <v>10</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E24" s="7">
-        <v>46179</v>
-      </c>
-      <c r="F24" s="21" t="s">
-        <v>250</v>
+        <v>46182</v>
+      </c>
+      <c r="F24" s="22" t="s">
+        <v>276</v>
       </c>
       <c r="G24" s="5"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="18" t="s">
         <v>151</v>
       </c>
       <c r="E25" s="7">
-        <v>46179</v>
-      </c>
-      <c r="F25" s="21" t="s">
-        <v>254</v>
-      </c>
-      <c r="G25" s="5"/>
+        <v>46182</v>
+      </c>
+      <c r="F25" s="23" t="s">
+        <v>281</v>
+      </c>
+      <c r="G25" s="20"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
@@ -1985,58 +2060,58 @@
         <v>4</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>5</v>
       </c>
       <c r="E26" s="7">
-        <v>46179</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>53</v>
+        <v>46182</v>
+      </c>
+      <c r="F26" s="22" t="s">
+        <v>267</v>
       </c>
       <c r="G26" s="5"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E27" s="7">
-        <v>46179</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>53</v>
+        <v>46182</v>
+      </c>
+      <c r="F27" s="22" t="s">
+        <v>278</v>
       </c>
       <c r="G27" s="5"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="E28" s="7">
-        <v>46179</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>53</v>
+        <v>46182</v>
+      </c>
+      <c r="F28" s="22" t="s">
+        <v>279</v>
       </c>
       <c r="G28" s="5"/>
     </row>
@@ -2048,58 +2123,58 @@
         <v>55</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>160</v>
       </c>
       <c r="E29" s="7">
-        <v>46179</v>
-      </c>
-      <c r="F29" s="21" t="s">
-        <v>253</v>
+        <v>46182</v>
+      </c>
+      <c r="F29" s="22" t="s">
+        <v>271</v>
       </c>
       <c r="G29" s="5"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>19</v>
+        <v>158</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>32</v>
+        <v>183</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>20</v>
+        <v>160</v>
       </c>
       <c r="E30" s="7">
-        <v>46179</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>53</v>
+        <v>46182</v>
+      </c>
+      <c r="F30" s="22" t="s">
+        <v>274</v>
       </c>
       <c r="G30" s="5"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>11</v>
+        <v>158</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>33</v>
+        <v>181</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>15</v>
+        <v>160</v>
       </c>
       <c r="E31" s="7">
-        <v>46179</v>
-      </c>
-      <c r="F31" s="21" t="s">
-        <v>252</v>
+        <v>46182</v>
+      </c>
+      <c r="F31" s="22" t="s">
+        <v>280</v>
       </c>
       <c r="G31" s="5"/>
     </row>
@@ -2111,34 +2186,34 @@
         <v>9</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>95</v>
+        <v>30</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E32" s="7">
-        <v>46179</v>
+        <v>46182</v>
       </c>
       <c r="F32" s="21" t="s">
-        <v>251</v>
+        <v>269</v>
       </c>
       <c r="G32" s="5"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E33" s="7">
-        <v>46179</v>
+        <v>46182</v>
       </c>
       <c r="F33" s="8" t="s">
         <v>53</v>
@@ -2153,16 +2228,16 @@
         <v>7</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E34" s="7">
-        <v>46178</v>
-      </c>
-      <c r="F34" s="17" t="s">
-        <v>240</v>
+        <v>46181</v>
+      </c>
+      <c r="F34" s="22" t="s">
+        <v>257</v>
       </c>
       <c r="G34" s="5"/>
     </row>
@@ -2174,37 +2249,37 @@
         <v>7</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E35" s="7">
-        <v>46178</v>
-      </c>
-      <c r="F35" s="17" t="s">
-        <v>241</v>
+        <v>46181</v>
+      </c>
+      <c r="F35" s="22" t="s">
+        <v>263</v>
       </c>
       <c r="G35" s="5"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>6</v>
+        <v>153</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>7</v>
+        <v>154</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>71</v>
+        <v>155</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>8</v>
+        <v>156</v>
       </c>
       <c r="E36" s="7">
-        <v>46178</v>
-      </c>
-      <c r="F36" s="11" t="s">
-        <v>246</v>
+        <v>46181</v>
+      </c>
+      <c r="F36" s="21" t="s">
+        <v>254</v>
       </c>
       <c r="G36" s="5"/>
     </row>
@@ -2216,286 +2291,286 @@
         <v>154</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>156</v>
       </c>
       <c r="E37" s="7">
-        <v>46178</v>
-      </c>
-      <c r="F37" s="17" t="s">
-        <v>235</v>
+        <v>46181</v>
+      </c>
+      <c r="F37" s="21" t="s">
+        <v>262</v>
       </c>
       <c r="G37" s="5"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>154</v>
+        <v>10</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>186</v>
+        <v>150</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E38" s="7">
-        <v>46178</v>
-      </c>
-      <c r="F38" s="17" t="s">
-        <v>244</v>
+        <v>46181</v>
+      </c>
+      <c r="F38" s="22" t="s">
+        <v>255</v>
       </c>
       <c r="G38" s="5"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>154</v>
+        <v>10</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E39" s="7">
-        <v>46178</v>
-      </c>
-      <c r="F39" s="17" t="s">
-        <v>247</v>
+        <v>46181</v>
+      </c>
+      <c r="F39" s="22" t="s">
+        <v>264</v>
       </c>
       <c r="G39" s="5"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>149</v>
+        <v>3</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>150</v>
+        <v>29</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>151</v>
+        <v>5</v>
       </c>
       <c r="E40" s="7">
-        <v>46178</v>
-      </c>
-      <c r="F40" s="17" t="s">
-        <v>236</v>
+        <v>46181</v>
+      </c>
+      <c r="F40" s="22" t="s">
+        <v>259</v>
       </c>
       <c r="G40" s="5"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
-        <v>149</v>
+        <v>3</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>184</v>
+        <v>28</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>151</v>
+        <v>5</v>
       </c>
       <c r="E41" s="7">
-        <v>46178</v>
-      </c>
-      <c r="F41" s="17" t="s">
-        <v>242</v>
+        <v>46181</v>
+      </c>
+      <c r="F41" s="23" t="s">
+        <v>260</v>
       </c>
       <c r="G41" s="5"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>212</v>
+        <v>159</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="E42" s="7">
-        <v>46178</v>
-      </c>
-      <c r="F42" s="17" t="s">
-        <v>245</v>
+        <v>46181</v>
+      </c>
+      <c r="F42" s="22" t="s">
+        <v>258</v>
       </c>
       <c r="G42" s="5"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>55</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>187</v>
+        <v>161</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="E43" s="7">
-        <v>46178</v>
-      </c>
-      <c r="F43" s="17" t="s">
-        <v>248</v>
+        <v>46181</v>
+      </c>
+      <c r="F43" s="22" t="s">
+        <v>261</v>
       </c>
       <c r="G43" s="5"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>5</v>
+      <c r="A44" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="B44" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C44" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="D44" s="18" t="s">
+        <v>160</v>
       </c>
       <c r="E44" s="7">
-        <v>46178</v>
-      </c>
-      <c r="F44" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G44" s="5"/>
+        <v>46181</v>
+      </c>
+      <c r="F44" s="23" t="s">
+        <v>265</v>
+      </c>
+      <c r="G44" s="20"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E45" s="7">
-        <v>46178</v>
-      </c>
-      <c r="F45" s="8" t="s">
-        <v>53</v>
+        <v>46181</v>
+      </c>
+      <c r="F45" s="21" t="s">
+        <v>256</v>
       </c>
       <c r="G45" s="5"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E46" s="7">
-        <v>46178</v>
-      </c>
-      <c r="F46" s="17" t="s">
-        <v>239</v>
+        <v>46181</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G46" s="5"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E47" s="7">
-        <v>46178</v>
-      </c>
-      <c r="F47" s="8" t="s">
-        <v>53</v>
+        <v>46179</v>
+      </c>
+      <c r="F47" s="16" t="s">
+        <v>253</v>
       </c>
       <c r="G47" s="5"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
-        <v>16</v>
+        <v>153</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>18</v>
+        <v>154</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>34</v>
+        <v>186</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>17</v>
+        <v>156</v>
       </c>
       <c r="E48" s="7">
-        <v>46178</v>
-      </c>
-      <c r="F48" s="17" t="s">
-        <v>243</v>
+        <v>46179</v>
+      </c>
+      <c r="F48" s="16" t="s">
+        <v>248</v>
       </c>
       <c r="G48" s="5"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
-        <v>21</v>
+        <v>149</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>60</v>
+        <v>187</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>23</v>
+        <v>151</v>
       </c>
       <c r="E49" s="7">
-        <v>46178</v>
-      </c>
-      <c r="F49" s="8" t="s">
-        <v>53</v>
+        <v>46179</v>
+      </c>
+      <c r="F49" s="16" t="s">
+        <v>252</v>
       </c>
       <c r="G49" s="5"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>94</v>
+        <v>28</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="E50" s="7">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="F50" s="8" t="s">
         <v>53</v>
@@ -2504,40 +2579,40 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
-        <v>158</v>
+        <v>16</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>162</v>
+        <v>34</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>160</v>
+        <v>17</v>
       </c>
       <c r="E51" s="7">
-        <v>46178</v>
-      </c>
-      <c r="F51" s="17" t="s">
-        <v>237</v>
+        <v>46179</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G51" s="5"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
-        <v>158</v>
+        <v>21</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>161</v>
+        <v>38</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>160</v>
+        <v>23</v>
       </c>
       <c r="E52" s="7">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>53</v>
@@ -2545,41 +2620,41 @@
       <c r="G52" s="5"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53" s="22" t="s">
+      <c r="A53" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="B53" s="22" t="s">
+      <c r="B53" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C53" s="22" t="s">
-        <v>159</v>
-      </c>
-      <c r="D53" s="22" t="s">
+      <c r="C53" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D53" s="4" t="s">
         <v>160</v>
       </c>
       <c r="E53" s="7">
-        <v>46178</v>
-      </c>
-      <c r="F53" s="24">
-        <v>0.34930555555555554</v>
-      </c>
-      <c r="G53" s="23"/>
+        <v>46179</v>
+      </c>
+      <c r="F53" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="G53" s="5"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
         <v>19</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>91</v>
+        <v>18</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>92</v>
+        <v>32</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E54" s="7">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="F54" s="8" t="s">
         <v>53</v>
@@ -2588,61 +2663,61 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E55" s="7">
-        <v>46178</v>
-      </c>
-      <c r="F55" s="8" t="s">
-        <v>53</v>
+        <v>46179</v>
+      </c>
+      <c r="F55" s="16" t="s">
+        <v>250</v>
       </c>
       <c r="G55" s="5"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E56" s="7">
-        <v>46178</v>
-      </c>
-      <c r="F56" s="8" t="s">
-        <v>53</v>
+        <v>46179</v>
+      </c>
+      <c r="F56" s="16" t="s">
+        <v>249</v>
       </c>
       <c r="G56" s="5"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E57" s="7">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="F57" s="8" t="s">
         <v>53</v>
@@ -2651,660 +2726,652 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>90</v>
+        <v>47</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E58" s="7">
         <v>46178</v>
       </c>
-      <c r="F58" s="8" t="s">
-        <v>53</v>
+      <c r="F58" s="12" t="s">
+        <v>238</v>
       </c>
       <c r="G58" s="5"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E59" s="7">
         <v>46178</v>
       </c>
-      <c r="F59" s="18" t="s">
-        <v>238</v>
+      <c r="F59" s="12" t="s">
+        <v>239</v>
       </c>
       <c r="G59" s="5"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>67</v>
+        <v>7</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E60" s="7">
         <v>46178</v>
       </c>
-      <c r="F60" s="18" t="s">
-        <v>249</v>
+      <c r="F60" s="15" t="s">
+        <v>244</v>
       </c>
       <c r="G60" s="5"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
-        <v>24</v>
+        <v>153</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>25</v>
+        <v>154</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>27</v>
+        <v>155</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>26</v>
+        <v>156</v>
       </c>
       <c r="E61" s="7">
         <v>46178</v>
       </c>
-      <c r="F61" s="8" t="s">
-        <v>53</v>
+      <c r="F61" s="12" t="s">
+        <v>233</v>
       </c>
       <c r="G61" s="5"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
-        <v>24</v>
+        <v>153</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>25</v>
+        <v>154</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>62</v>
+        <v>186</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>26</v>
+        <v>156</v>
       </c>
       <c r="E62" s="7">
         <v>46178</v>
       </c>
-      <c r="F62" s="8" t="s">
+      <c r="F62" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="G62" s="5"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A63" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="E63" s="7">
+        <v>46178</v>
+      </c>
+      <c r="F63" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="G63" s="5"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A64" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="E64" s="7">
+        <v>46178</v>
+      </c>
+      <c r="F64" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="G64" s="5"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A65" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="E65" s="7">
+        <v>46178</v>
+      </c>
+      <c r="F65" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="G65" s="5"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A66" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="E66" s="7">
+        <v>46178</v>
+      </c>
+      <c r="F66" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="G66" s="5"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A67" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="E67" s="7">
+        <v>46178</v>
+      </c>
+      <c r="F67" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="G67" s="5"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A68" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E68" s="7">
+        <v>46178</v>
+      </c>
+      <c r="F68" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="G62" s="5"/>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
+      <c r="G68" s="5"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A69" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E69" s="7">
+        <v>46178</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G69" s="5"/>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A70" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E70" s="7">
+        <v>46178</v>
+      </c>
+      <c r="F70" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="G70" s="5"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A71" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E71" s="7">
+        <v>46178</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G71" s="5"/>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A72" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E72" s="7">
+        <v>46178</v>
+      </c>
+      <c r="F72" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="G72" s="5"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A73" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E73" s="7">
+        <v>46178</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G73" s="5"/>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A74" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E74" s="7">
+        <v>46178</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G74" s="5"/>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A75" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E75" s="7">
+        <v>46178</v>
+      </c>
+      <c r="F75" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="G75" s="5"/>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A76" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E76" s="7">
+        <v>46178</v>
+      </c>
+      <c r="F76" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G76" s="5"/>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A77" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E77" s="7">
+        <v>46178</v>
+      </c>
+      <c r="F77" s="17">
+        <v>0.34930555555555554</v>
+      </c>
+      <c r="G77" s="5"/>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A78" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E78" s="7">
+        <v>46178</v>
+      </c>
+      <c r="F78" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G78" s="5"/>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A79" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E79" s="7">
+        <v>46178</v>
+      </c>
+      <c r="F79" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G79" s="5"/>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A80" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E80" s="7">
+        <v>46178</v>
+      </c>
+      <c r="F80" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G80" s="5"/>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A81" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E81" s="7">
+        <v>46178</v>
+      </c>
+      <c r="F81" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G81" s="5"/>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A82" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E82" s="7">
+        <v>46178</v>
+      </c>
+      <c r="F82" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G82" s="5"/>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A83" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E83" s="7">
+        <v>46178</v>
+      </c>
+      <c r="F83" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="G83" s="5"/>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A84" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E84" s="7">
+        <v>46178</v>
+      </c>
+      <c r="F84" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="G84" s="5"/>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A85" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E85" s="7">
+        <v>46178</v>
+      </c>
+      <c r="F85" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G85" s="5"/>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A86" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E86" s="7">
+        <v>46178</v>
+      </c>
+      <c r="F86" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G86" s="5"/>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A87" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B87" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C87" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D87" s="4" t="s">
         <v>8</v>
-      </c>
-      <c r="E63" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F63" s="17" t="s">
-        <v>221</v>
-      </c>
-      <c r="G63" s="5"/>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>6</v>
-      </c>
-      <c r="B64" t="s">
-        <v>7</v>
-      </c>
-      <c r="C64" t="s">
-        <v>73</v>
-      </c>
-      <c r="D64" t="s">
-        <v>8</v>
-      </c>
-      <c r="E64" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F64" s="17" t="s">
-        <v>224</v>
-      </c>
-      <c r="G64" s="5"/>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>6</v>
-      </c>
-      <c r="B65" t="s">
-        <v>7</v>
-      </c>
-      <c r="C65" t="s">
-        <v>71</v>
-      </c>
-      <c r="D65" t="s">
-        <v>8</v>
-      </c>
-      <c r="E65" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F65" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="G65" s="5"/>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>153</v>
-      </c>
-      <c r="B66" t="s">
-        <v>154</v>
-      </c>
-      <c r="C66" t="s">
-        <v>155</v>
-      </c>
-      <c r="D66" t="s">
-        <v>156</v>
-      </c>
-      <c r="E66" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F66" s="17" t="s">
-        <v>219</v>
-      </c>
-      <c r="G66" s="5"/>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
-        <v>153</v>
-      </c>
-      <c r="B67" t="s">
-        <v>154</v>
-      </c>
-      <c r="C67" t="s">
-        <v>186</v>
-      </c>
-      <c r="D67" t="s">
-        <v>156</v>
-      </c>
-      <c r="E67" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F67" s="17" t="s">
-        <v>230</v>
-      </c>
-      <c r="G67" s="5"/>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
-        <v>149</v>
-      </c>
-      <c r="B68" t="s">
-        <v>10</v>
-      </c>
-      <c r="C68" t="s">
-        <v>150</v>
-      </c>
-      <c r="D68" t="s">
-        <v>151</v>
-      </c>
-      <c r="E68" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F68" s="17" t="s">
-        <v>220</v>
-      </c>
-      <c r="G68" s="5"/>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>149</v>
-      </c>
-      <c r="B69" t="s">
-        <v>55</v>
-      </c>
-      <c r="C69" t="s">
-        <v>187</v>
-      </c>
-      <c r="D69" t="s">
-        <v>151</v>
-      </c>
-      <c r="E69" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F69" s="17" t="s">
-        <v>225</v>
-      </c>
-      <c r="G69" s="5"/>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
-        <v>149</v>
-      </c>
-      <c r="B70" t="s">
-        <v>10</v>
-      </c>
-      <c r="C70" t="s">
-        <v>212</v>
-      </c>
-      <c r="D70" t="s">
-        <v>151</v>
-      </c>
-      <c r="E70" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F70" s="17" t="s">
-        <v>231</v>
-      </c>
-      <c r="G70" s="5"/>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>3</v>
-      </c>
-      <c r="B71" t="s">
-        <v>4</v>
-      </c>
-      <c r="C71" t="s">
-        <v>29</v>
-      </c>
-      <c r="D71" t="s">
-        <v>5</v>
-      </c>
-      <c r="E71" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F71" s="18" t="s">
-        <v>218</v>
-      </c>
-      <c r="G71" s="5"/>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>3</v>
-      </c>
-      <c r="B72" t="s">
-        <v>4</v>
-      </c>
-      <c r="C72" t="s">
-        <v>28</v>
-      </c>
-      <c r="D72" t="s">
-        <v>5</v>
-      </c>
-      <c r="E72" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F72" s="18" t="s">
-        <v>226</v>
-      </c>
-      <c r="G72" s="5"/>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>16</v>
-      </c>
-      <c r="B73" t="s">
-        <v>18</v>
-      </c>
-      <c r="C73" t="s">
-        <v>58</v>
-      </c>
-      <c r="D73" t="s">
-        <v>17</v>
-      </c>
-      <c r="E73" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F73" s="18" t="s">
-        <v>223</v>
-      </c>
-      <c r="G73" s="5"/>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
-        <v>16</v>
-      </c>
-      <c r="B74" t="s">
-        <v>55</v>
-      </c>
-      <c r="C74" t="s">
-        <v>56</v>
-      </c>
-      <c r="D74" t="s">
-        <v>17</v>
-      </c>
-      <c r="E74" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F74" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="G74" s="5"/>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>21</v>
-      </c>
-      <c r="B75" t="s">
-        <v>22</v>
-      </c>
-      <c r="C75" t="s">
-        <v>60</v>
-      </c>
-      <c r="D75" t="s">
-        <v>23</v>
-      </c>
-      <c r="E75" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F75" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="G75" s="5"/>
-    </row>
-    <row r="76" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
-        <v>21</v>
-      </c>
-      <c r="B76" t="s">
-        <v>22</v>
-      </c>
-      <c r="C76" t="s">
-        <v>94</v>
-      </c>
-      <c r="D76" t="s">
-        <v>23</v>
-      </c>
-      <c r="E76" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F76" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="G76" s="5" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
-        <v>158</v>
-      </c>
-      <c r="B77" t="s">
-        <v>55</v>
-      </c>
-      <c r="C77" t="s">
-        <v>159</v>
-      </c>
-      <c r="D77" t="s">
-        <v>160</v>
-      </c>
-      <c r="E77" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F77" s="17" t="s">
-        <v>227</v>
-      </c>
-      <c r="G77" s="5"/>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
-        <v>158</v>
-      </c>
-      <c r="B78" t="s">
-        <v>55</v>
-      </c>
-      <c r="C78" t="s">
-        <v>161</v>
-      </c>
-      <c r="D78" t="s">
-        <v>160</v>
-      </c>
-      <c r="E78" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F78" s="17" t="s">
-        <v>233</v>
-      </c>
-      <c r="G78" s="5"/>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
-        <v>158</v>
-      </c>
-      <c r="B79" t="s">
-        <v>55</v>
-      </c>
-      <c r="C79" t="s">
-        <v>162</v>
-      </c>
-      <c r="D79" t="s">
-        <v>160</v>
-      </c>
-      <c r="E79" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F79" s="11" t="s">
-        <v>234</v>
-      </c>
-      <c r="G79" s="5"/>
-    </row>
-    <row r="80" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
-        <v>19</v>
-      </c>
-      <c r="B80" t="s">
-        <v>91</v>
-      </c>
-      <c r="C80" t="s">
-        <v>92</v>
-      </c>
-      <c r="D80" t="s">
-        <v>20</v>
-      </c>
-      <c r="E80" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F80" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="G80" s="5" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
-        <v>19</v>
-      </c>
-      <c r="B81" t="s">
-        <v>18</v>
-      </c>
-      <c r="C81" t="s">
-        <v>59</v>
-      </c>
-      <c r="D81" t="s">
-        <v>20</v>
-      </c>
-      <c r="E81" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F81" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="G81" s="5" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
-        <v>19</v>
-      </c>
-      <c r="B82" t="s">
-        <v>18</v>
-      </c>
-      <c r="C82" t="s">
-        <v>93</v>
-      </c>
-      <c r="D82" t="s">
-        <v>20</v>
-      </c>
-      <c r="E82" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F82" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="G82" s="5" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
-        <v>11</v>
-      </c>
-      <c r="B83" t="s">
-        <v>10</v>
-      </c>
-      <c r="C83" t="s">
-        <v>14</v>
-      </c>
-      <c r="D83" t="s">
-        <v>15</v>
-      </c>
-      <c r="E83" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F83" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="G83" s="5"/>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
-        <v>11</v>
-      </c>
-      <c r="B84" t="s">
-        <v>10</v>
-      </c>
-      <c r="C84" t="s">
-        <v>90</v>
-      </c>
-      <c r="D84" t="s">
-        <v>15</v>
-      </c>
-      <c r="E84" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F84" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="G84" s="5"/>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
-        <v>12</v>
-      </c>
-      <c r="B85" t="s">
-        <v>9</v>
-      </c>
-      <c r="C85" t="s">
-        <v>30</v>
-      </c>
-      <c r="D85" t="s">
-        <v>13</v>
-      </c>
-      <c r="E85" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F85" s="18" t="s">
-        <v>222</v>
-      </c>
-      <c r="G85" s="5"/>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
-        <v>12</v>
-      </c>
-      <c r="B86" t="s">
-        <v>9</v>
-      </c>
-      <c r="C86" t="s">
-        <v>95</v>
-      </c>
-      <c r="D86" t="s">
-        <v>13</v>
-      </c>
-      <c r="E86" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F86" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="G86" s="5"/>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
-        <v>24</v>
-      </c>
-      <c r="B87" t="s">
-        <v>25</v>
-      </c>
-      <c r="C87" t="s">
-        <v>62</v>
-      </c>
-      <c r="D87" t="s">
-        <v>26</v>
       </c>
       <c r="E87" s="7">
         <v>46176</v>
       </c>
-      <c r="F87" s="17" t="s">
-        <v>217</v>
+      <c r="F87" s="12" t="s">
+        <v>219</v>
       </c>
       <c r="G87" s="5"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
-        <v>24</v>
-      </c>
-      <c r="B88" t="s">
-        <v>25</v>
-      </c>
-      <c r="C88" t="s">
-        <v>27</v>
-      </c>
-      <c r="D88" t="s">
-        <v>26</v>
+      <c r="A88" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="E88" s="7">
         <v>46176</v>
       </c>
-      <c r="F88" s="11" t="s">
-        <v>228</v>
+      <c r="F88" s="12" t="s">
+        <v>222</v>
       </c>
       <c r="G88" s="5"/>
     </row>
@@ -3316,790 +3383,798 @@
         <v>7</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="D89" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E89" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F89" s="17" t="s">
-        <v>197</v>
+        <v>46176</v>
+      </c>
+      <c r="F89" s="15" t="s">
+        <v>227</v>
       </c>
       <c r="G89" s="5"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
-        <v>6</v>
+        <v>153</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>7</v>
+        <v>154</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>48</v>
+        <v>155</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>8</v>
+        <v>156</v>
       </c>
       <c r="E90" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F90" s="17" t="s">
-        <v>204</v>
+        <v>46176</v>
+      </c>
+      <c r="F90" s="12" t="s">
+        <v>217</v>
       </c>
       <c r="G90" s="5"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
-        <v>6</v>
+        <v>153</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>7</v>
+        <v>154</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>46</v>
+        <v>186</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>8</v>
+        <v>156</v>
       </c>
       <c r="E91" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F91" s="17" t="s">
-        <v>208</v>
+        <v>46176</v>
+      </c>
+      <c r="F91" s="12" t="s">
+        <v>228</v>
       </c>
       <c r="G91" s="5"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>154</v>
+        <v>10</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E92" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F92" s="17" t="s">
-        <v>191</v>
+        <v>46176</v>
+      </c>
+      <c r="F92" s="12" t="s">
+        <v>218</v>
       </c>
       <c r="G92" s="5"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>154</v>
+        <v>55</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E93" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F93" s="17" t="s">
-        <v>202</v>
+        <v>46176</v>
+      </c>
+      <c r="F93" s="12" t="s">
+        <v>223</v>
       </c>
       <c r="G93" s="5"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>154</v>
+        <v>10</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>186</v>
+        <v>212</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E94" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F94" s="17" t="s">
-        <v>206</v>
+        <v>46176</v>
+      </c>
+      <c r="F94" s="12" t="s">
+        <v>229</v>
       </c>
       <c r="G94" s="5"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
-        <v>149</v>
+        <v>3</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>150</v>
+        <v>29</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>151</v>
+        <v>5</v>
       </c>
       <c r="E95" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F95" s="17" t="s">
-        <v>193</v>
+        <v>46176</v>
+      </c>
+      <c r="F95" s="13" t="s">
+        <v>216</v>
       </c>
       <c r="G95" s="5"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
-        <v>149</v>
+        <v>3</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>184</v>
+        <v>28</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>151</v>
+        <v>5</v>
       </c>
       <c r="E96" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F96" s="17" t="s">
-        <v>201</v>
+        <v>46176</v>
+      </c>
+      <c r="F96" s="13" t="s">
+        <v>224</v>
       </c>
       <c r="G96" s="5"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
-        <v>149</v>
+        <v>16</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>187</v>
+        <v>58</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>151</v>
+        <v>17</v>
       </c>
       <c r="E97" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F97" s="17" t="s">
-        <v>210</v>
+        <v>46176</v>
+      </c>
+      <c r="F97" s="13" t="s">
+        <v>221</v>
       </c>
       <c r="G97" s="5"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E98" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F98" s="18" t="s">
-        <v>189</v>
+        <v>46176</v>
+      </c>
+      <c r="F98" s="14" t="s">
+        <v>53</v>
       </c>
       <c r="G98" s="5"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="E99" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F99" s="18" t="s">
-        <v>199</v>
+        <v>46176</v>
+      </c>
+      <c r="F99" s="12" t="s">
+        <v>214</v>
       </c>
       <c r="G99" s="5"/>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="E100" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F100" s="18" t="s">
-        <v>203</v>
-      </c>
-      <c r="G100" s="5"/>
+        <v>46176</v>
+      </c>
+      <c r="F100" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="G100" s="5" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
-        <v>16</v>
+        <v>158</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>36</v>
+        <v>159</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>17</v>
+        <v>160</v>
       </c>
       <c r="E101" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F101" s="17" t="s">
-        <v>194</v>
+        <v>46176</v>
+      </c>
+      <c r="F101" s="12" t="s">
+        <v>225</v>
       </c>
       <c r="G101" s="5"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
-        <v>16</v>
+        <v>158</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>34</v>
+        <v>161</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>17</v>
+        <v>160</v>
       </c>
       <c r="E102" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F102" s="8" t="s">
-        <v>53</v>
+        <v>46176</v>
+      </c>
+      <c r="F102" s="12" t="s">
+        <v>231</v>
       </c>
       <c r="G102" s="5"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
-        <v>21</v>
+        <v>158</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>40</v>
+        <v>162</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>23</v>
+        <v>160</v>
       </c>
       <c r="E103" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F103" s="17" t="s">
-        <v>188</v>
+        <v>46176</v>
+      </c>
+      <c r="F103" s="15" t="s">
+        <v>232</v>
       </c>
       <c r="G103" s="5"/>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>39</v>
+        <v>91</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E104" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F104" s="17" t="s">
-        <v>198</v>
-      </c>
-      <c r="G104" s="5"/>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+        <v>46176</v>
+      </c>
+      <c r="F104" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="G104" s="5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E105" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F105" s="17" t="s">
-        <v>205</v>
-      </c>
-      <c r="G105" s="5"/>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+        <v>46176</v>
+      </c>
+      <c r="F105" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="G105" s="5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
-        <v>158</v>
+        <v>19</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>181</v>
+        <v>93</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="E106" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F106" s="17" t="s">
-        <v>192</v>
-      </c>
-      <c r="G106" s="5"/>
+        <v>46176</v>
+      </c>
+      <c r="F106" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="G106" s="5" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
-        <v>158</v>
+        <v>11</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>182</v>
+        <v>14</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
       <c r="E107" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F107" s="8" t="s">
-        <v>53</v>
+        <v>46176</v>
+      </c>
+      <c r="F107" s="15" t="s">
+        <v>213</v>
       </c>
       <c r="G107" s="5"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
-        <v>158</v>
+        <v>11</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>183</v>
+        <v>90</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
       <c r="E108" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F108" s="17" t="s">
-        <v>200</v>
+        <v>46176</v>
+      </c>
+      <c r="F108" s="14" t="s">
+        <v>53</v>
       </c>
       <c r="G108" s="5"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E109" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F109" s="8" t="s">
-        <v>53</v>
+        <v>46176</v>
+      </c>
+      <c r="F109" s="13" t="s">
+        <v>220</v>
       </c>
       <c r="G109" s="5"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" s="4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>37</v>
+        <v>95</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E110" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F110" s="8" t="s">
-        <v>53</v>
+        <v>46176</v>
+      </c>
+      <c r="F110" s="13" t="s">
+        <v>230</v>
       </c>
       <c r="G110" s="5"/>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E111" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F111" s="17" t="s">
-        <v>195</v>
+        <v>46176</v>
+      </c>
+      <c r="F111" s="12" t="s">
+        <v>215</v>
       </c>
       <c r="G111" s="5"/>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" s="4" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E112" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F112" s="17" t="s">
-        <v>207</v>
+        <v>46176</v>
+      </c>
+      <c r="F112" s="15" t="s">
+        <v>226</v>
       </c>
       <c r="G112" s="5"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" s="4" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E113" s="7">
         <v>46175</v>
       </c>
-      <c r="F113" s="18" t="s">
-        <v>196</v>
+      <c r="F113" s="12" t="s">
+        <v>197</v>
       </c>
       <c r="G113" s="5"/>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E114" s="7">
         <v>46175</v>
       </c>
-      <c r="F114" s="18" t="s">
-        <v>211</v>
+      <c r="F114" s="12" t="s">
+        <v>204</v>
       </c>
       <c r="G114" s="5"/>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="E115" s="7">
         <v>46175</v>
       </c>
-      <c r="F115" s="17" t="s">
-        <v>190</v>
+      <c r="F115" s="12" t="s">
+        <v>208</v>
       </c>
       <c r="G115" s="5"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" s="4" t="s">
-        <v>24</v>
+        <v>153</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>25</v>
+        <v>154</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>26</v>
+        <v>156</v>
       </c>
       <c r="E116" s="7">
         <v>46175</v>
       </c>
-      <c r="F116" s="17" t="s">
-        <v>209</v>
+      <c r="F116" s="12" t="s">
+        <v>191</v>
       </c>
       <c r="G116" s="5"/>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
-        <v>6</v>
-      </c>
-      <c r="B117" t="s">
-        <v>7</v>
-      </c>
-      <c r="C117" t="s">
-        <v>73</v>
-      </c>
-      <c r="D117" t="s">
-        <v>8</v>
+      <c r="A117" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="D117" s="4" t="s">
+        <v>156</v>
       </c>
       <c r="E117" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F117" s="17" t="s">
-        <v>169</v>
+        <v>46175</v>
+      </c>
+      <c r="F117" s="12" t="s">
+        <v>202</v>
       </c>
       <c r="G117" s="5"/>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A118" t="s">
-        <v>6</v>
-      </c>
-      <c r="B118" t="s">
-        <v>7</v>
-      </c>
-      <c r="C118" t="s">
-        <v>71</v>
-      </c>
-      <c r="D118" t="s">
-        <v>8</v>
+      <c r="A118" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="D118" s="4" t="s">
+        <v>156</v>
       </c>
       <c r="E118" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F118" s="17" t="s">
-        <v>176</v>
+        <v>46175</v>
+      </c>
+      <c r="F118" s="12" t="s">
+        <v>206</v>
       </c>
       <c r="G118" s="5"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A119" t="s">
-        <v>153</v>
-      </c>
-      <c r="B119" t="s">
-        <v>154</v>
-      </c>
-      <c r="C119" t="s">
-        <v>155</v>
-      </c>
-      <c r="D119" t="s">
-        <v>156</v>
+      <c r="A119" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="D119" s="4" t="s">
+        <v>151</v>
       </c>
       <c r="E119" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F119" s="17" t="s">
-        <v>171</v>
+        <v>46175</v>
+      </c>
+      <c r="F119" s="12" t="s">
+        <v>193</v>
       </c>
       <c r="G119" s="5"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A120" t="s">
-        <v>153</v>
-      </c>
-      <c r="B120" t="s">
-        <v>154</v>
-      </c>
-      <c r="C120" t="s">
-        <v>157</v>
-      </c>
-      <c r="D120" t="s">
-        <v>156</v>
+      <c r="A120" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="D120" s="4" t="s">
+        <v>151</v>
       </c>
       <c r="E120" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F120" s="17" t="s">
-        <v>177</v>
+        <v>46175</v>
+      </c>
+      <c r="F120" s="12" t="s">
+        <v>201</v>
       </c>
       <c r="G120" s="5"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A121" t="s">
+      <c r="A121" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="B121" t="s">
-        <v>10</v>
-      </c>
-      <c r="C121" t="s">
-        <v>150</v>
-      </c>
-      <c r="D121" t="s">
+      <c r="B121" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D121" s="4" t="s">
         <v>151</v>
       </c>
       <c r="E121" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F121" s="17" t="s">
-        <v>168</v>
+        <v>46175</v>
+      </c>
+      <c r="F121" s="12" t="s">
+        <v>210</v>
       </c>
       <c r="G121" s="5"/>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A122" t="s">
-        <v>149</v>
-      </c>
-      <c r="B122" t="s">
-        <v>10</v>
-      </c>
-      <c r="C122" t="s">
-        <v>152</v>
-      </c>
-      <c r="D122" t="s">
-        <v>151</v>
+      <c r="A122" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C122" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D122" s="4" t="s">
+        <v>5</v>
       </c>
       <c r="E122" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F122" s="11" t="s">
-        <v>178</v>
+        <v>46175</v>
+      </c>
+      <c r="F122" s="13" t="s">
+        <v>189</v>
       </c>
       <c r="G122" s="5"/>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A123" t="s">
+      <c r="A123" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C123" t="s">
-        <v>29</v>
-      </c>
-      <c r="D123" t="s">
+      <c r="C123" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D123" s="4" t="s">
         <v>5</v>
       </c>
       <c r="E123" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F123" s="18" t="s">
-        <v>166</v>
+        <v>46175</v>
+      </c>
+      <c r="F123" s="13" t="s">
+        <v>199</v>
       </c>
       <c r="G123" s="5"/>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A124" t="s">
+      <c r="A124" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B124" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C124" t="s">
-        <v>28</v>
-      </c>
-      <c r="D124" t="s">
+      <c r="C124" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D124" s="4" t="s">
         <v>5</v>
       </c>
       <c r="E124" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F124" s="18" t="s">
-        <v>174</v>
+        <v>46175</v>
+      </c>
+      <c r="F124" s="13" t="s">
+        <v>203</v>
       </c>
       <c r="G124" s="5"/>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A125" t="s">
+      <c r="A125" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B125" t="s">
-        <v>55</v>
-      </c>
-      <c r="C125" t="s">
-        <v>56</v>
-      </c>
-      <c r="D125" t="s">
+      <c r="B125" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C125" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D125" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E125" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F125" s="17" t="s">
-        <v>173</v>
+        <v>46175</v>
+      </c>
+      <c r="F125" s="12" t="s">
+        <v>194</v>
       </c>
       <c r="G125" s="5"/>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A126" t="s">
+      <c r="A126" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B126" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C126" t="s">
-        <v>58</v>
-      </c>
-      <c r="D126" t="s">
+      <c r="C126" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D126" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E126" s="7">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="F126" s="8" t="s">
         <v>53</v>
@@ -4107,2327 +4182,2831 @@
       <c r="G126" s="5"/>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A127" t="s">
+      <c r="A127" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B127" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C127" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D127" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E127" s="7">
+        <v>46175</v>
+      </c>
+      <c r="F127" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="G127" s="5"/>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A128" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C128" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D128" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E128" s="7">
+        <v>46175</v>
+      </c>
+      <c r="F128" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="G128" s="5"/>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A129" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B129" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C127" t="s">
-        <v>60</v>
-      </c>
-      <c r="D127" t="s">
+      <c r="C129" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D129" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E127" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F127" s="17" t="s">
-        <v>167</v>
-      </c>
-      <c r="G127" s="5"/>
-    </row>
-    <row r="128" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A128" t="s">
+      <c r="E129" s="7">
+        <v>46175</v>
+      </c>
+      <c r="F129" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="G129" s="5"/>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A130" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B130" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C128" t="s">
-        <v>159</v>
-      </c>
-      <c r="D128" t="s">
+      <c r="C130" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="D130" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="E128" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F128" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G128" s="5" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A129" t="s">
+      <c r="E130" s="7">
+        <v>46175</v>
+      </c>
+      <c r="F130" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="G130" s="5"/>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A131" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B131" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C129" t="s">
-        <v>161</v>
-      </c>
-      <c r="D129" t="s">
+      <c r="C131" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="D131" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="E129" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F129" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G129" s="5" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A130" t="s">
-        <v>158</v>
-      </c>
-      <c r="B130" t="s">
-        <v>55</v>
-      </c>
-      <c r="C130" t="s">
-        <v>162</v>
-      </c>
-      <c r="D130" t="s">
-        <v>160</v>
-      </c>
-      <c r="E130" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F130" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="G130" s="5"/>
-    </row>
-    <row r="131" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A131" t="s">
-        <v>19</v>
-      </c>
-      <c r="B131" t="s">
-        <v>18</v>
-      </c>
-      <c r="C131" t="s">
-        <v>59</v>
-      </c>
-      <c r="D131" t="s">
-        <v>20</v>
-      </c>
       <c r="E131" s="7">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="F131" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="G131" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A132" t="s">
+      <c r="G131" s="5"/>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A132" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D132" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E132" s="7">
+        <v>46175</v>
+      </c>
+      <c r="F132" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="G132" s="5"/>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A133" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B133" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C132" t="s">
+      <c r="C133" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D132" t="s">
+      <c r="D133" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E132" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F132" s="8" t="s">
+      <c r="E133" s="7">
+        <v>46175</v>
+      </c>
+      <c r="F133" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="G132" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A133" t="s">
+      <c r="G133" s="5"/>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A134" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D134" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E134" s="7">
+        <v>46175</v>
+      </c>
+      <c r="F134" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G134" s="5"/>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A135" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B135" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C133" t="s">
+      <c r="C135" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D133" t="s">
+      <c r="D135" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E133" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F133" s="17" t="s">
-        <v>170</v>
-      </c>
-      <c r="G133" s="5"/>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A134" t="s">
+      <c r="E135" s="7">
+        <v>46175</v>
+      </c>
+      <c r="F135" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="G135" s="5"/>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A136" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C136" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D136" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E136" s="7">
+        <v>46175</v>
+      </c>
+      <c r="F136" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="G136" s="5"/>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A137" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B137" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C134" t="s">
+      <c r="C137" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D134" t="s">
+      <c r="D137" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E134" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F134" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="G134" s="5"/>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A135" t="s">
-        <v>12</v>
-      </c>
-      <c r="B135" t="s">
-        <v>67</v>
-      </c>
-      <c r="C135" t="s">
-        <v>68</v>
-      </c>
-      <c r="D135" t="s">
-        <v>13</v>
-      </c>
-      <c r="E135" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F135" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G135" s="5"/>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A136" t="s">
-        <v>24</v>
-      </c>
-      <c r="B136" t="s">
-        <v>25</v>
-      </c>
-      <c r="C136" t="s">
-        <v>62</v>
-      </c>
-      <c r="D136" t="s">
-        <v>26</v>
-      </c>
-      <c r="E136" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F136" s="17" t="s">
-        <v>165</v>
-      </c>
-      <c r="G136" s="5"/>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A137" t="s">
-        <v>24</v>
-      </c>
-      <c r="B137" t="s">
-        <v>25</v>
-      </c>
-      <c r="C137" t="s">
-        <v>27</v>
-      </c>
-      <c r="D137" t="s">
-        <v>26</v>
-      </c>
       <c r="E137" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F137" s="17" t="s">
-        <v>175</v>
+        <v>46175</v>
+      </c>
+      <c r="F137" s="13" t="s">
+        <v>196</v>
       </c>
       <c r="G137" s="5"/>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" s="4" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E138" s="7">
-        <v>46172</v>
+        <v>46175</v>
       </c>
       <c r="F138" s="13" t="s">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="G138" s="5"/>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" s="4" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="E139" s="7">
-        <v>46172</v>
-      </c>
-      <c r="F139" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G139" s="5" t="s">
-        <v>164</v>
-      </c>
+        <v>46175</v>
+      </c>
+      <c r="F139" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="G139" s="5"/>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" s="4" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E140" s="7">
-        <v>46172</v>
-      </c>
-      <c r="F140" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="G140" s="6"/>
+        <v>46175</v>
+      </c>
+      <c r="F140" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="G140" s="5"/>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" s="4" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E141" s="7">
-        <v>46172</v>
-      </c>
-      <c r="F141" s="13" t="s">
-        <v>144</v>
+        <v>46174</v>
+      </c>
+      <c r="F141" s="12" t="s">
+        <v>169</v>
       </c>
       <c r="G141" s="5"/>
     </row>
-    <row r="142" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" s="4" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E142" s="7">
-        <v>46172</v>
-      </c>
-      <c r="F142" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G142" s="5" t="s">
-        <v>31</v>
-      </c>
+        <v>46174</v>
+      </c>
+      <c r="F142" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="G142" s="5"/>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" s="4" t="s">
-        <v>11</v>
+        <v>153</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>10</v>
+        <v>154</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>33</v>
+        <v>155</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>15</v>
+        <v>156</v>
       </c>
       <c r="E143" s="7">
-        <v>46172</v>
-      </c>
-      <c r="F143" s="13" t="s">
-        <v>145</v>
+        <v>46174</v>
+      </c>
+      <c r="F143" s="12" t="s">
+        <v>171</v>
       </c>
       <c r="G143" s="5"/>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" s="4" t="s">
-        <v>12</v>
+        <v>153</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>9</v>
+        <v>154</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>95</v>
+        <v>157</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>13</v>
+        <v>156</v>
       </c>
       <c r="E144" s="7">
-        <v>46172</v>
-      </c>
-      <c r="F144" s="14" t="s">
-        <v>147</v>
+        <v>46174</v>
+      </c>
+      <c r="F144" s="12" t="s">
+        <v>177</v>
       </c>
       <c r="G144" s="5"/>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" s="4" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>42</v>
+        <v>150</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>26</v>
+        <v>151</v>
       </c>
       <c r="E145" s="7">
-        <v>46172</v>
-      </c>
-      <c r="F145" s="13" t="s">
-        <v>143</v>
+        <v>46174</v>
+      </c>
+      <c r="F145" s="12" t="s">
+        <v>168</v>
       </c>
       <c r="G145" s="5"/>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" s="4" t="s">
-        <v>6</v>
+        <v>149</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>47</v>
+        <v>152</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>8</v>
+        <v>151</v>
       </c>
       <c r="E146" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F146" s="13" t="s">
-        <v>128</v>
+        <v>46174</v>
+      </c>
+      <c r="F146" s="15" t="s">
+        <v>178</v>
       </c>
       <c r="G146" s="5"/>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" s="4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E147" s="7">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="F147" s="13" t="s">
-        <v>135</v>
+        <v>166</v>
       </c>
       <c r="G147" s="5"/>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" s="4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E148" s="7">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="F148" s="13" t="s">
-        <v>140</v>
+        <v>174</v>
       </c>
       <c r="G148" s="5"/>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" s="4" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E149" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F149" s="14" t="s">
-        <v>129</v>
+        <v>46174</v>
+      </c>
+      <c r="F149" s="12" t="s">
+        <v>173</v>
       </c>
       <c r="G149" s="5"/>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" s="4" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E150" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F150" s="14" t="s">
-        <v>136</v>
+        <v>46174</v>
+      </c>
+      <c r="F150" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G150" s="5"/>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" s="4" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E151" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F151" s="14" t="s">
-        <v>134</v>
+        <v>46174</v>
+      </c>
+      <c r="F151" s="12" t="s">
+        <v>167</v>
       </c>
       <c r="G151" s="5"/>
     </row>
     <row r="152" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A152" s="4" t="s">
-        <v>16</v>
+        <v>158</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>34</v>
+        <v>159</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>17</v>
+        <v>160</v>
       </c>
       <c r="E152" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F152" s="15" t="s">
+        <v>46174</v>
+      </c>
+      <c r="F152" s="8" t="s">
         <v>53</v>
       </c>
       <c r="G152" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A153" s="4" t="s">
-        <v>16</v>
+        <v>158</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>36</v>
+        <v>161</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>17</v>
+        <v>160</v>
       </c>
       <c r="E153" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F153" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="G153" s="5"/>
+        <v>46174</v>
+      </c>
+      <c r="F153" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G153" s="5" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" s="4" t="s">
-        <v>21</v>
+        <v>158</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>60</v>
+        <v>162</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>23</v>
+        <v>160</v>
       </c>
       <c r="E154" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F154" s="13" t="s">
-        <v>131</v>
+        <v>46174</v>
+      </c>
+      <c r="F154" s="15" t="s">
+        <v>179</v>
       </c>
       <c r="G154" s="5"/>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A155" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E155" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F155" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="G155" s="5"/>
+        <v>46174</v>
+      </c>
+      <c r="F155" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G155" s="5" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="156" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A156" s="4" t="s">
         <v>19</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>91</v>
+        <v>18</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>92</v>
+        <v>32</v>
       </c>
       <c r="D156" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E156" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F156" s="15" t="s">
+        <v>46174</v>
+      </c>
+      <c r="F156" s="8" t="s">
         <v>53</v>
       </c>
       <c r="G156" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="157" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" s="4" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E157" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F157" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="G157" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>46174</v>
+      </c>
+      <c r="F157" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="G157" s="5"/>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" s="4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>93</v>
+        <v>30</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E158" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F158" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="G158" s="5" t="s">
-        <v>31</v>
-      </c>
+        <v>46174</v>
+      </c>
+      <c r="F158" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="G158" s="5"/>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E159" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F159" s="13" t="s">
-        <v>132</v>
+        <v>46174</v>
+      </c>
+      <c r="F159" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G159" s="5"/>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" s="4" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E160" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F160" s="13" t="s">
-        <v>139</v>
+        <v>46174</v>
+      </c>
+      <c r="F160" s="12" t="s">
+        <v>165</v>
       </c>
       <c r="G160" s="5"/>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" s="4" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E161" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F161" s="14" t="s">
-        <v>133</v>
+        <v>46174</v>
+      </c>
+      <c r="F161" s="12" t="s">
+        <v>175</v>
       </c>
       <c r="G161" s="5"/>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162" s="4" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>67</v>
+        <v>7</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E162" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F162" s="14" t="s">
-        <v>141</v>
+        <v>46172</v>
+      </c>
+      <c r="F162" s="12" t="s">
+        <v>148</v>
       </c>
       <c r="G162" s="5"/>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163" s="4" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="E163" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F163" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="G163" s="5"/>
+        <v>46172</v>
+      </c>
+      <c r="F163" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G163" s="5" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" s="4" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E164" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F164" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="G164" s="5"/>
+        <v>46172</v>
+      </c>
+      <c r="F164" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="G164" s="6"/>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" s="4" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E165" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F165" s="13" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
+        <v>46172</v>
+      </c>
+      <c r="F165" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="G165" s="5"/>
+    </row>
+    <row r="166" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A166" s="4" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E166" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F166" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="G166" s="5"/>
+        <v>46172</v>
+      </c>
+      <c r="F166" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G166" s="5" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" s="4" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E167" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F167" s="16" t="s">
-        <v>125</v>
-      </c>
+        <v>46172</v>
+      </c>
+      <c r="F167" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G167" s="5"/>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" s="4" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>28</v>
+        <v>95</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E168" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F168" s="14" t="s">
-        <v>116</v>
-      </c>
+        <v>46172</v>
+      </c>
+      <c r="F168" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="G168" s="5"/>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" s="4" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="E169" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F169" s="15" t="s">
-        <v>53</v>
-      </c>
+        <v>46172</v>
+      </c>
+      <c r="F169" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="G169" s="5"/>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" s="4" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E170" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F170" s="14" t="s">
-        <v>127</v>
-      </c>
+        <v>46171</v>
+      </c>
+      <c r="F170" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G170" s="5"/>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" s="4" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E171" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F171" s="13" t="s">
-        <v>118</v>
-      </c>
+        <v>46171</v>
+      </c>
+      <c r="F171" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="G171" s="5"/>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" s="4" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E172" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F172" s="15" t="s">
-        <v>53</v>
-      </c>
+        <v>46171</v>
+      </c>
+      <c r="F172" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="G172" s="5"/>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" s="4" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E173" s="7">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="F173" s="13" t="s">
-        <v>124</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="G173" s="5"/>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" s="4" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="E174" s="7">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="F174" s="13" t="s">
-        <v>97</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="G174" s="5"/>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" s="4" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E175" s="7">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="F175" s="13" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
+        <v>134</v>
+      </c>
+      <c r="G175" s="5"/>
+    </row>
+    <row r="176" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A176" s="4" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E176" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F176" s="13" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>46171</v>
+      </c>
+      <c r="F176" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="G176" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B177" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E177" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F177" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="G177" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="178" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>46171</v>
+      </c>
+      <c r="F177" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="G177" s="5"/>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E178" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F178" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="G178" s="5" t="s">
-        <v>31</v>
-      </c>
+        <v>46171</v>
+      </c>
+      <c r="F178" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="G178" s="5"/>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A179" s="4" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E179" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F179" s="13" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
+        <v>46171</v>
+      </c>
+      <c r="F179" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="G179" s="5"/>
+    </row>
+    <row r="180" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A180" s="4" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>33</v>
+        <v>92</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E180" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F180" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
+        <v>46171</v>
+      </c>
+      <c r="F180" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="G180" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A181" s="4" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E181" s="7">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="F181" s="14" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+      <c r="G181" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A182" s="4" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>45</v>
+        <v>93</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E182" s="7">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="F182" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="G182" s="5"/>
+        <v>53</v>
+      </c>
+      <c r="G182" s="5" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A183" s="4" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="E183" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F183" s="13" t="s">
-        <v>113</v>
-      </c>
+        <v>46171</v>
+      </c>
+      <c r="F183" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="G183" s="5"/>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A184" s="4" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="E184" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F184" s="13" t="s">
-        <v>123</v>
-      </c>
+        <v>46171</v>
+      </c>
+      <c r="F184" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="G184" s="5"/>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A185" s="4" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E185" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F185" s="14" t="s">
-        <v>96</v>
-      </c>
+        <v>46171</v>
+      </c>
+      <c r="F185" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="G185" s="5"/>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A186" s="4" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>7</v>
+        <v>67</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E186" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F186" s="14" t="s">
-        <v>98</v>
-      </c>
+        <v>46171</v>
+      </c>
+      <c r="F186" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="G186" s="5"/>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A187" s="4" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="E187" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F187" s="14" t="s">
-        <v>99</v>
-      </c>
+        <v>46171</v>
+      </c>
+      <c r="F187" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="G187" s="5"/>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A188" s="4" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="E188" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F188" s="14" t="s">
-        <v>100</v>
-      </c>
+        <v>46171</v>
+      </c>
+      <c r="F188" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="G188" s="5"/>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189" s="4" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="D189" s="4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E189" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F189" s="14" t="s">
-        <v>101</v>
+        <v>46170</v>
+      </c>
+      <c r="F189" s="12" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A190" s="4" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D190" s="4" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E190" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F190" s="14" t="s">
-        <v>102</v>
-      </c>
+        <v>46170</v>
+      </c>
+      <c r="F190" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="G190" s="5"/>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A191" s="4" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="D191" s="4" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E191" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F191" s="8" t="s">
-        <v>53</v>
+        <v>46170</v>
+      </c>
+      <c r="F191" s="15" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A192" s="4" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="D192" s="4" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="E192" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F192" s="14" t="s">
-        <v>103</v>
+        <v>46170</v>
+      </c>
+      <c r="F192" s="13" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A193" s="4" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>94</v>
+        <v>29</v>
       </c>
       <c r="D193" s="4" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="E193" s="7">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="F193" s="14" t="s">
-        <v>104</v>
+        <v>53</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A194" s="4" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>91</v>
+        <v>4</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="D194" s="4" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E194" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F194" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G194" s="4" t="s">
-        <v>105</v>
+        <v>46170</v>
+      </c>
+      <c r="F194" s="13" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A195" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B195" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="D195" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E195" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F195" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G195" s="4" t="s">
-        <v>105</v>
+        <v>46170</v>
+      </c>
+      <c r="F195" s="24" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A196" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B196" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="D196" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E196" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F196" s="8" t="s">
+        <v>46170</v>
+      </c>
+      <c r="F196" s="14" t="s">
         <v>53</v>
-      </c>
-      <c r="G196" s="4" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A197" s="4" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="D197" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E197" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F197" s="14" t="s">
-        <v>106</v>
+        <v>46170</v>
+      </c>
+      <c r="F197" s="12" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A198" s="4" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="D198" s="4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E198" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F198" s="14" t="s">
-        <v>107</v>
+        <v>46170</v>
+      </c>
+      <c r="F198" s="12" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A199" s="4" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="D199" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E199" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F199" s="14" t="s">
-        <v>108</v>
+        <v>46170</v>
+      </c>
+      <c r="F199" s="12" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A200" s="4" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="D200" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E200" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F200" s="16" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
+        <v>46170</v>
+      </c>
+      <c r="F200" s="12" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A201" s="4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="D201" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E201" s="7">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="F201" s="14" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+      <c r="G201" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A202" s="4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C202" s="4" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D202" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E202" s="7">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="F202" s="14" t="s">
-        <v>111</v>
+        <v>53</v>
+      </c>
+      <c r="G202" s="5" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A203" s="4" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C203" s="4" t="s">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="D203" s="4" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E203" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F203" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="G203" s="5"/>
+        <v>46170</v>
+      </c>
+      <c r="F203" s="12" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A204" s="4" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="D204" s="4" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E204" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F204" s="13" t="s">
-        <v>89</v>
+        <v>46170</v>
+      </c>
+      <c r="F204" s="12" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A205" s="4" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C205" s="4" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="D205" s="4" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E205" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F205" s="16" t="s">
-        <v>87</v>
+        <v>46170</v>
+      </c>
+      <c r="F205" s="13" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A206" s="4" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="D206" s="4" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E206" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F206" s="14" t="s">
-        <v>43</v>
+        <v>46170</v>
+      </c>
+      <c r="F206" s="13" t="s">
+        <v>121</v>
       </c>
       <c r="G206" s="5"/>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A207" s="4" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C207" s="4" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D207" s="4" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="E207" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F207" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="G207" s="6"/>
+        <v>46170</v>
+      </c>
+      <c r="F207" s="12" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A208" s="4" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C208" s="4" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="D208" s="4" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="E208" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F208" s="14" t="s">
-        <v>84</v>
+        <v>46170</v>
+      </c>
+      <c r="F208" s="12" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A209" s="4" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C209" s="4" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="D209" s="4" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E209" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F209" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="G209" s="6"/>
-    </row>
-    <row r="210" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>46169</v>
+      </c>
+      <c r="F209" s="13" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A210" s="4" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C210" s="4" t="s">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="D210" s="4" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E210" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F210" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G210" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="211" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>46169</v>
+      </c>
+      <c r="F210" s="13" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A211" s="4" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C211" s="4" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="D211" s="4" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E211" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F211" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G211" s="5" t="s">
-        <v>112</v>
+        <v>46169</v>
+      </c>
+      <c r="F211" s="13" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A212" s="4" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="C212" s="4" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="D212" s="4" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="E212" s="7">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="F212" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="G212" s="5"/>
+        <v>100</v>
+      </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A213" s="4" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="C213" s="4" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D213" s="4" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="E213" s="7">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="F213" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="G213" s="6"/>
+        <v>101</v>
+      </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A214" s="4" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="C214" s="4" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="D214" s="4" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E214" s="7">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="F214" s="13" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="215" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A215" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B215" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C215" s="4" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="D215" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E215" s="7">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="F215" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="G215" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="216" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A216" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C216" s="4" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="D216" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E216" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F216" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="G216" s="5" t="s">
-        <v>31</v>
+        <v>46169</v>
+      </c>
+      <c r="F216" s="13" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A217" s="4" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="C217" s="4" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="D217" s="4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E217" s="7">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="F217" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="G217" s="5"/>
+        <v>104</v>
+      </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A218" s="4" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="C218" s="4" t="s">
-        <v>33</v>
+        <v>92</v>
       </c>
       <c r="D218" s="4" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E218" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F218" s="13" t="s">
-        <v>75</v>
+        <v>46169</v>
+      </c>
+      <c r="F218" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G218" s="4" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A219" s="4" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C219" s="4" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="D219" s="4" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E219" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F219" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="G219" s="5"/>
+        <v>46169</v>
+      </c>
+      <c r="F219" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G219" s="4" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A220" s="4" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>45</v>
+        <v>93</v>
       </c>
       <c r="D220" s="4" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E220" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F220" s="14" t="s">
-        <v>85</v>
+        <v>46169</v>
+      </c>
+      <c r="F220" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G220" s="4" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A221" s="4" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C221" s="4" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="D221" s="4" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="E221" s="7">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="F221" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="G221" s="6"/>
+        <v>106</v>
+      </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A222" s="4" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C222" s="4" t="s">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="D222" s="4" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="E222" s="7">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="F222" s="13" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A223" s="4" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C223" s="4" t="s">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="D223" s="4" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E223" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F223" s="9" t="s">
-        <v>72</v>
+        <v>46169</v>
+      </c>
+      <c r="F223" s="13" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A224" s="4" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B224" s="4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C224" s="4" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="D224" s="4" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E224" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F224" s="9" t="s">
-        <v>74</v>
+        <v>46169</v>
+      </c>
+      <c r="F224" s="15" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A225" s="4" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="B225" s="4" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C225" s="4" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="D225" s="4" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="E225" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F225" s="10" t="s">
-        <v>65</v>
+        <v>46169</v>
+      </c>
+      <c r="F225" s="13" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A226" s="4" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C226" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D226" s="4" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="E226" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F226" s="10" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="227" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>46169</v>
+      </c>
+      <c r="F226" s="13" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A227" s="4" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C227" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D227" s="12" t="s">
-        <v>17</v>
+        <v>47</v>
+      </c>
+      <c r="D227" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="E227" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F227" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G227" s="5" t="s">
-        <v>112</v>
-      </c>
+        <v>46168</v>
+      </c>
+      <c r="F227" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="G227" s="5"/>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A228" s="4" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B228" s="4" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C228" s="4" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D228" s="4" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E228" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F228" s="9" t="s">
-        <v>57</v>
+        <v>46168</v>
+      </c>
+      <c r="F228" s="12" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A229" s="4" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C229" s="4" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="D229" s="4" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E229" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F229" s="8" t="s">
-        <v>53</v>
+        <v>46168</v>
+      </c>
+      <c r="F229" s="15" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A230" s="4" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="C230" s="4" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="D230" s="4" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="E230" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F230" s="9" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="231" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>46168</v>
+      </c>
+      <c r="F230" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="G230" s="5"/>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A231" s="4" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C231" s="4" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="D231" s="4" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E231" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F231" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G231" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="232" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>46168</v>
+      </c>
+      <c r="F231" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="G231" s="6"/>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A232" s="4" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C232" s="4" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="D232" s="4" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E232" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F232" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G232" s="5" t="s">
-        <v>31</v>
+        <v>46168</v>
+      </c>
+      <c r="F232" s="13" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A233" s="4" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C233" s="4" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="D233" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E233" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F233" s="9" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
+        <v>46168</v>
+      </c>
+      <c r="F233" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="G233" s="6"/>
+    </row>
+    <row r="234" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A234" s="4" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="C234" s="4" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="D234" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E234" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F234" s="10" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.3">
+        <v>46168</v>
+      </c>
+      <c r="F234" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G234" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A235" s="4" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C235" s="4" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D235" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E235" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F235" s="10" t="s">
-        <v>70</v>
+        <v>46168</v>
+      </c>
+      <c r="F235" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G235" s="5" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A236" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="C236" s="4" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="D236" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E236" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F236" s="9" t="s">
-        <v>63</v>
-      </c>
+        <v>46168</v>
+      </c>
+      <c r="F236" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="G236" s="5"/>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A237" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B237" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C237" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D237" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E237" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F237" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="G237" s="6"/>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A238" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B238" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C238" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D238" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E238" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F238" s="12" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A239" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B239" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C239" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D239" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E239" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F239" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G239" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A240" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B240" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C240" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D240" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E240" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F240" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G240" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A241" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B241" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C241" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D241" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E241" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F241" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="G241" s="5"/>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A242" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B242" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C242" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D242" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E242" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F242" s="12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A243" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B243" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C243" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D243" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E243" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F243" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="G243" s="5"/>
+    </row>
+    <row r="244" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A244" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B244" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C244" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D244" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E244" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F244" s="13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A245" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B237" s="4" t="s">
+      <c r="B245" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C237" s="4" t="s">
+      <c r="C245" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D237" s="4" t="s">
+      <c r="D245" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E237" s="7">
+      <c r="E245" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F245" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="G245" s="6"/>
+    </row>
+    <row r="246" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A246" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B246" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C246" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D246" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E246" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F246" s="12" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A247" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B247" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C247" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D247" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E247" s="7">
         <v>46167</v>
       </c>
-      <c r="F237" s="9" t="s">
+      <c r="F247" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A248" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B248" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C248" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D248" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E248" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F248" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A249" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B249" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C249" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D249" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E249" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F249" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A250" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B250" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C250" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D250" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E250" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F250" s="10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A251" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B251" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C251" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D251" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E251" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F251" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G251" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A252" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B252" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C252" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D252" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E252" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F252" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A253" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B253" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C253" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D253" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E253" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F253" s="8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A254" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B254" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C254" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D254" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E254" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F254" s="9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A255" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B255" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C255" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D255" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E255" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F255" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G255" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A256" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B256" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C256" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D256" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E256" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F256" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G256" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A257" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B257" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C257" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D257" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E257" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F257" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A258" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B258" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C258" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D258" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E258" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F258" s="10" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A259" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B259" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C259" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D259" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E259" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F259" s="10" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A260" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B260" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C260" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D260" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E260" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F260" s="9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A261" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B261" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C261" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D261" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E261" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F261" s="9" t="s">
         <v>64</v>
       </c>
     </row>

--- a/EFETIVIDADE.xlsx
+++ b/EFETIVIDADE.xlsx
@@ -1003,7 +1003,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1056,14 +1056,8 @@
     <xf numFmtId="20" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1564,7 +1558,7 @@
       <c r="E2" s="7">
         <v>46183</v>
       </c>
-      <c r="F2" s="23" t="s">
+      <c r="F2" s="21" t="s">
         <v>283</v>
       </c>
       <c r="G2" s="5"/>
@@ -1669,7 +1663,7 @@
       <c r="E7" s="7">
         <v>46183</v>
       </c>
-      <c r="F7" s="23" t="s">
+      <c r="F7" s="21" t="s">
         <v>284</v>
       </c>
       <c r="G7" s="5"/>
@@ -1732,7 +1726,7 @@
       <c r="E10" s="7">
         <v>46183</v>
       </c>
-      <c r="F10" s="23" t="s">
+      <c r="F10" s="21" t="s">
         <v>282</v>
       </c>
       <c r="G10" s="5"/>
@@ -1774,7 +1768,7 @@
       <c r="E12" s="7">
         <v>46183</v>
       </c>
-      <c r="F12" s="23" t="s">
+      <c r="F12" s="21" t="s">
         <v>285</v>
       </c>
       <c r="G12" s="5"/>
@@ -1837,22 +1831,22 @@
       <c r="E15" s="7">
         <v>46183</v>
       </c>
-      <c r="F15" s="23" t="s">
+      <c r="F15" s="21" t="s">
         <v>248</v>
       </c>
       <c r="G15" s="5"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E16" s="7">
@@ -1861,7 +1855,7 @@
       <c r="F16" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="G16" s="20"/>
+      <c r="G16" s="5"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
@@ -1879,7 +1873,7 @@
       <c r="E17" s="7">
         <v>46182</v>
       </c>
-      <c r="F17" s="22" t="s">
+      <c r="F17" s="20" t="s">
         <v>270</v>
       </c>
       <c r="G17" s="5"/>
@@ -1900,7 +1894,7 @@
       <c r="E18" s="7">
         <v>46182</v>
       </c>
-      <c r="F18" s="22" t="s">
+      <c r="F18" s="20" t="s">
         <v>272</v>
       </c>
       <c r="G18" s="5"/>
@@ -1921,7 +1915,7 @@
       <c r="E19" s="7">
         <v>46182</v>
       </c>
-      <c r="F19" s="23" t="s">
+      <c r="F19" s="21" t="s">
         <v>275</v>
       </c>
       <c r="G19" s="5"/>
@@ -1942,7 +1936,7 @@
       <c r="E20" s="7">
         <v>46182</v>
       </c>
-      <c r="F20" s="22" t="s">
+      <c r="F20" s="20" t="s">
         <v>266</v>
       </c>
       <c r="G20" s="5"/>
@@ -1963,7 +1957,7 @@
       <c r="E21" s="7">
         <v>46182</v>
       </c>
-      <c r="F21" s="22" t="s">
+      <c r="F21" s="20" t="s">
         <v>273</v>
       </c>
       <c r="G21" s="5"/>
@@ -1984,7 +1978,7 @@
       <c r="E22" s="7">
         <v>46182</v>
       </c>
-      <c r="F22" s="22" t="s">
+      <c r="F22" s="20" t="s">
         <v>277</v>
       </c>
       <c r="G22" s="5"/>
@@ -2005,7 +1999,7 @@
       <c r="E23" s="7">
         <v>46182</v>
       </c>
-      <c r="F23" s="22" t="s">
+      <c r="F23" s="20" t="s">
         <v>268</v>
       </c>
       <c r="G23" s="5"/>
@@ -2026,31 +2020,31 @@
       <c r="E24" s="7">
         <v>46182</v>
       </c>
-      <c r="F24" s="22" t="s">
+      <c r="F24" s="20" t="s">
         <v>276</v>
       </c>
       <c r="G24" s="5"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="18" t="s">
+      <c r="A25" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="B25" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C25" s="18" t="s">
+      <c r="C25" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="D25" s="18" t="s">
+      <c r="D25" s="4" t="s">
         <v>151</v>
       </c>
       <c r="E25" s="7">
         <v>46182</v>
       </c>
-      <c r="F25" s="23" t="s">
+      <c r="F25" s="21" t="s">
         <v>281</v>
       </c>
-      <c r="G25" s="20"/>
+      <c r="G25" s="5"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
@@ -2068,7 +2062,7 @@
       <c r="E26" s="7">
         <v>46182</v>
       </c>
-      <c r="F26" s="22" t="s">
+      <c r="F26" s="20" t="s">
         <v>267</v>
       </c>
       <c r="G26" s="5"/>
@@ -2089,7 +2083,7 @@
       <c r="E27" s="7">
         <v>46182</v>
       </c>
-      <c r="F27" s="22" t="s">
+      <c r="F27" s="20" t="s">
         <v>278</v>
       </c>
       <c r="G27" s="5"/>
@@ -2110,7 +2104,7 @@
       <c r="E28" s="7">
         <v>46182</v>
       </c>
-      <c r="F28" s="22" t="s">
+      <c r="F28" s="20" t="s">
         <v>279</v>
       </c>
       <c r="G28" s="5"/>
@@ -2131,7 +2125,7 @@
       <c r="E29" s="7">
         <v>46182</v>
       </c>
-      <c r="F29" s="22" t="s">
+      <c r="F29" s="20" t="s">
         <v>271</v>
       </c>
       <c r="G29" s="5"/>
@@ -2152,7 +2146,7 @@
       <c r="E30" s="7">
         <v>46182</v>
       </c>
-      <c r="F30" s="22" t="s">
+      <c r="F30" s="20" t="s">
         <v>274</v>
       </c>
       <c r="G30" s="5"/>
@@ -2173,7 +2167,7 @@
       <c r="E31" s="7">
         <v>46182</v>
       </c>
-      <c r="F31" s="22" t="s">
+      <c r="F31" s="20" t="s">
         <v>280</v>
       </c>
       <c r="G31" s="5"/>
@@ -2194,7 +2188,7 @@
       <c r="E32" s="7">
         <v>46182</v>
       </c>
-      <c r="F32" s="21" t="s">
+      <c r="F32" s="19" t="s">
         <v>269</v>
       </c>
       <c r="G32" s="5"/>
@@ -2236,7 +2230,7 @@
       <c r="E34" s="7">
         <v>46181</v>
       </c>
-      <c r="F34" s="22" t="s">
+      <c r="F34" s="20" t="s">
         <v>257</v>
       </c>
       <c r="G34" s="5"/>
@@ -2257,7 +2251,7 @@
       <c r="E35" s="7">
         <v>46181</v>
       </c>
-      <c r="F35" s="22" t="s">
+      <c r="F35" s="20" t="s">
         <v>263</v>
       </c>
       <c r="G35" s="5"/>
@@ -2278,7 +2272,7 @@
       <c r="E36" s="7">
         <v>46181</v>
       </c>
-      <c r="F36" s="21" t="s">
+      <c r="F36" s="19" t="s">
         <v>254</v>
       </c>
       <c r="G36" s="5"/>
@@ -2299,7 +2293,7 @@
       <c r="E37" s="7">
         <v>46181</v>
       </c>
-      <c r="F37" s="21" t="s">
+      <c r="F37" s="19" t="s">
         <v>262</v>
       </c>
       <c r="G37" s="5"/>
@@ -2320,7 +2314,7 @@
       <c r="E38" s="7">
         <v>46181</v>
       </c>
-      <c r="F38" s="22" t="s">
+      <c r="F38" s="20" t="s">
         <v>255</v>
       </c>
       <c r="G38" s="5"/>
@@ -2341,7 +2335,7 @@
       <c r="E39" s="7">
         <v>46181</v>
       </c>
-      <c r="F39" s="22" t="s">
+      <c r="F39" s="20" t="s">
         <v>264</v>
       </c>
       <c r="G39" s="5"/>
@@ -2362,7 +2356,7 @@
       <c r="E40" s="7">
         <v>46181</v>
       </c>
-      <c r="F40" s="22" t="s">
+      <c r="F40" s="20" t="s">
         <v>259</v>
       </c>
       <c r="G40" s="5"/>
@@ -2383,7 +2377,7 @@
       <c r="E41" s="7">
         <v>46181</v>
       </c>
-      <c r="F41" s="23" t="s">
+      <c r="F41" s="21" t="s">
         <v>260</v>
       </c>
       <c r="G41" s="5"/>
@@ -2404,7 +2398,7 @@
       <c r="E42" s="7">
         <v>46181</v>
       </c>
-      <c r="F42" s="22" t="s">
+      <c r="F42" s="20" t="s">
         <v>258</v>
       </c>
       <c r="G42" s="5"/>
@@ -2425,31 +2419,31 @@
       <c r="E43" s="7">
         <v>46181</v>
       </c>
-      <c r="F43" s="22" t="s">
+      <c r="F43" s="20" t="s">
         <v>261</v>
       </c>
       <c r="G43" s="5"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="18" t="s">
+      <c r="A44" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="B44" s="18" t="s">
+      <c r="B44" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C44" s="18" t="s">
+      <c r="C44" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="D44" s="18" t="s">
+      <c r="D44" s="4" t="s">
         <v>160</v>
       </c>
       <c r="E44" s="7">
         <v>46181</v>
       </c>
-      <c r="F44" s="23" t="s">
+      <c r="F44" s="21" t="s">
         <v>265</v>
       </c>
-      <c r="G44" s="20"/>
+      <c r="G44" s="5"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
@@ -2467,7 +2461,7 @@
       <c r="E45" s="7">
         <v>46181</v>
       </c>
-      <c r="F45" s="21" t="s">
+      <c r="F45" s="19" t="s">
         <v>256</v>
       </c>
       <c r="G45" s="5"/>
@@ -2635,7 +2629,7 @@
       <c r="E53" s="7">
         <v>46179</v>
       </c>
-      <c r="F53" s="19" t="s">
+      <c r="F53" s="18" t="s">
         <v>251</v>
       </c>
       <c r="G53" s="5"/>
@@ -5640,7 +5634,7 @@
       <c r="E195" s="7">
         <v>46170</v>
       </c>
-      <c r="F195" s="24" t="s">
+      <c r="F195" s="22" t="s">
         <v>118</v>
       </c>
     </row>
@@ -7019,26 +7013,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6b3feda4-8a83-4113-98ac-b9b0c9bd9eab">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="6ca87d14-fc9d-4fcf-a42b-2754e6b3d00d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100AC3CF276C202334E979D7C4EA00D1CCA" ma:contentTypeVersion="13" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="fb5f1640dc82e33e0e3c6b4a833ae52f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6b3feda4-8a83-4113-98ac-b9b0c9bd9eab" xmlns:ns3="6ca87d14-fc9d-4fcf-a42b-2754e6b3d00d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dc11f865ff45eacf010d723a908863aa" ns2:_="" ns3:_="">
     <xsd:import namespace="6b3feda4-8a83-4113-98ac-b9b0c9bd9eab"/>
@@ -7245,10 +7219,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6b3feda4-8a83-4113-98ac-b9b0c9bd9eab">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="6ca87d14-fc9d-4fcf-a42b-2754e6b3d00d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6F72255-F15E-4B46-A16C-2F18C675CB37}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E295317-F47C-4C92-88FC-9DAD72755AAC}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="6b3feda4-8a83-4113-98ac-b9b0c9bd9eab"/>
+    <ds:schemaRef ds:uri="6ca87d14-fc9d-4fcf-a42b-2754e6b3d00d"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -7265,20 +7270,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E295317-F47C-4C92-88FC-9DAD72755AAC}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6F72255-F15E-4B46-A16C-2F18C675CB37}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="6b3feda4-8a83-4113-98ac-b9b0c9bd9eab"/>
-    <ds:schemaRef ds:uri="6ca87d14-fc9d-4fcf-a42b-2754e6b3d00d"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/EFETIVIDADE.xlsx
+++ b/EFETIVIDADE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://spotpromo.sharepoint.com/sites/bko.pribeiro/Documentos Compartilhados/PRibeiro/BAUDUCCO TMP/20 - EFETIVIDADE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="987" documentId="13_ncr:1_{C64068DB-D04A-49E7-B037-1281E1EE8D6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CBA4CB14-EFF3-4BD3-8808-958E7799F316}"/>
+  <xr:revisionPtr revIDLastSave="1000" documentId="13_ncr:1_{C64068DB-D04A-49E7-B037-1281E1EE8D6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61FA25F0-7D05-4368-8BD0-901D816666F8}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1332" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1417" uniqueCount="304">
   <si>
     <t>ROTA</t>
   </si>
@@ -884,13 +884,67 @@
     <t>06:48</t>
   </si>
   <si>
-    <t>07:28</t>
-  </si>
-  <si>
-    <t>07:33</t>
-  </si>
-  <si>
-    <t>08:02</t>
+    <t>07:10  13:53</t>
+  </si>
+  <si>
+    <t>07:28  09:03</t>
+  </si>
+  <si>
+    <t>07:33  11:57</t>
+  </si>
+  <si>
+    <t>08:02  11:16</t>
+  </si>
+  <si>
+    <t>08:47  15:31</t>
+  </si>
+  <si>
+    <t>09:30  11:06</t>
+  </si>
+  <si>
+    <t>11:37  15:32</t>
+  </si>
+  <si>
+    <t>12:34  16:25</t>
+  </si>
+  <si>
+    <t>13:32  16:07</t>
+  </si>
+  <si>
+    <t>14:23  16:06</t>
+  </si>
+  <si>
+    <t>15:41  17:04</t>
+  </si>
+  <si>
+    <t>16:00  18:16</t>
+  </si>
+  <si>
+    <t>16:33  20:39</t>
+  </si>
+  <si>
+    <t>SUPERNOSSO - RUA MARMORE 641, 641 - BELO HORIZONTE/MG</t>
+  </si>
+  <si>
+    <t>CARREFOUR - AV BARAO DO RIO BRANCO, 5001 - JUIZ DE FORA/MG</t>
+  </si>
+  <si>
+    <t>06:39</t>
+  </si>
+  <si>
+    <t>07:06</t>
+  </si>
+  <si>
+    <t>07:39</t>
+  </si>
+  <si>
+    <t>07:43  09:35</t>
+  </si>
+  <si>
+    <t>08:58</t>
+  </si>
+  <si>
+    <t>09:51</t>
   </si>
 </sst>
 </file>
@@ -917,11 +971,13 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1003,7 +1059,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1056,9 +1112,6 @@
     <xf numFmtId="20" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1070,6 +1123,18 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1171,10 +1236,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A4474625-D582-4F1B-AA27-C9E6E4248EEA}" name="Tabela1" displayName="Tabela1" ref="A1:G261" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7" headerRowCellStyle="Normal 2">
-  <autoFilter ref="A1:G261" xr:uid="{A4474625-D582-4F1B-AA27-C9E6E4248EEA}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G261">
-    <sortCondition descending="1" ref="E1:E261"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A4474625-D582-4F1B-AA27-C9E6E4248EEA}" name="Tabela1" displayName="Tabela1" ref="A1:G278" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7" headerRowCellStyle="Normal 2">
+  <autoFilter ref="A1:G278" xr:uid="{A4474625-D582-4F1B-AA27-C9E6E4248EEA}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G278">
+    <sortCondition descending="1" ref="E1:E278"/>
   </sortState>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{8C18829A-5E6C-4A32-820C-446F688CFF40}" name="ROTA" dataDxfId="6"/>
@@ -1506,7 +1571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G261"/>
+  <dimension ref="A1:G278"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" style="4" customWidth="1"/>
@@ -1556,10 +1621,10 @@
         <v>8</v>
       </c>
       <c r="E2" s="7">
-        <v>46183</v>
-      </c>
-      <c r="F2" s="21" t="s">
-        <v>283</v>
+        <v>46184</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>301</v>
       </c>
       <c r="G2" s="5"/>
     </row>
@@ -1571,39 +1636,39 @@
         <v>7</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>73</v>
+        <v>46</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="7">
-        <v>46183</v>
-      </c>
-      <c r="F3" s="8" t="s">
+        <v>46184</v>
+      </c>
+      <c r="F3" s="22" t="s">
         <v>53</v>
       </c>
       <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D4" s="4" t="s">
+      <c r="C4" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="23" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="7">
-        <v>46183</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G4" s="5"/>
+        <v>46184</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>303</v>
+      </c>
+      <c r="G4" s="24"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
@@ -1613,16 +1678,16 @@
         <v>154</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>156</v>
       </c>
       <c r="E5" s="7">
-        <v>46183</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>53</v>
+        <v>46184</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>299</v>
       </c>
       <c r="G5" s="5"/>
     </row>
@@ -1634,37 +1699,37 @@
         <v>154</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>156</v>
       </c>
       <c r="E6" s="7">
-        <v>46183</v>
-      </c>
-      <c r="F6" s="8" t="s">
+        <v>46184</v>
+      </c>
+      <c r="F6" s="22" t="s">
         <v>53</v>
       </c>
       <c r="G6" s="5"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>10</v>
+        <v>154</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E7" s="7">
-        <v>46183</v>
-      </c>
-      <c r="F7" s="21" t="s">
-        <v>284</v>
+        <v>46184</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>53</v>
       </c>
       <c r="G7" s="5"/>
     </row>
@@ -1673,19 +1738,19 @@
         <v>149</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>151</v>
       </c>
       <c r="E8" s="7">
-        <v>46183</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>53</v>
+        <v>46184</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>300</v>
       </c>
       <c r="G8" s="5"/>
     </row>
@@ -1703,93 +1768,93 @@
         <v>151</v>
       </c>
       <c r="E9" s="7">
-        <v>46183</v>
-      </c>
-      <c r="F9" s="8" t="s">
+        <v>46184</v>
+      </c>
+      <c r="F9" s="22" t="s">
         <v>53</v>
       </c>
       <c r="G9" s="5"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>3</v>
+        <v>149</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>28</v>
+        <v>152</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>5</v>
+        <v>151</v>
       </c>
       <c r="E10" s="7">
-        <v>46183</v>
-      </c>
-      <c r="F10" s="21" t="s">
-        <v>282</v>
+        <v>46184</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>53</v>
       </c>
       <c r="G10" s="5"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>3</v>
+        <v>149</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>29</v>
+        <v>184</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>5</v>
+        <v>151</v>
       </c>
       <c r="E11" s="7">
-        <v>46183</v>
-      </c>
-      <c r="F11" s="8" t="s">
+        <v>46184</v>
+      </c>
+      <c r="F11" s="22" t="s">
         <v>53</v>
       </c>
       <c r="G11" s="5"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>158</v>
+        <v>3</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>162</v>
+        <v>28</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>160</v>
+        <v>5</v>
       </c>
       <c r="E12" s="7">
-        <v>46183</v>
-      </c>
-      <c r="F12" s="21" t="s">
-        <v>285</v>
+        <v>46184</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>298</v>
       </c>
       <c r="G12" s="5"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>158</v>
+        <v>3</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>159</v>
+        <v>297</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>160</v>
+        <v>5</v>
       </c>
       <c r="E13" s="7">
-        <v>46183</v>
-      </c>
-      <c r="F13" s="8" t="s">
+        <v>46184</v>
+      </c>
+      <c r="F13" s="22" t="s">
         <v>53</v>
       </c>
       <c r="G13" s="5"/>
@@ -1802,415 +1867,415 @@
         <v>55</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>160</v>
       </c>
       <c r="E14" s="7">
-        <v>46183</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>53</v>
+        <v>46184</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>302</v>
       </c>
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>12</v>
+        <v>158</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>30</v>
+        <v>181</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>13</v>
+        <v>160</v>
       </c>
       <c r="E15" s="7">
-        <v>46183</v>
-      </c>
-      <c r="F15" s="21" t="s">
-        <v>248</v>
+        <v>46184</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>53</v>
       </c>
       <c r="G15" s="5"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>12</v>
+        <v>158</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>95</v>
+        <v>296</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>13</v>
+        <v>160</v>
       </c>
       <c r="E16" s="7">
-        <v>46183</v>
-      </c>
-      <c r="F16" s="8" t="s">
+        <v>46184</v>
+      </c>
+      <c r="F16" s="22" t="s">
         <v>53</v>
       </c>
       <c r="G16" s="5"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E17" s="7">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>270</v>
+        <v>213</v>
       </c>
       <c r="G17" s="5"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="7">
+        <v>46184</v>
+      </c>
+      <c r="F18" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="G18" s="5"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B19" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D18" s="4" t="s">
+      <c r="C19" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" t="s">
         <v>8</v>
       </c>
-      <c r="E18" s="7">
-        <v>46182</v>
-      </c>
-      <c r="F18" s="20" t="s">
-        <v>272</v>
-      </c>
-      <c r="G18" s="5"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
+      <c r="E19" s="7">
+        <v>46183</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="G19" s="5"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>6</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B20" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D19" s="4" t="s">
+      <c r="C20" t="s">
+        <v>73</v>
+      </c>
+      <c r="D20" t="s">
         <v>8</v>
       </c>
-      <c r="E19" s="7">
-        <v>46182</v>
-      </c>
-      <c r="F19" s="21" t="s">
-        <v>275</v>
-      </c>
-      <c r="G19" s="5"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="4" t="s">
+      <c r="E20" s="7">
+        <v>46183</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>288</v>
+      </c>
+      <c r="G20" s="5"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" t="s">
+        <v>71</v>
+      </c>
+      <c r="D21" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="7">
+        <v>46183</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>291</v>
+      </c>
+      <c r="G21" s="5"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>153</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B22" t="s">
         <v>154</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="D20" s="4" t="s">
+      <c r="C22" t="s">
+        <v>155</v>
+      </c>
+      <c r="D22" t="s">
         <v>156</v>
       </c>
-      <c r="E20" s="7">
-        <v>46182</v>
-      </c>
-      <c r="F20" s="20" t="s">
-        <v>266</v>
-      </c>
-      <c r="G20" s="5"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
+      <c r="E22" s="7">
+        <v>46183</v>
+      </c>
+      <c r="F22" s="19" t="s">
+        <v>287</v>
+      </c>
+      <c r="G22" s="5"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>153</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B23" t="s">
         <v>154</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C23" t="s">
         <v>186</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D23" t="s">
         <v>156</v>
       </c>
-      <c r="E21" s="7">
-        <v>46182</v>
-      </c>
-      <c r="F21" s="20" t="s">
-        <v>273</v>
-      </c>
-      <c r="G21" s="5"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="E22" s="7">
-        <v>46182</v>
-      </c>
-      <c r="F22" s="20" t="s">
-        <v>277</v>
-      </c>
-      <c r="G22" s="5"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
+      <c r="E23" s="7">
+        <v>46183</v>
+      </c>
+      <c r="F23" s="19" t="s">
+        <v>293</v>
+      </c>
+      <c r="G23" s="5"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>149</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B24" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C24" t="s">
         <v>150</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D24" t="s">
         <v>151</v>
       </c>
-      <c r="E23" s="7">
-        <v>46182</v>
-      </c>
-      <c r="F23" s="20" t="s">
-        <v>268</v>
-      </c>
-      <c r="G23" s="5"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
+      <c r="E24" s="7">
+        <v>46183</v>
+      </c>
+      <c r="F24" s="19" t="s">
+        <v>285</v>
+      </c>
+      <c r="G24" s="5"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>149</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B25" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25" t="s">
+        <v>187</v>
+      </c>
+      <c r="D25" t="s">
+        <v>151</v>
+      </c>
+      <c r="E25" s="7">
+        <v>46183</v>
+      </c>
+      <c r="F25" s="19" t="s">
+        <v>290</v>
+      </c>
+      <c r="G25" s="5"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>149</v>
+      </c>
+      <c r="B26" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="D24" s="4" t="s">
+      <c r="C26" t="s">
+        <v>212</v>
+      </c>
+      <c r="D26" t="s">
         <v>151</v>
       </c>
-      <c r="E24" s="7">
-        <v>46182</v>
-      </c>
-      <c r="F24" s="20" t="s">
-        <v>276</v>
-      </c>
-      <c r="G24" s="5"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="B25" s="4" t="s">
+      <c r="E26" s="7">
+        <v>46183</v>
+      </c>
+      <c r="F26" s="19" t="s">
+        <v>295</v>
+      </c>
+      <c r="G26" s="5"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>3</v>
+      </c>
+      <c r="B27" t="s">
+        <v>4</v>
+      </c>
+      <c r="C27" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" t="s">
+        <v>5</v>
+      </c>
+      <c r="E27" s="7">
+        <v>46183</v>
+      </c>
+      <c r="F27" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="G27" s="5"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>3</v>
+      </c>
+      <c r="B28" t="s">
+        <v>4</v>
+      </c>
+      <c r="C28" t="s">
+        <v>29</v>
+      </c>
+      <c r="D28" t="s">
+        <v>5</v>
+      </c>
+      <c r="E28" s="7">
+        <v>46183</v>
+      </c>
+      <c r="F28" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="G28" s="5"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>158</v>
+      </c>
+      <c r="B29" t="s">
         <v>55</v>
       </c>
-      <c r="C25" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="E25" s="7">
-        <v>46182</v>
-      </c>
-      <c r="F25" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="G25" s="5"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E26" s="7">
-        <v>46182</v>
-      </c>
-      <c r="F26" s="20" t="s">
-        <v>267</v>
-      </c>
-      <c r="G26" s="5"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E27" s="7">
-        <v>46182</v>
-      </c>
-      <c r="F27" s="20" t="s">
-        <v>278</v>
-      </c>
-      <c r="G27" s="5"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E28" s="7">
-        <v>46182</v>
-      </c>
-      <c r="F28" s="20" t="s">
-        <v>279</v>
-      </c>
-      <c r="G28" s="5"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="4" t="s">
+      <c r="C29" t="s">
+        <v>162</v>
+      </c>
+      <c r="D29" t="s">
+        <v>160</v>
+      </c>
+      <c r="E29" s="7">
+        <v>46183</v>
+      </c>
+      <c r="F29" s="19" t="s">
+        <v>286</v>
+      </c>
+      <c r="G29" s="5"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>158</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B30" t="s">
         <v>55</v>
       </c>
-      <c r="C29" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="D29" s="4" t="s">
+      <c r="C30" t="s">
+        <v>161</v>
+      </c>
+      <c r="D30" t="s">
         <v>160</v>
       </c>
-      <c r="E29" s="7">
-        <v>46182</v>
-      </c>
-      <c r="F29" s="20" t="s">
-        <v>271</v>
-      </c>
-      <c r="G29" s="5"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="4" t="s">
+      <c r="E30" s="7">
+        <v>46183</v>
+      </c>
+      <c r="F30" s="19" t="s">
+        <v>289</v>
+      </c>
+      <c r="G30" s="5"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>158</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B31" t="s">
         <v>55</v>
       </c>
-      <c r="C30" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="D30" s="4" t="s">
+      <c r="C31" t="s">
+        <v>159</v>
+      </c>
+      <c r="D31" t="s">
         <v>160</v>
       </c>
-      <c r="E30" s="7">
-        <v>46182</v>
-      </c>
-      <c r="F30" s="20" t="s">
-        <v>274</v>
-      </c>
-      <c r="G30" s="5"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>160</v>
-      </c>
       <c r="E31" s="7">
-        <v>46182</v>
-      </c>
-      <c r="F31" s="20" t="s">
-        <v>280</v>
+        <v>46183</v>
+      </c>
+      <c r="F31" s="19" t="s">
+        <v>294</v>
       </c>
       <c r="G31" s="5"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="4" t="s">
+      <c r="A32" t="s">
         <v>12</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" t="s">
         <v>9</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" t="s">
         <v>30</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" t="s">
         <v>13</v>
       </c>
       <c r="E32" s="7">
-        <v>46182</v>
-      </c>
-      <c r="F32" s="19" t="s">
-        <v>269</v>
+        <v>46183</v>
+      </c>
+      <c r="F32" s="18" t="s">
+        <v>283</v>
       </c>
       <c r="G32" s="5"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="4" t="s">
+      <c r="A33" t="s">
         <v>12</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" t="s">
         <v>9</v>
       </c>
-      <c r="C33" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D33" s="4" t="s">
+      <c r="C33" t="s">
+        <v>95</v>
+      </c>
+      <c r="D33" t="s">
         <v>13</v>
       </c>
       <c r="E33" s="7">
-        <v>46182</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>53</v>
+        <v>46183</v>
+      </c>
+      <c r="F33" s="18" t="s">
+        <v>292</v>
       </c>
       <c r="G33" s="5"/>
     </row>
@@ -2222,16 +2287,16 @@
         <v>7</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E34" s="7">
-        <v>46181</v>
-      </c>
-      <c r="F34" s="20" t="s">
-        <v>257</v>
+        <v>46182</v>
+      </c>
+      <c r="F34" s="19" t="s">
+        <v>270</v>
       </c>
       <c r="G34" s="5"/>
     </row>
@@ -2243,37 +2308,37 @@
         <v>7</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E35" s="7">
-        <v>46181</v>
-      </c>
-      <c r="F35" s="20" t="s">
-        <v>263</v>
+        <v>46182</v>
+      </c>
+      <c r="F35" s="19" t="s">
+        <v>272</v>
       </c>
       <c r="G35" s="5"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>153</v>
+        <v>6</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>154</v>
+        <v>7</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>155</v>
+        <v>46</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>156</v>
+        <v>8</v>
       </c>
       <c r="E36" s="7">
-        <v>46181</v>
-      </c>
-      <c r="F36" s="19" t="s">
-        <v>254</v>
+        <v>46182</v>
+      </c>
+      <c r="F36" s="20" t="s">
+        <v>275</v>
       </c>
       <c r="G36" s="5"/>
     </row>
@@ -2285,286 +2350,286 @@
         <v>154</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>156</v>
       </c>
       <c r="E37" s="7">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="F37" s="19" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="G37" s="5"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>10</v>
+        <v>154</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>150</v>
+        <v>186</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E38" s="7">
-        <v>46181</v>
-      </c>
-      <c r="F38" s="20" t="s">
-        <v>255</v>
+        <v>46182</v>
+      </c>
+      <c r="F38" s="19" t="s">
+        <v>273</v>
       </c>
       <c r="G38" s="5"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>10</v>
+        <v>154</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>152</v>
+        <v>185</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E39" s="7">
-        <v>46181</v>
-      </c>
-      <c r="F39" s="20" t="s">
-        <v>264</v>
+        <v>46182</v>
+      </c>
+      <c r="F39" s="19" t="s">
+        <v>277</v>
       </c>
       <c r="G39" s="5"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>3</v>
+        <v>149</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>29</v>
+        <v>150</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>5</v>
+        <v>151</v>
       </c>
       <c r="E40" s="7">
-        <v>46181</v>
-      </c>
-      <c r="F40" s="20" t="s">
-        <v>259</v>
+        <v>46182</v>
+      </c>
+      <c r="F40" s="19" t="s">
+        <v>268</v>
       </c>
       <c r="G40" s="5"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
-        <v>3</v>
+        <v>149</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>28</v>
+        <v>184</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>5</v>
+        <v>151</v>
       </c>
       <c r="E41" s="7">
-        <v>46181</v>
-      </c>
-      <c r="F41" s="21" t="s">
-        <v>260</v>
+        <v>46182</v>
+      </c>
+      <c r="F41" s="19" t="s">
+        <v>276</v>
       </c>
       <c r="G41" s="5"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>55</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>159</v>
+        <v>187</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="E42" s="7">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="F42" s="20" t="s">
-        <v>258</v>
+        <v>281</v>
       </c>
       <c r="G42" s="5"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
-        <v>158</v>
+        <v>3</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>161</v>
+        <v>29</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>160</v>
+        <v>5</v>
       </c>
       <c r="E43" s="7">
-        <v>46181</v>
-      </c>
-      <c r="F43" s="20" t="s">
-        <v>261</v>
+        <v>46182</v>
+      </c>
+      <c r="F43" s="19" t="s">
+        <v>267</v>
       </c>
       <c r="G43" s="5"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
-        <v>158</v>
+        <v>3</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>162</v>
+        <v>28</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>160</v>
+        <v>5</v>
       </c>
       <c r="E44" s="7">
-        <v>46181</v>
-      </c>
-      <c r="F44" s="21" t="s">
-        <v>265</v>
+        <v>46182</v>
+      </c>
+      <c r="F44" s="19" t="s">
+        <v>278</v>
       </c>
       <c r="G44" s="5"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E45" s="7">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="F45" s="19" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="G45" s="5"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
-        <v>12</v>
+        <v>158</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>68</v>
+        <v>182</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>13</v>
+        <v>160</v>
       </c>
       <c r="E46" s="7">
-        <v>46181</v>
-      </c>
-      <c r="F46" s="8" t="s">
-        <v>53</v>
+        <v>46182</v>
+      </c>
+      <c r="F46" s="19" t="s">
+        <v>271</v>
       </c>
       <c r="G46" s="5"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
-        <v>6</v>
+        <v>158</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>73</v>
+        <v>183</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>8</v>
+        <v>160</v>
       </c>
       <c r="E47" s="7">
-        <v>46179</v>
-      </c>
-      <c r="F47" s="16" t="s">
-        <v>253</v>
+        <v>46182</v>
+      </c>
+      <c r="F47" s="19" t="s">
+        <v>274</v>
       </c>
       <c r="G47" s="5"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>154</v>
+        <v>55</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E48" s="7">
-        <v>46179</v>
-      </c>
-      <c r="F48" s="16" t="s">
-        <v>248</v>
+        <v>46182</v>
+      </c>
+      <c r="F48" s="19" t="s">
+        <v>280</v>
       </c>
       <c r="G48" s="5"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
-        <v>149</v>
+        <v>12</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>187</v>
+        <v>30</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>151</v>
+        <v>13</v>
       </c>
       <c r="E49" s="7">
-        <v>46179</v>
-      </c>
-      <c r="F49" s="16" t="s">
-        <v>252</v>
+        <v>46182</v>
+      </c>
+      <c r="F49" s="18" t="s">
+        <v>269</v>
       </c>
       <c r="G49" s="5"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E50" s="7">
-        <v>46179</v>
+        <v>46182</v>
       </c>
       <c r="F50" s="8" t="s">
         <v>53</v>
@@ -2573,316 +2638,316 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E51" s="7">
-        <v>46179</v>
-      </c>
-      <c r="F51" s="8" t="s">
-        <v>53</v>
+        <v>46181</v>
+      </c>
+      <c r="F51" s="19" t="s">
+        <v>257</v>
       </c>
       <c r="G51" s="5"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E52" s="7">
-        <v>46179</v>
-      </c>
-      <c r="F52" s="8" t="s">
-        <v>53</v>
+        <v>46181</v>
+      </c>
+      <c r="F52" s="19" t="s">
+        <v>263</v>
       </c>
       <c r="G52" s="5"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>55</v>
+        <v>154</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>183</v>
+        <v>155</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E53" s="7">
-        <v>46179</v>
-      </c>
-      <c r="F53" s="18" t="s">
-        <v>251</v>
+        <v>46181</v>
+      </c>
+      <c r="F53" s="25" t="s">
+        <v>254</v>
       </c>
       <c r="G53" s="5"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
-        <v>19</v>
+        <v>153</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>18</v>
+        <v>154</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>32</v>
+        <v>157</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>20</v>
+        <v>156</v>
       </c>
       <c r="E54" s="7">
-        <v>46179</v>
-      </c>
-      <c r="F54" s="8" t="s">
-        <v>53</v>
+        <v>46181</v>
+      </c>
+      <c r="F54" s="18" t="s">
+        <v>262</v>
       </c>
       <c r="G54" s="5"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
-        <v>11</v>
+        <v>149</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>33</v>
+        <v>150</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>15</v>
+        <v>151</v>
       </c>
       <c r="E55" s="7">
-        <v>46179</v>
-      </c>
-      <c r="F55" s="16" t="s">
-        <v>250</v>
+        <v>46181</v>
+      </c>
+      <c r="F55" s="19" t="s">
+        <v>255</v>
       </c>
       <c r="G55" s="5"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
-        <v>12</v>
+        <v>149</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>95</v>
+        <v>152</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>13</v>
+        <v>151</v>
       </c>
       <c r="E56" s="7">
-        <v>46179</v>
-      </c>
-      <c r="F56" s="16" t="s">
-        <v>249</v>
+        <v>46181</v>
+      </c>
+      <c r="F56" s="19" t="s">
+        <v>264</v>
       </c>
       <c r="G56" s="5"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="E57" s="7">
-        <v>46179</v>
-      </c>
-      <c r="F57" s="8" t="s">
-        <v>53</v>
+        <v>46181</v>
+      </c>
+      <c r="F57" s="19" t="s">
+        <v>259</v>
       </c>
       <c r="G57" s="5"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E58" s="7">
-        <v>46178</v>
-      </c>
-      <c r="F58" s="12" t="s">
-        <v>238</v>
+        <v>46181</v>
+      </c>
+      <c r="F58" s="20" t="s">
+        <v>260</v>
       </c>
       <c r="G58" s="5"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
-        <v>6</v>
+        <v>158</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>73</v>
+        <v>159</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>8</v>
+        <v>160</v>
       </c>
       <c r="E59" s="7">
-        <v>46178</v>
-      </c>
-      <c r="F59" s="12" t="s">
-        <v>239</v>
+        <v>46181</v>
+      </c>
+      <c r="F59" s="19" t="s">
+        <v>258</v>
       </c>
       <c r="G59" s="5"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
-        <v>6</v>
+        <v>158</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>71</v>
+        <v>161</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>8</v>
+        <v>160</v>
       </c>
       <c r="E60" s="7">
-        <v>46178</v>
-      </c>
-      <c r="F60" s="15" t="s">
-        <v>244</v>
+        <v>46181</v>
+      </c>
+      <c r="F60" s="19" t="s">
+        <v>261</v>
       </c>
       <c r="G60" s="5"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>154</v>
+        <v>55</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E61" s="7">
-        <v>46178</v>
-      </c>
-      <c r="F61" s="12" t="s">
-        <v>233</v>
+        <v>46181</v>
+      </c>
+      <c r="F61" s="20" t="s">
+        <v>265</v>
       </c>
       <c r="G61" s="5"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
-        <v>153</v>
+        <v>12</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>154</v>
+        <v>9</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>186</v>
+        <v>30</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>156</v>
+        <v>13</v>
       </c>
       <c r="E62" s="7">
-        <v>46178</v>
-      </c>
-      <c r="F62" s="12" t="s">
-        <v>242</v>
+        <v>46181</v>
+      </c>
+      <c r="F62" s="18" t="s">
+        <v>256</v>
       </c>
       <c r="G62" s="5"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
-        <v>153</v>
+        <v>12</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>154</v>
+        <v>67</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>157</v>
+        <v>68</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>156</v>
+        <v>13</v>
       </c>
       <c r="E63" s="7">
-        <v>46178</v>
-      </c>
-      <c r="F63" s="12" t="s">
-        <v>245</v>
+        <v>46181</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G63" s="5"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
-        <v>149</v>
+        <v>6</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>150</v>
+        <v>73</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>151</v>
+        <v>8</v>
       </c>
       <c r="E64" s="7">
-        <v>46178</v>
-      </c>
-      <c r="F64" s="12" t="s">
-        <v>234</v>
+        <v>46179</v>
+      </c>
+      <c r="F64" s="16" t="s">
+        <v>253</v>
       </c>
       <c r="G64" s="5"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>10</v>
+        <v>154</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E65" s="7">
-        <v>46178</v>
-      </c>
-      <c r="F65" s="12" t="s">
-        <v>240</v>
+        <v>46179</v>
+      </c>
+      <c r="F65" s="16" t="s">
+        <v>248</v>
       </c>
       <c r="G65" s="5"/>
     </row>
@@ -2891,58 +2956,58 @@
         <v>149</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>212</v>
+        <v>187</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>151</v>
       </c>
       <c r="E66" s="7">
-        <v>46178</v>
-      </c>
-      <c r="F66" s="12" t="s">
-        <v>243</v>
+        <v>46179</v>
+      </c>
+      <c r="F66" s="16" t="s">
+        <v>252</v>
       </c>
       <c r="G66" s="5"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
-        <v>149</v>
+        <v>3</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>187</v>
+        <v>28</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>151</v>
+        <v>5</v>
       </c>
       <c r="E67" s="7">
-        <v>46178</v>
-      </c>
-      <c r="F67" s="12" t="s">
-        <v>246</v>
+        <v>46179</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G67" s="5"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E68" s="7">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="F68" s="8" t="s">
         <v>53</v>
@@ -2951,19 +3016,19 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="E69" s="7">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="F69" s="8" t="s">
         <v>53</v>
@@ -2972,40 +3037,40 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
-        <v>16</v>
+        <v>158</v>
       </c>
       <c r="B70" s="4" t="s">
         <v>55</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>56</v>
+        <v>183</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>17</v>
+        <v>160</v>
       </c>
       <c r="E70" s="7">
-        <v>46178</v>
-      </c>
-      <c r="F70" s="12" t="s">
-        <v>237</v>
+        <v>46179</v>
+      </c>
+      <c r="F70" s="16" t="s">
+        <v>251</v>
       </c>
       <c r="G70" s="5"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E71" s="7">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="F71" s="8" t="s">
         <v>53</v>
@@ -3014,61 +3079,61 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E72" s="7">
-        <v>46178</v>
-      </c>
-      <c r="F72" s="12" t="s">
-        <v>241</v>
+        <v>46179</v>
+      </c>
+      <c r="F72" s="16" t="s">
+        <v>250</v>
       </c>
       <c r="G72" s="5"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E73" s="7">
-        <v>46178</v>
-      </c>
-      <c r="F73" s="8" t="s">
-        <v>53</v>
+        <v>46179</v>
+      </c>
+      <c r="F73" s="16" t="s">
+        <v>249</v>
       </c>
       <c r="G73" s="5"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E74" s="7">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="F74" s="8" t="s">
         <v>53</v>
@@ -3077,226 +3142,226 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
-        <v>158</v>
+        <v>6</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>162</v>
+        <v>47</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>160</v>
+        <v>8</v>
       </c>
       <c r="E75" s="7">
         <v>46178</v>
       </c>
       <c r="F75" s="12" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="G75" s="5"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
-        <v>158</v>
+        <v>6</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>161</v>
+        <v>73</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>160</v>
+        <v>8</v>
       </c>
       <c r="E76" s="7">
         <v>46178</v>
       </c>
-      <c r="F76" s="8" t="s">
-        <v>53</v>
+      <c r="F76" s="12" t="s">
+        <v>239</v>
       </c>
       <c r="G76" s="5"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
-        <v>158</v>
+        <v>6</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>159</v>
+        <v>71</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>160</v>
+        <v>8</v>
       </c>
       <c r="E77" s="7">
         <v>46178</v>
       </c>
-      <c r="F77" s="17">
-        <v>0.34930555555555554</v>
+      <c r="F77" s="15" t="s">
+        <v>244</v>
       </c>
       <c r="G77" s="5"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
-        <v>19</v>
+        <v>153</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>91</v>
+        <v>154</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>92</v>
+        <v>155</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>20</v>
+        <v>156</v>
       </c>
       <c r="E78" s="7">
         <v>46178</v>
       </c>
-      <c r="F78" s="8" t="s">
-        <v>53</v>
+      <c r="F78" s="12" t="s">
+        <v>233</v>
       </c>
       <c r="G78" s="5"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
-        <v>19</v>
+        <v>153</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>18</v>
+        <v>154</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>59</v>
+        <v>186</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>20</v>
+        <v>156</v>
       </c>
       <c r="E79" s="7">
         <v>46178</v>
       </c>
-      <c r="F79" s="8" t="s">
-        <v>53</v>
+      <c r="F79" s="12" t="s">
+        <v>242</v>
       </c>
       <c r="G79" s="5"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
-        <v>19</v>
+        <v>153</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>18</v>
+        <v>154</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>93</v>
+        <v>157</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>20</v>
+        <v>156</v>
       </c>
       <c r="E80" s="7">
         <v>46178</v>
       </c>
-      <c r="F80" s="8" t="s">
-        <v>53</v>
+      <c r="F80" s="12" t="s">
+        <v>245</v>
       </c>
       <c r="G80" s="5"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
-        <v>11</v>
+        <v>149</v>
       </c>
       <c r="B81" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>14</v>
+        <v>150</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>15</v>
+        <v>151</v>
       </c>
       <c r="E81" s="7">
         <v>46178</v>
       </c>
-      <c r="F81" s="8" t="s">
-        <v>53</v>
+      <c r="F81" s="12" t="s">
+        <v>234</v>
       </c>
       <c r="G81" s="5"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
-        <v>11</v>
+        <v>149</v>
       </c>
       <c r="B82" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>90</v>
+        <v>184</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>15</v>
+        <v>151</v>
       </c>
       <c r="E82" s="7">
         <v>46178</v>
       </c>
-      <c r="F82" s="8" t="s">
-        <v>53</v>
+      <c r="F82" s="12" t="s">
+        <v>240</v>
       </c>
       <c r="G82" s="5"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
-        <v>12</v>
+        <v>149</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>30</v>
+        <v>212</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>13</v>
+        <v>151</v>
       </c>
       <c r="E83" s="7">
         <v>46178</v>
       </c>
-      <c r="F83" s="13" t="s">
-        <v>236</v>
+      <c r="F83" s="12" t="s">
+        <v>243</v>
       </c>
       <c r="G83" s="5"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
-        <v>12</v>
+        <v>149</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>68</v>
+        <v>187</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>13</v>
+        <v>151</v>
       </c>
       <c r="E84" s="7">
         <v>46178</v>
       </c>
-      <c r="F84" s="13" t="s">
-        <v>247</v>
+      <c r="F84" s="12" t="s">
+        <v>246</v>
       </c>
       <c r="G84" s="5"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="E85" s="7">
         <v>46178</v>
@@ -3308,16 +3373,16 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="E86" s="7">
         <v>46178</v>
@@ -3329,1350 +3394,1350 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E87" s="7">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="F87" s="12" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="G87" s="5"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E88" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F88" s="12" t="s">
-        <v>222</v>
+        <v>46178</v>
+      </c>
+      <c r="F88" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G88" s="5"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E89" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F89" s="15" t="s">
-        <v>227</v>
+        <v>46178</v>
+      </c>
+      <c r="F89" s="12" t="s">
+        <v>241</v>
       </c>
       <c r="G89" s="5"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>154</v>
+        <v>22</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>155</v>
+        <v>60</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>156</v>
+        <v>23</v>
       </c>
       <c r="E90" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F90" s="12" t="s">
-        <v>217</v>
+        <v>46178</v>
+      </c>
+      <c r="F90" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G90" s="5"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>154</v>
+        <v>22</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>186</v>
+        <v>94</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>156</v>
+        <v>23</v>
       </c>
       <c r="E91" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F91" s="12" t="s">
-        <v>228</v>
+        <v>46178</v>
+      </c>
+      <c r="F91" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G91" s="5"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="E92" s="7">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="F92" s="12" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="G92" s="5"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="B93" s="4" t="s">
         <v>55</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>187</v>
+        <v>161</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="E93" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F93" s="12" t="s">
-        <v>223</v>
+        <v>46178</v>
+      </c>
+      <c r="F93" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G93" s="5"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>212</v>
+        <v>159</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="E94" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F94" s="12" t="s">
-        <v>229</v>
+        <v>46178</v>
+      </c>
+      <c r="F94" s="17">
+        <v>0.34930555555555554</v>
       </c>
       <c r="G94" s="5"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>4</v>
+        <v>91</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>29</v>
+        <v>92</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E95" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F95" s="13" t="s">
-        <v>216</v>
+        <v>46178</v>
+      </c>
+      <c r="F95" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G95" s="5"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E96" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F96" s="13" t="s">
-        <v>224</v>
+        <v>46178</v>
+      </c>
+      <c r="F96" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G96" s="5"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B97" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E97" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F97" s="13" t="s">
-        <v>221</v>
+        <v>46178</v>
+      </c>
+      <c r="F97" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G97" s="5"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E98" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F98" s="14" t="s">
+        <v>46178</v>
+      </c>
+      <c r="F98" s="8" t="s">
         <v>53</v>
       </c>
       <c r="G98" s="5"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E99" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F99" s="12" t="s">
-        <v>214</v>
+        <v>46178</v>
+      </c>
+      <c r="F99" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G99" s="5"/>
     </row>
-    <row r="100" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>94</v>
+        <v>30</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E100" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F100" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="G100" s="5" t="s">
-        <v>163</v>
-      </c>
+        <v>46178</v>
+      </c>
+      <c r="F100" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="G100" s="5"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
-        <v>158</v>
+        <v>12</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>159</v>
+        <v>68</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>160</v>
+        <v>13</v>
       </c>
       <c r="E101" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F101" s="12" t="s">
-        <v>225</v>
+        <v>46178</v>
+      </c>
+      <c r="F101" s="13" t="s">
+        <v>247</v>
       </c>
       <c r="G101" s="5"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
-        <v>158</v>
+        <v>24</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>161</v>
+        <v>27</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>160</v>
+        <v>26</v>
       </c>
       <c r="E102" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F102" s="12" t="s">
-        <v>231</v>
+        <v>46178</v>
+      </c>
+      <c r="F102" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G102" s="5"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
-        <v>158</v>
+        <v>24</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>162</v>
+        <v>62</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>160</v>
+        <v>26</v>
       </c>
       <c r="E103" s="7">
-        <v>46176</v>
-      </c>
-      <c r="F103" s="15" t="s">
-        <v>232</v>
+        <v>46178</v>
+      </c>
+      <c r="F103" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G103" s="5"/>
     </row>
-    <row r="104" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>91</v>
+        <v>7</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>92</v>
+        <v>47</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E104" s="7">
         <v>46176</v>
       </c>
-      <c r="F104" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="G104" s="5" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F104" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="G104" s="5"/>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E105" s="7">
         <v>46176</v>
       </c>
-      <c r="F105" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="G105" s="5" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F105" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="G105" s="5"/>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E106" s="7">
         <v>46176</v>
       </c>
-      <c r="F106" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="G106" s="5" t="s">
-        <v>163</v>
-      </c>
+      <c r="F106" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="G106" s="5"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
-        <v>11</v>
+        <v>153</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>10</v>
+        <v>154</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>14</v>
+        <v>155</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>15</v>
+        <v>156</v>
       </c>
       <c r="E107" s="7">
         <v>46176</v>
       </c>
-      <c r="F107" s="15" t="s">
-        <v>213</v>
+      <c r="F107" s="12" t="s">
+        <v>217</v>
       </c>
       <c r="G107" s="5"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
-        <v>11</v>
+        <v>153</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>10</v>
+        <v>154</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>90</v>
+        <v>186</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>15</v>
+        <v>156</v>
       </c>
       <c r="E108" s="7">
         <v>46176</v>
       </c>
-      <c r="F108" s="14" t="s">
-        <v>53</v>
+      <c r="F108" s="12" t="s">
+        <v>228</v>
       </c>
       <c r="G108" s="5"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
-        <v>12</v>
+        <v>149</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>13</v>
+        <v>151</v>
       </c>
       <c r="E109" s="7">
         <v>46176</v>
       </c>
-      <c r="F109" s="13" t="s">
-        <v>220</v>
+      <c r="F109" s="12" t="s">
+        <v>218</v>
       </c>
       <c r="G109" s="5"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" s="4" t="s">
-        <v>12</v>
+        <v>149</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>95</v>
+        <v>187</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>13</v>
+        <v>151</v>
       </c>
       <c r="E110" s="7">
         <v>46176</v>
       </c>
-      <c r="F110" s="13" t="s">
-        <v>230</v>
+      <c r="F110" s="12" t="s">
+        <v>223</v>
       </c>
       <c r="G110" s="5"/>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>62</v>
+        <v>212</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>26</v>
+        <v>151</v>
       </c>
       <c r="E111" s="7">
         <v>46176</v>
       </c>
       <c r="F111" s="12" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="G111" s="5"/>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" s="4" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="E112" s="7">
         <v>46176</v>
       </c>
-      <c r="F112" s="15" t="s">
-        <v>226</v>
+      <c r="F112" s="13" t="s">
+        <v>216</v>
       </c>
       <c r="G112" s="5"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" s="4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E113" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F113" s="12" t="s">
-        <v>197</v>
+        <v>46176</v>
+      </c>
+      <c r="F113" s="13" t="s">
+        <v>224</v>
       </c>
       <c r="G113" s="5"/>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E114" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F114" s="12" t="s">
-        <v>204</v>
+        <v>46176</v>
+      </c>
+      <c r="F114" s="13" t="s">
+        <v>221</v>
       </c>
       <c r="G114" s="5"/>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E115" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F115" s="12" t="s">
-        <v>208</v>
+        <v>46176</v>
+      </c>
+      <c r="F115" s="14" t="s">
+        <v>53</v>
       </c>
       <c r="G115" s="5"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" s="4" t="s">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>154</v>
+        <v>22</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>156</v>
+        <v>23</v>
       </c>
       <c r="E116" s="7">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="F116" s="12" t="s">
-        <v>191</v>
+        <v>214</v>
       </c>
       <c r="G116" s="5"/>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>154</v>
+        <v>22</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>185</v>
+        <v>94</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>156</v>
+        <v>23</v>
       </c>
       <c r="E117" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F117" s="12" t="s">
-        <v>202</v>
-      </c>
-      <c r="G117" s="5"/>
+        <v>46176</v>
+      </c>
+      <c r="F117" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="G117" s="5" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" s="4" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>154</v>
+        <v>55</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>186</v>
+        <v>159</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E118" s="7">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="F118" s="12" t="s">
-        <v>206</v>
+        <v>225</v>
       </c>
       <c r="G118" s="5"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="E119" s="7">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="F119" s="12" t="s">
-        <v>193</v>
+        <v>231</v>
       </c>
       <c r="G119" s="5"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" s="4" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="E120" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F120" s="12" t="s">
-        <v>201</v>
+        <v>46176</v>
+      </c>
+      <c r="F120" s="15" t="s">
+        <v>232</v>
       </c>
       <c r="G120" s="5"/>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
-        <v>149</v>
+        <v>19</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>187</v>
+        <v>92</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>151</v>
+        <v>20</v>
       </c>
       <c r="E121" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F121" s="12" t="s">
-        <v>210</v>
-      </c>
-      <c r="G121" s="5"/>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+        <v>46176</v>
+      </c>
+      <c r="F121" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="G121" s="5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A122" s="4" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E122" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F122" s="13" t="s">
-        <v>189</v>
-      </c>
-      <c r="G122" s="5"/>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+        <v>46176</v>
+      </c>
+      <c r="F122" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="G122" s="5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A123" s="4" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>28</v>
+        <v>93</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E123" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F123" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="G123" s="5"/>
+        <v>46176</v>
+      </c>
+      <c r="F123" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="G123" s="5" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" s="4" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E124" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F124" s="13" t="s">
-        <v>203</v>
+        <v>46176</v>
+      </c>
+      <c r="F124" s="15" t="s">
+        <v>213</v>
       </c>
       <c r="G124" s="5"/>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" s="4" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E125" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F125" s="12" t="s">
-        <v>194</v>
+        <v>46176</v>
+      </c>
+      <c r="F125" s="14" t="s">
+        <v>53</v>
       </c>
       <c r="G125" s="5"/>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E126" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F126" s="8" t="s">
-        <v>53</v>
+        <v>46176</v>
+      </c>
+      <c r="F126" s="13" t="s">
+        <v>220</v>
       </c>
       <c r="G126" s="5"/>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" s="4" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E127" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F127" s="12" t="s">
-        <v>188</v>
+        <v>46176</v>
+      </c>
+      <c r="F127" s="13" t="s">
+        <v>230</v>
       </c>
       <c r="G127" s="5"/>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E128" s="7">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="F128" s="12" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="G128" s="5"/>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E129" s="7">
-        <v>46175</v>
-      </c>
-      <c r="F129" s="12" t="s">
-        <v>205</v>
+        <v>46176</v>
+      </c>
+      <c r="F129" s="15" t="s">
+        <v>226</v>
       </c>
       <c r="G129" s="5"/>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" s="4" t="s">
-        <v>158</v>
+        <v>6</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>181</v>
+        <v>47</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>160</v>
+        <v>8</v>
       </c>
       <c r="E130" s="7">
         <v>46175</v>
       </c>
       <c r="F130" s="12" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="G130" s="5"/>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" s="4" t="s">
-        <v>158</v>
+        <v>6</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>182</v>
+        <v>48</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>160</v>
+        <v>8</v>
       </c>
       <c r="E131" s="7">
         <v>46175</v>
       </c>
-      <c r="F131" s="8" t="s">
-        <v>53</v>
+      <c r="F131" s="12" t="s">
+        <v>204</v>
       </c>
       <c r="G131" s="5"/>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" s="4" t="s">
-        <v>158</v>
+        <v>6</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>183</v>
+        <v>46</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>160</v>
+        <v>8</v>
       </c>
       <c r="E132" s="7">
         <v>46175</v>
       </c>
       <c r="F132" s="12" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="G132" s="5"/>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" s="4" t="s">
-        <v>19</v>
+        <v>153</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>18</v>
+        <v>154</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>32</v>
+        <v>180</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>20</v>
+        <v>156</v>
       </c>
       <c r="E133" s="7">
         <v>46175</v>
       </c>
-      <c r="F133" s="8" t="s">
-        <v>53</v>
+      <c r="F133" s="12" t="s">
+        <v>191</v>
       </c>
       <c r="G133" s="5"/>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" s="4" t="s">
-        <v>19</v>
+        <v>153</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>18</v>
+        <v>154</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>37</v>
+        <v>185</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>20</v>
+        <v>156</v>
       </c>
       <c r="E134" s="7">
         <v>46175</v>
       </c>
-      <c r="F134" s="8" t="s">
-        <v>53</v>
+      <c r="F134" s="12" t="s">
+        <v>202</v>
       </c>
       <c r="G134" s="5"/>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" s="4" t="s">
-        <v>11</v>
+        <v>153</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>10</v>
+        <v>154</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>14</v>
+        <v>186</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>15</v>
+        <v>156</v>
       </c>
       <c r="E135" s="7">
         <v>46175</v>
       </c>
       <c r="F135" s="12" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="G135" s="5"/>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" s="4" t="s">
-        <v>11</v>
+        <v>149</v>
       </c>
       <c r="B136" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>33</v>
+        <v>150</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>15</v>
+        <v>151</v>
       </c>
       <c r="E136" s="7">
         <v>46175</v>
       </c>
       <c r="F136" s="12" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="G136" s="5"/>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" s="4" t="s">
-        <v>12</v>
+        <v>149</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>30</v>
+        <v>184</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>13</v>
+        <v>151</v>
       </c>
       <c r="E137" s="7">
         <v>46175</v>
       </c>
-      <c r="F137" s="13" t="s">
-        <v>196</v>
+      <c r="F137" s="12" t="s">
+        <v>201</v>
       </c>
       <c r="G137" s="5"/>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" s="4" t="s">
-        <v>12</v>
+        <v>149</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>45</v>
+        <v>187</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>13</v>
+        <v>151</v>
       </c>
       <c r="E138" s="7">
         <v>46175</v>
       </c>
-      <c r="F138" s="13" t="s">
-        <v>211</v>
+      <c r="F138" s="12" t="s">
+        <v>210</v>
       </c>
       <c r="G138" s="5"/>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" s="4" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="E139" s="7">
         <v>46175</v>
       </c>
-      <c r="F139" s="12" t="s">
-        <v>190</v>
+      <c r="F139" s="13" t="s">
+        <v>189</v>
       </c>
       <c r="G139" s="5"/>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" s="4" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="E140" s="7">
         <v>46175</v>
       </c>
-      <c r="F140" s="12" t="s">
-        <v>209</v>
+      <c r="F140" s="13" t="s">
+        <v>199</v>
       </c>
       <c r="G140" s="5"/>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" s="4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>73</v>
+        <v>44</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E141" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F141" s="12" t="s">
-        <v>169</v>
+        <v>46175</v>
+      </c>
+      <c r="F141" s="13" t="s">
+        <v>203</v>
       </c>
       <c r="G141" s="5"/>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" s="4" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E142" s="7">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="F142" s="12" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="G142" s="5"/>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" s="4" t="s">
-        <v>153</v>
+        <v>16</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>154</v>
+        <v>18</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>155</v>
+        <v>34</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>156</v>
+        <v>17</v>
       </c>
       <c r="E143" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F143" s="12" t="s">
-        <v>171</v>
+        <v>46175</v>
+      </c>
+      <c r="F143" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G143" s="5"/>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" s="4" t="s">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>154</v>
+        <v>39</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>157</v>
+        <v>40</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>156</v>
+        <v>23</v>
       </c>
       <c r="E144" s="7">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="F144" s="12" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="G144" s="5"/>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" s="4" t="s">
-        <v>149</v>
+        <v>21</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>150</v>
+        <v>41</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>151</v>
+        <v>23</v>
       </c>
       <c r="E145" s="7">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="F145" s="12" t="s">
-        <v>168</v>
+        <v>198</v>
       </c>
       <c r="G145" s="5"/>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" s="4" t="s">
-        <v>149</v>
+        <v>21</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>152</v>
+        <v>38</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>151</v>
+        <v>23</v>
       </c>
       <c r="E146" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F146" s="15" t="s">
-        <v>178</v>
+        <v>46175</v>
+      </c>
+      <c r="F146" s="12" t="s">
+        <v>205</v>
       </c>
       <c r="G146" s="5"/>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" s="4" t="s">
-        <v>3</v>
+        <v>158</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>29</v>
+        <v>181</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>5</v>
+        <v>160</v>
       </c>
       <c r="E147" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F147" s="13" t="s">
-        <v>166</v>
+        <v>46175</v>
+      </c>
+      <c r="F147" s="12" t="s">
+        <v>192</v>
       </c>
       <c r="G147" s="5"/>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" s="4" t="s">
-        <v>3</v>
+        <v>158</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>28</v>
+        <v>182</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>5</v>
+        <v>160</v>
       </c>
       <c r="E148" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F148" s="13" t="s">
-        <v>174</v>
+        <v>46175</v>
+      </c>
+      <c r="F148" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G148" s="5"/>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" s="4" t="s">
-        <v>16</v>
+        <v>158</v>
       </c>
       <c r="B149" s="4" t="s">
         <v>55</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>56</v>
+        <v>183</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>17</v>
+        <v>160</v>
       </c>
       <c r="E149" s="7">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="F149" s="12" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="G149" s="5"/>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B150" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E150" s="7">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="F150" s="8" t="s">
         <v>53</v>
@@ -4681,716 +4746,708 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E151" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F151" s="12" t="s">
-        <v>167</v>
+        <v>46175</v>
+      </c>
+      <c r="F151" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G151" s="5"/>
     </row>
-    <row r="152" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" s="4" t="s">
-        <v>158</v>
+        <v>11</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>159</v>
+        <v>14</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
       <c r="E152" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F152" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G152" s="5" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>46175</v>
+      </c>
+      <c r="F152" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="G152" s="5"/>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" s="4" t="s">
-        <v>158</v>
+        <v>11</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>161</v>
+        <v>33</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>160</v>
+        <v>15</v>
       </c>
       <c r="E153" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F153" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G153" s="5" t="s">
-        <v>163</v>
-      </c>
+        <v>46175</v>
+      </c>
+      <c r="F153" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="G153" s="5"/>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" s="4" t="s">
-        <v>158</v>
+        <v>12</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>162</v>
+        <v>30</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>160</v>
+        <v>13</v>
       </c>
       <c r="E154" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F154" s="15" t="s">
-        <v>179</v>
+        <v>46175</v>
+      </c>
+      <c r="F154" s="13" t="s">
+        <v>196</v>
       </c>
       <c r="G154" s="5"/>
     </row>
-    <row r="155" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" s="4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E155" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F155" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G155" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>46175</v>
+      </c>
+      <c r="F155" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="G155" s="5"/>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" s="4" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E156" s="7">
-        <v>46174</v>
-      </c>
-      <c r="F156" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G156" s="5" t="s">
-        <v>31</v>
-      </c>
+        <v>46175</v>
+      </c>
+      <c r="F156" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="G156" s="5"/>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" s="4" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E157" s="7">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="F157" s="12" t="s">
-        <v>170</v>
+        <v>209</v>
       </c>
       <c r="G157" s="5"/>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" s="4" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E158" s="7">
         <v>46174</v>
       </c>
-      <c r="F158" s="13" t="s">
-        <v>172</v>
+      <c r="F158" s="12" t="s">
+        <v>169</v>
       </c>
       <c r="G158" s="5"/>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" s="4" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>67</v>
+        <v>7</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E159" s="7">
         <v>46174</v>
       </c>
-      <c r="F159" s="8" t="s">
-        <v>53</v>
+      <c r="F159" s="12" t="s">
+        <v>176</v>
       </c>
       <c r="G159" s="5"/>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" s="4" t="s">
-        <v>24</v>
+        <v>153</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>25</v>
+        <v>154</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>62</v>
+        <v>155</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>26</v>
+        <v>156</v>
       </c>
       <c r="E160" s="7">
         <v>46174</v>
       </c>
       <c r="F160" s="12" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="G160" s="5"/>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" s="4" t="s">
-        <v>24</v>
+        <v>153</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>25</v>
+        <v>154</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>27</v>
+        <v>157</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>26</v>
+        <v>156</v>
       </c>
       <c r="E161" s="7">
         <v>46174</v>
       </c>
       <c r="F161" s="12" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G161" s="5"/>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162" s="4" t="s">
-        <v>6</v>
+        <v>149</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>73</v>
+        <v>150</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>8</v>
+        <v>151</v>
       </c>
       <c r="E162" s="7">
-        <v>46172</v>
+        <v>46174</v>
       </c>
       <c r="F162" s="12" t="s">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="G162" s="5"/>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163" s="4" t="s">
-        <v>3</v>
+        <v>149</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>28</v>
+        <v>152</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>5</v>
+        <v>151</v>
       </c>
       <c r="E163" s="7">
-        <v>46172</v>
-      </c>
-      <c r="F163" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G163" s="5" t="s">
-        <v>164</v>
-      </c>
+        <v>46174</v>
+      </c>
+      <c r="F163" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="G163" s="5"/>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" s="4" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E164" s="7">
-        <v>46172</v>
-      </c>
-      <c r="F164" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="G164" s="6"/>
+        <v>46174</v>
+      </c>
+      <c r="F164" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="G164" s="5"/>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" s="4" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="E165" s="7">
-        <v>46172</v>
-      </c>
-      <c r="F165" s="12" t="s">
-        <v>144</v>
+        <v>46174</v>
+      </c>
+      <c r="F165" s="13" t="s">
+        <v>174</v>
       </c>
       <c r="G165" s="5"/>
     </row>
-    <row r="166" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E166" s="7">
-        <v>46172</v>
-      </c>
-      <c r="F166" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G166" s="5" t="s">
-        <v>31</v>
-      </c>
+        <v>46174</v>
+      </c>
+      <c r="F166" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="G166" s="5"/>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" s="4" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E167" s="7">
-        <v>46172</v>
-      </c>
-      <c r="F167" s="12" t="s">
-        <v>145</v>
+        <v>46174</v>
+      </c>
+      <c r="F167" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="G167" s="5"/>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" s="4" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E168" s="7">
-        <v>46172</v>
-      </c>
-      <c r="F168" s="13" t="s">
-        <v>147</v>
+        <v>46174</v>
+      </c>
+      <c r="F168" s="12" t="s">
+        <v>167</v>
       </c>
       <c r="G168" s="5"/>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A169" s="4" t="s">
-        <v>24</v>
+        <v>158</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>42</v>
+        <v>159</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>26</v>
+        <v>160</v>
       </c>
       <c r="E169" s="7">
-        <v>46172</v>
-      </c>
-      <c r="F169" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="G169" s="5"/>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+        <v>46174</v>
+      </c>
+      <c r="F169" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G169" s="5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A170" s="4" t="s">
-        <v>6</v>
+        <v>158</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>47</v>
+        <v>161</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>8</v>
+        <v>160</v>
       </c>
       <c r="E170" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F170" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="G170" s="5"/>
+        <v>46174</v>
+      </c>
+      <c r="F170" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G170" s="5" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" s="4" t="s">
-        <v>6</v>
+        <v>158</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>73</v>
+        <v>162</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>8</v>
+        <v>160</v>
       </c>
       <c r="E171" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F171" s="12" t="s">
-        <v>135</v>
+        <v>46174</v>
+      </c>
+      <c r="F171" s="15" t="s">
+        <v>179</v>
       </c>
       <c r="G171" s="5"/>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A172" s="4" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E172" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F172" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="G172" s="5"/>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+        <v>46174</v>
+      </c>
+      <c r="F172" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G172" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A173" s="4" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E173" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F173" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="G173" s="5"/>
+        <v>46174</v>
+      </c>
+      <c r="F173" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G173" s="5" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" s="4" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E174" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F174" s="13" t="s">
-        <v>136</v>
+        <v>46174</v>
+      </c>
+      <c r="F174" s="12" t="s">
+        <v>170</v>
       </c>
       <c r="G174" s="5"/>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E175" s="7">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="F175" s="13" t="s">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="G175" s="5"/>
     </row>
-    <row r="176" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E176" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F176" s="14" t="s">
+        <v>46174</v>
+      </c>
+      <c r="F176" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="G176" s="5" t="s">
-        <v>31</v>
-      </c>
+      <c r="G176" s="5"/>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177" s="4" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E177" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F177" s="13" t="s">
-        <v>142</v>
+        <v>46174</v>
+      </c>
+      <c r="F177" s="12" t="s">
+        <v>165</v>
       </c>
       <c r="G177" s="5"/>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E178" s="7">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="F178" s="12" t="s">
-        <v>131</v>
+        <v>175</v>
       </c>
       <c r="G178" s="5"/>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A179" s="4" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E179" s="7">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="F179" s="12" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="G179" s="5"/>
     </row>
-    <row r="180" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A180" s="4" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>91</v>
+        <v>4</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>92</v>
+        <v>28</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E180" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F180" s="14" t="s">
+        <v>46172</v>
+      </c>
+      <c r="F180" s="8" t="s">
         <v>53</v>
       </c>
       <c r="G180" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A181" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B181" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="D181" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E181" s="7">
+        <v>46172</v>
+      </c>
+      <c r="F181" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="G181" s="6"/>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A182" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B182" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C182" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D182" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E182" s="7">
+        <v>46172</v>
+      </c>
+      <c r="F182" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="G182" s="5"/>
+    </row>
+    <row r="183" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A183" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B183" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C183" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D183" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E181" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F181" s="14" t="s">
+      <c r="E183" s="7">
+        <v>46172</v>
+      </c>
+      <c r="F183" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="G181" s="5" t="s">
+      <c r="G183" s="5" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="182" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A182" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B182" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C182" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="D182" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E182" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F182" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="G182" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A183" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B183" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C183" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D183" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E183" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F183" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="G183" s="5"/>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A184" s="4" t="s">
@@ -5400,16 +5457,16 @@
         <v>10</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="D184" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E184" s="7">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="F184" s="12" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="G184" s="5"/>
     </row>
@@ -5421,79 +5478,79 @@
         <v>9</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="D185" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E185" s="7">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="F185" s="13" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="G185" s="5"/>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A186" s="4" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E186" s="7">
-        <v>46171</v>
-      </c>
-      <c r="F186" s="13" t="s">
-        <v>141</v>
+        <v>46172</v>
+      </c>
+      <c r="F186" s="12" t="s">
+        <v>143</v>
       </c>
       <c r="G186" s="5"/>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A187" s="4" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="E187" s="7">
         <v>46171</v>
       </c>
       <c r="F187" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G187" s="5"/>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A188" s="4" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="E188" s="7">
         <v>46171</v>
       </c>
       <c r="F188" s="12" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G188" s="5"/>
     </row>
@@ -5505,504 +5562,522 @@
         <v>7</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="D189" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E189" s="7">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="F189" s="12" t="s">
-        <v>114</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="G189" s="5"/>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A190" s="4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="D190" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E190" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F190" s="12" t="s">
-        <v>120</v>
+        <v>46171</v>
+      </c>
+      <c r="F190" s="13" t="s">
+        <v>129</v>
       </c>
       <c r="G190" s="5"/>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A191" s="4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="D191" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E191" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F191" s="15" t="s">
-        <v>125</v>
-      </c>
+        <v>46171</v>
+      </c>
+      <c r="F191" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="G191" s="5"/>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A192" s="4" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="D192" s="4" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E192" s="7">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="F192" s="13" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
+        <v>134</v>
+      </c>
+      <c r="G192" s="5"/>
+    </row>
+    <row r="193" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A193" s="4" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D193" s="4" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E193" s="7">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="F193" s="14" t="s">
         <v>53</v>
       </c>
+      <c r="G193" s="5" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A194" s="4" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D194" s="4" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E194" s="7">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="F194" s="13" t="s">
-        <v>127</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="G194" s="5"/>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A195" s="4" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="D195" s="4" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E195" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F195" s="22" t="s">
-        <v>118</v>
-      </c>
+        <v>46171</v>
+      </c>
+      <c r="F195" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="G195" s="5"/>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A196" s="4" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B196" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C196" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D196" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E196" s="7">
+        <v>46171</v>
+      </c>
+      <c r="F196" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="G196" s="5"/>
+    </row>
+    <row r="197" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A197" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B197" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C197" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D197" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E197" s="7">
+        <v>46171</v>
+      </c>
+      <c r="F197" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="G197" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A198" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B198" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C196" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D196" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E196" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F196" s="14" t="s">
+      <c r="C198" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D198" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E198" s="7">
+        <v>46171</v>
+      </c>
+      <c r="F198" s="14" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A197" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B197" s="4" t="s">
+      <c r="G198" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A199" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B199" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C197" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D197" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E197" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F197" s="12" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A198" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B198" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C198" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D198" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E198" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F198" s="12" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A199" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B199" s="4" t="s">
-        <v>39</v>
-      </c>
       <c r="C199" s="4" t="s">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="D199" s="4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E199" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F199" s="12" t="s">
-        <v>119</v>
+        <v>46171</v>
+      </c>
+      <c r="F199" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="G199" s="5" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A200" s="4" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="D200" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E200" s="7">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="F200" s="12" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="201" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+      <c r="G200" s="5"/>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A201" s="4" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>37</v>
+        <v>90</v>
       </c>
       <c r="D201" s="4" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E201" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F201" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="G201" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="202" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>46171</v>
+      </c>
+      <c r="F201" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="G201" s="5"/>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A202" s="4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C202" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D202" s="4" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E202" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F202" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="G202" s="5" t="s">
-        <v>31</v>
-      </c>
+        <v>46171</v>
+      </c>
+      <c r="F202" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="G202" s="5"/>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A203" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="C203" s="4" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="D203" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E203" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F203" s="12" t="s">
-        <v>117</v>
-      </c>
+        <v>46171</v>
+      </c>
+      <c r="F203" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="G203" s="5"/>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A204" s="4" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="D204" s="4" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E204" s="7">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="F204" s="12" t="s">
-        <v>126</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="G204" s="5"/>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A205" s="4" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="C205" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D205" s="4" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E205" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F205" s="13" t="s">
-        <v>115</v>
-      </c>
+        <v>46171</v>
+      </c>
+      <c r="F205" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="G205" s="5"/>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A206" s="4" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D206" s="4" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E206" s="7">
         <v>46170</v>
       </c>
-      <c r="F206" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="G206" s="5"/>
+      <c r="F206" s="12" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A207" s="4" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="C207" s="4" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D207" s="4" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="E207" s="7">
         <v>46170</v>
       </c>
       <c r="F207" s="12" t="s">
-        <v>113</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="G207" s="5"/>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A208" s="4" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="C208" s="4" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="D208" s="4" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="E208" s="7">
         <v>46170</v>
       </c>
-      <c r="F208" s="12" t="s">
-        <v>123</v>
+      <c r="F208" s="15" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A209" s="4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C209" s="4" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="D209" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E209" s="7">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="F209" s="13" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A210" s="4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C210" s="4" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="D210" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E210" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F210" s="13" t="s">
-        <v>98</v>
+        <v>46170</v>
+      </c>
+      <c r="F210" s="14" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A211" s="4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C211" s="4" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="D211" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E211" s="7">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="F211" s="13" t="s">
-        <v>99</v>
+        <v>127</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A212" s="4" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C212" s="4" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D212" s="4" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E212" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F212" s="13" t="s">
-        <v>100</v>
+        <v>46170</v>
+      </c>
+      <c r="F212" s="12" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A213" s="4" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C213" s="4" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="D213" s="4" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E213" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F213" s="13" t="s">
-        <v>101</v>
+        <v>46170</v>
+      </c>
+      <c r="F213" s="14" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.3">
@@ -6010,39 +6085,39 @@
         <v>16</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="C214" s="4" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="D214" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E214" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F214" s="13" t="s">
-        <v>102</v>
+        <v>46170</v>
+      </c>
+      <c r="F214" s="12" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A215" s="4" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="C215" s="4" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="D215" s="4" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E215" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F215" s="8" t="s">
-        <v>53</v>
+        <v>46170</v>
+      </c>
+      <c r="F215" s="12" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.3">
@@ -6050,19 +6125,19 @@
         <v>21</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="C216" s="4" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="D216" s="4" t="s">
         <v>23</v>
       </c>
       <c r="E216" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F216" s="13" t="s">
-        <v>103</v>
+        <v>46170</v>
+      </c>
+      <c r="F216" s="12" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.3">
@@ -6073,42 +6148,42 @@
         <v>22</v>
       </c>
       <c r="C217" s="4" t="s">
-        <v>94</v>
+        <v>38</v>
       </c>
       <c r="D217" s="4" t="s">
         <v>23</v>
       </c>
       <c r="E217" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F217" s="13" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
+        <v>46170</v>
+      </c>
+      <c r="F217" s="12" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A218" s="4" t="s">
         <v>19</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>91</v>
+        <v>18</v>
       </c>
       <c r="C218" s="4" t="s">
-        <v>92</v>
+        <v>37</v>
       </c>
       <c r="D218" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E218" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F218" s="8" t="s">
+        <v>46170</v>
+      </c>
+      <c r="F218" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="G218" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G218" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A219" s="4" t="s">
         <v>19</v>
       </c>
@@ -6116,42 +6191,39 @@
         <v>18</v>
       </c>
       <c r="C219" s="4" t="s">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="D219" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E219" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F219" s="8" t="s">
+        <v>46170</v>
+      </c>
+      <c r="F219" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="G219" s="4" t="s">
-        <v>105</v>
+      <c r="G219" s="5" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A220" s="4" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>93</v>
+        <v>14</v>
       </c>
       <c r="D220" s="4" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E220" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F220" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G220" s="4" t="s">
-        <v>105</v>
+        <v>46170</v>
+      </c>
+      <c r="F220" s="12" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.3">
@@ -6162,36 +6234,36 @@
         <v>10</v>
       </c>
       <c r="C221" s="4" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="D221" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E221" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F221" s="13" t="s">
-        <v>106</v>
+        <v>46170</v>
+      </c>
+      <c r="F221" s="12" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A222" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C222" s="4" t="s">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="D222" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E222" s="7">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="F222" s="13" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.3">
@@ -6202,36 +6274,37 @@
         <v>9</v>
       </c>
       <c r="C223" s="4" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D223" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E223" s="7">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="F223" s="13" t="s">
-        <v>108</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="G223" s="5"/>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A224" s="4" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B224" s="4" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="C224" s="4" t="s">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="D224" s="4" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E224" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F224" s="15" t="s">
-        <v>109</v>
+        <v>46170</v>
+      </c>
+      <c r="F224" s="12" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.3">
@@ -6242,36 +6315,36 @@
         <v>25</v>
       </c>
       <c r="C225" s="4" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="D225" s="4" t="s">
         <v>26</v>
       </c>
       <c r="E225" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F225" s="13" t="s">
-        <v>110</v>
+        <v>46170</v>
+      </c>
+      <c r="F225" s="12" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A226" s="4" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="C226" s="4" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="D226" s="4" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="E226" s="7">
         <v>46169</v>
       </c>
       <c r="F226" s="13" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.3">
@@ -6282,18 +6355,17 @@
         <v>7</v>
       </c>
       <c r="C227" s="4" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="D227" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E227" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F227" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="G227" s="5"/>
+        <v>46169</v>
+      </c>
+      <c r="F227" s="13" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A228" s="4" t="s">
@@ -6303,36 +6375,36 @@
         <v>7</v>
       </c>
       <c r="C228" s="4" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="D228" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E228" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F228" s="12" t="s">
-        <v>89</v>
+        <v>46169</v>
+      </c>
+      <c r="F228" s="13" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A229" s="4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C229" s="4" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D229" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E229" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F229" s="15" t="s">
-        <v>87</v>
+        <v>46169</v>
+      </c>
+      <c r="F229" s="13" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.3">
@@ -6343,397 +6415,389 @@
         <v>4</v>
       </c>
       <c r="C230" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D230" s="4" t="s">
         <v>5</v>
       </c>
       <c r="E230" s="7">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="F230" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="G230" s="5"/>
+        <v>101</v>
+      </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A231" s="4" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="C231" s="4" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="D231" s="4" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E231" s="7">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="F231" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="G231" s="6"/>
+        <v>102</v>
+      </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A232" s="4" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C232" s="4" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D232" s="4" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E232" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F232" s="13" t="s">
-        <v>84</v>
+        <v>46169</v>
+      </c>
+      <c r="F232" s="8" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A233" s="4" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C233" s="4" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="D233" s="4" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E233" s="7">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="F233" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="G233" s="6"/>
-    </row>
-    <row r="234" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A234" s="4" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C234" s="4" t="s">
-        <v>34</v>
+        <v>94</v>
       </c>
       <c r="D234" s="4" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E234" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F234" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G234" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="235" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>46169</v>
+      </c>
+      <c r="F234" s="13" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A235" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="C235" s="4" t="s">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="D235" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E235" s="7">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="F235" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="G235" s="5" t="s">
-        <v>112</v>
+      <c r="G235" s="4" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A236" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="C236" s="4" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="D236" s="4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E236" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F236" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="G236" s="5"/>
+        <v>46169</v>
+      </c>
+      <c r="F236" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G236" s="4" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A237" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="C237" s="4" t="s">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="D237" s="4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E237" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F237" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="G237" s="6"/>
+        <v>46169</v>
+      </c>
+      <c r="F237" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G237" s="4" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A238" s="4" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C238" s="4" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="D238" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E238" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F238" s="12" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="239" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>46169</v>
+      </c>
+      <c r="F238" s="13" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A239" s="4" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C239" s="4" t="s">
-        <v>37</v>
+        <v>90</v>
       </c>
       <c r="D239" s="4" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E239" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F239" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G239" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="240" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>46169</v>
+      </c>
+      <c r="F239" s="13" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A240" s="4" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C240" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D240" s="4" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E240" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F240" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G240" s="5" t="s">
-        <v>31</v>
+        <v>46169</v>
+      </c>
+      <c r="F240" s="13" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A241" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B241" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C241" s="4" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="D241" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E241" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F241" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="G241" s="5"/>
+        <v>46169</v>
+      </c>
+      <c r="F241" s="15" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A242" s="4" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B242" s="4" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C242" s="4" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="D242" s="4" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E242" s="7">
-        <v>46168</v>
-      </c>
-      <c r="F242" s="12" t="s">
-        <v>75</v>
+        <v>46169</v>
+      </c>
+      <c r="F242" s="13" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A243" s="4" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="C243" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D243" s="4" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E243" s="7">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="F243" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="G243" s="5"/>
+        <v>111</v>
+      </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A244" s="4" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C244" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D244" s="4" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E244" s="7">
         <v>46168</v>
       </c>
-      <c r="F244" s="13" t="s">
-        <v>85</v>
-      </c>
+      <c r="F244" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="G244" s="5"/>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A245" s="4" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="C245" s="4" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="D245" s="4" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="E245" s="7">
         <v>46168</v>
       </c>
       <c r="F245" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="G245" s="6"/>
+        <v>89</v>
+      </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A246" s="4" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="C246" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D246" s="4" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="E246" s="7">
         <v>46168</v>
       </c>
-      <c r="F246" s="12" t="s">
-        <v>81</v>
+      <c r="F246" s="15" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A247" s="4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B247" s="4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C247" s="4" t="s">
-        <v>71</v>
+        <v>29</v>
       </c>
       <c r="D247" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E247" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F247" s="9" t="s">
-        <v>72</v>
-      </c>
+        <v>46168</v>
+      </c>
+      <c r="F247" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="G247" s="5"/>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A248" s="4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C248" s="4" t="s">
-        <v>73</v>
+        <v>28</v>
       </c>
       <c r="D248" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E248" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F248" s="9" t="s">
-        <v>74</v>
-      </c>
+        <v>46168</v>
+      </c>
+      <c r="F248" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="G248" s="6"/>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A249" s="4" t="s">
@@ -6743,37 +6807,38 @@
         <v>4</v>
       </c>
       <c r="C249" s="4" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="D249" s="4" t="s">
         <v>5</v>
       </c>
       <c r="E249" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F249" s="10" t="s">
-        <v>65</v>
+        <v>46168</v>
+      </c>
+      <c r="F249" s="13" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A250" s="4" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C250" s="4" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D250" s="4" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E250" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F250" s="10" t="s">
-        <v>66</v>
-      </c>
+        <v>46168</v>
+      </c>
+      <c r="F250" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="G250" s="6"/>
     </row>
     <row r="251" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A251" s="4" t="s">
@@ -6783,13 +6848,13 @@
         <v>18</v>
       </c>
       <c r="C251" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D251" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D251" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E251" s="7">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="F251" s="8" t="s">
         <v>53</v>
@@ -6798,87 +6863,89 @@
         <v>112</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A252" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B252" s="4" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="C252" s="4" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="D252" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E252" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F252" s="9" t="s">
-        <v>57</v>
+        <v>46168</v>
+      </c>
+      <c r="F252" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G252" s="5" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A253" s="4" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="C253" s="4" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="D253" s="4" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E253" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F253" s="8" t="s">
-        <v>53</v>
-      </c>
+        <v>46168</v>
+      </c>
+      <c r="F253" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="G253" s="5"/>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A254" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B254" s="4" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="C254" s="4" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="D254" s="4" t="s">
         <v>23</v>
       </c>
       <c r="E254" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F254" s="9" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="255" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>46168</v>
+      </c>
+      <c r="F254" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="G254" s="6"/>
+    </row>
+    <row r="255" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A255" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B255" s="4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C255" s="4" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="D255" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E255" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F255" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G255" s="5" t="s">
-        <v>31</v>
+        <v>46168</v>
+      </c>
+      <c r="F255" s="12" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="256" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -6889,13 +6956,13 @@
         <v>18</v>
       </c>
       <c r="C256" s="4" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D256" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E256" s="7">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="F256" s="8" t="s">
         <v>53</v>
@@ -6904,103 +6971,458 @@
         <v>31</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A257" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B257" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C257" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D257" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E257" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F257" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G257" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A258" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B257" s="4" t="s">
+      <c r="B258" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C257" s="4" t="s">
+      <c r="C258" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D257" s="4" t="s">
+      <c r="D258" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E257" s="7">
+      <c r="E258" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F258" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="G258" s="5"/>
+    </row>
+    <row r="259" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A259" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B259" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C259" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D259" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E259" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F259" s="12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A260" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B260" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C260" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D260" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E260" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F260" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="G260" s="5"/>
+    </row>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A261" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B261" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C261" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D261" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E261" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F261" s="13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A262" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B262" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C262" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D262" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E262" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F262" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="G262" s="6"/>
+    </row>
+    <row r="263" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A263" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B263" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C263" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D263" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E263" s="7">
+        <v>46168</v>
+      </c>
+      <c r="F263" s="12" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A264" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B264" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C264" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D264" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E264" s="7">
         <v>46167</v>
       </c>
-      <c r="F257" s="9" t="s">
+      <c r="F264" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A265" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B265" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C265" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D265" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E265" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F265" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A266" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B266" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C266" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D266" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E266" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F266" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A267" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B267" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C267" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D267" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E267" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F267" s="10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A268" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B268" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C268" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D268" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E268" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F268" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G268" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A269" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B269" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C269" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D269" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E269" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F269" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A270" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B270" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C270" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D270" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E270" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F270" s="8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A271" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B271" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C271" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D271" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E271" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F271" s="9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A272" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B272" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C272" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D272" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E272" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F272" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G272" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A273" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B273" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C273" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D273" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E273" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F273" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G273" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A274" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B274" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C274" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D274" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E274" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F274" s="9" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A258" s="4" t="s">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A275" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B258" s="4" t="s">
+      <c r="B275" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C258" s="4" t="s">
+      <c r="C275" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D258" s="4" t="s">
+      <c r="D275" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E258" s="7">
+      <c r="E275" s="7">
         <v>46167</v>
       </c>
-      <c r="F258" s="10" t="s">
+      <c r="F275" s="10" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A259" s="4" t="s">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A276" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B259" s="4" t="s">
+      <c r="B276" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C259" s="4" t="s">
+      <c r="C276" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D259" s="4" t="s">
+      <c r="D276" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E259" s="7">
+      <c r="E276" s="7">
         <v>46167</v>
       </c>
-      <c r="F259" s="10" t="s">
+      <c r="F276" s="10" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A260" s="4" t="s">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A277" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B260" s="4" t="s">
+      <c r="B277" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C260" s="4" t="s">
+      <c r="C277" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="D260" s="4" t="s">
+      <c r="D277" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E260" s="7">
+      <c r="E277" s="7">
         <v>46167</v>
       </c>
-      <c r="F260" s="9" t="s">
+      <c r="F277" s="9" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A261" s="4" t="s">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A278" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B261" s="4" t="s">
+      <c r="B278" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C261" s="4" t="s">
+      <c r="C278" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D261" s="4" t="s">
+      <c r="D278" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E261" s="7">
+      <c r="E278" s="7">
         <v>46167</v>
       </c>
-      <c r="F261" s="9" t="s">
+      <c r="F278" s="9" t="s">
         <v>64</v>
       </c>
     </row>
@@ -7013,6 +7435,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6b3feda4-8a83-4113-98ac-b9b0c9bd9eab">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="6ca87d14-fc9d-4fcf-a42b-2754e6b3d00d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100AC3CF276C202334E979D7C4EA00D1CCA" ma:contentTypeVersion="13" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="fb5f1640dc82e33e0e3c6b4a833ae52f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6b3feda4-8a83-4113-98ac-b9b0c9bd9eab" xmlns:ns3="6ca87d14-fc9d-4fcf-a42b-2754e6b3d00d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dc11f865ff45eacf010d723a908863aa" ns2:_="" ns3:_="">
     <xsd:import namespace="6b3feda4-8a83-4113-98ac-b9b0c9bd9eab"/>
@@ -7219,27 +7661,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6b3feda4-8a83-4113-98ac-b9b0c9bd9eab">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="6ca87d14-fc9d-4fcf-a42b-2754e6b3d00d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6F72255-F15E-4B46-A16C-2F18C675CB37}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFC5C71E-79D6-437C-A06A-B0BD52E89317}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6b3feda4-8a83-4113-98ac-b9b0c9bd9eab"/>
+    <ds:schemaRef ds:uri="6ca87d14-fc9d-4fcf-a42b-2754e6b3d00d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E295317-F47C-4C92-88FC-9DAD72755AAC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7256,23 +7697,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFC5C71E-79D6-437C-A06A-B0BD52E89317}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6b3feda4-8a83-4113-98ac-b9b0c9bd9eab"/>
-    <ds:schemaRef ds:uri="6ca87d14-fc9d-4fcf-a42b-2754e6b3d00d"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6F72255-F15E-4B46-A16C-2F18C675CB37}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>